--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129060039</v>
+        <v>129060007</v>
       </c>
       <c r="B18" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,34 +2353,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469139</v>
+        <v>469364</v>
       </c>
       <c r="R18" t="n">
-        <v>7065094</v>
+        <v>7065232</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,6 +2418,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,10 +2449,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129059695</v>
+        <v>129059685</v>
       </c>
       <c r="B19" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2450,34 +2460,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469141</v>
+        <v>468878</v>
       </c>
       <c r="R19" t="n">
-        <v>7065114</v>
+        <v>7065401</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,6 +2527,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2520,21 +2540,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2551,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129059708</v>
+        <v>129059695</v>
       </c>
       <c r="B20" t="n">
-        <v>83015</v>
+        <v>80139</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,21 +2567,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2586,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468783</v>
+        <v>469141</v>
       </c>
       <c r="R20" t="n">
-        <v>7065001</v>
+        <v>7065114</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2635,17 +2640,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2663,10 +2668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129060003</v>
+        <v>129059708</v>
       </c>
       <c r="B21" t="n">
-        <v>91520</v>
+        <v>83015</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,21 +2679,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2698,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469006</v>
+        <v>468783</v>
       </c>
       <c r="R21" t="n">
-        <v>7065358</v>
+        <v>7065001</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,6 +2749,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2760,10 +2780,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129060007</v>
+        <v>129060003</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>91520</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2771,39 +2791,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469364</v>
+        <v>469006</v>
       </c>
       <c r="R22" t="n">
-        <v>7065232</v>
+        <v>7065358</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2836,11 +2851,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2867,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129059685</v>
+        <v>129060039</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2878,39 +2888,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468878</v>
+        <v>469139</v>
       </c>
       <c r="R23" t="n">
-        <v>7065401</v>
+        <v>7065094</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2943,11 +2948,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4426,50 +4426,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129059684</v>
+        <v>129060001</v>
       </c>
       <c r="B38" t="n">
-        <v>57723</v>
+        <v>91485</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>468895</v>
+        <v>468967</v>
       </c>
       <c r="R38" t="n">
-        <v>7065399</v>
+        <v>7065256</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4502,11 +4497,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4533,10 +4523,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129060026</v>
+        <v>129060002</v>
       </c>
       <c r="B39" t="n">
-        <v>57723</v>
+        <v>91520</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4544,39 +4534,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468886</v>
+        <v>469031</v>
       </c>
       <c r="R39" t="n">
-        <v>7065015</v>
+        <v>7065017</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4609,11 +4594,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4640,7 +4620,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129059715</v>
+        <v>129059684</v>
       </c>
       <c r="B40" t="n">
         <v>57723</v>
@@ -4680,10 +4660,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>469047</v>
+        <v>468895</v>
       </c>
       <c r="R40" t="n">
-        <v>7064912</v>
+        <v>7065399</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4747,45 +4727,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129060001</v>
+        <v>129060026</v>
       </c>
       <c r="B41" t="n">
-        <v>91485</v>
+        <v>57723</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468967</v>
+        <v>468886</v>
       </c>
       <c r="R41" t="n">
-        <v>7065256</v>
+        <v>7065015</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4818,6 +4803,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4844,10 +4834,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129060002</v>
+        <v>129059715</v>
       </c>
       <c r="B42" t="n">
-        <v>91520</v>
+        <v>57723</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4855,34 +4845,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469031</v>
+        <v>469047</v>
       </c>
       <c r="R42" t="n">
-        <v>7065017</v>
+        <v>7064912</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4915,6 +4910,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6374,10 +6374,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129059693</v>
+        <v>129060005</v>
       </c>
       <c r="B57" t="n">
-        <v>91538</v>
+        <v>91520</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6385,21 +6385,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6409,10 +6409,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>469137</v>
+        <v>468821</v>
       </c>
       <c r="R57" t="n">
-        <v>7065120</v>
+        <v>7065043</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6471,10 +6471,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129060005</v>
+        <v>129059693</v>
       </c>
       <c r="B58" t="n">
-        <v>91520</v>
+        <v>91538</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6482,21 +6482,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468821</v>
+        <v>469137</v>
       </c>
       <c r="R58" t="n">
-        <v>7065043</v>
+        <v>7065120</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8026,32 +8026,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129059677</v>
+        <v>129060047</v>
       </c>
       <c r="B73" t="n">
-        <v>78047</v>
+        <v>91881</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228579</v>
+        <v>2063</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>469160</v>
+        <v>469012</v>
       </c>
       <c r="R73" t="n">
-        <v>7065329</v>
+        <v>7065037</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8123,10 +8123,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129059714</v>
+        <v>129059698</v>
       </c>
       <c r="B74" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8134,39 +8134,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>468946</v>
+        <v>469120</v>
       </c>
       <c r="R74" t="n">
-        <v>7064969</v>
+        <v>7065078</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8201,11 +8196,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8214,6 +8204,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8230,10 +8235,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129059701</v>
+        <v>129060040</v>
       </c>
       <c r="B75" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8241,36 +8246,31 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>468991</v>
+        <v>469148</v>
       </c>
       <c r="R75" t="n">
         <v>7065056</v>
@@ -8306,11 +8306,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8337,45 +8332,50 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129060047</v>
+        <v>129059714</v>
       </c>
       <c r="B76" t="n">
-        <v>91881</v>
+        <v>57723</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>469012</v>
+        <v>468946</v>
       </c>
       <c r="R76" t="n">
-        <v>7065037</v>
+        <v>7064969</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8408,6 +8408,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8434,10 +8439,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129059698</v>
+        <v>129059701</v>
       </c>
       <c r="B77" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8445,34 +8450,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>469120</v>
+        <v>468991</v>
       </c>
       <c r="R77" t="n">
-        <v>7065078</v>
+        <v>7065056</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8507,6 +8517,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8515,21 +8530,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -8546,10 +8546,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129060040</v>
+        <v>129059677</v>
       </c>
       <c r="B78" t="n">
-        <v>80140</v>
+        <v>78047</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8557,21 +8557,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8581,10 +8581,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>469148</v>
+        <v>469160</v>
       </c>
       <c r="R78" t="n">
-        <v>7065056</v>
+        <v>7065329</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129060012</v>
+        <v>129059689</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469235</v>
+        <v>468887</v>
       </c>
       <c r="R2" t="n">
-        <v>7065256</v>
+        <v>7065318</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129060023</v>
+        <v>129059683</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469142</v>
+        <v>468964</v>
       </c>
       <c r="R3" t="n">
-        <v>7065079</v>
+        <v>7065331</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129060033</v>
+        <v>129060044</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>80139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,39 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469047</v>
+        <v>469111</v>
       </c>
       <c r="R4" t="n">
-        <v>7064905</v>
+        <v>7065086</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129060008</v>
+        <v>129059711</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>80139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,39 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469327</v>
+        <v>468844</v>
       </c>
       <c r="R5" t="n">
-        <v>7065224</v>
+        <v>7064978</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,11 +1039,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1087,6 +1047,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1103,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129060020</v>
+        <v>129059710</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,39 +1089,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468803</v>
+        <v>468844</v>
       </c>
       <c r="R6" t="n">
-        <v>7065369</v>
+        <v>7064978</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,11 +1151,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1194,6 +1159,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1210,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129060024</v>
+        <v>129060012</v>
       </c>
       <c r="B7" t="n">
         <v>57723</v>
@@ -1241,7 +1221,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1250,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469131</v>
+        <v>469235</v>
       </c>
       <c r="R7" t="n">
-        <v>7065083</v>
+        <v>7065256</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129059689</v>
+        <v>129060023</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,34 +1308,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468887</v>
+        <v>469142</v>
       </c>
       <c r="R8" t="n">
-        <v>7065318</v>
+        <v>7065079</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1373,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129059683</v>
+        <v>129060033</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1425,34 +1415,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468964</v>
+        <v>469047</v>
       </c>
       <c r="R9" t="n">
-        <v>7065331</v>
+        <v>7064905</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,6 +1480,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129060044</v>
+        <v>129060008</v>
       </c>
       <c r="B10" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,34 +1522,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469111</v>
+        <v>469327</v>
       </c>
       <c r="R10" t="n">
-        <v>7065086</v>
+        <v>7065224</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,6 +1587,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129059711</v>
+        <v>129060020</v>
       </c>
       <c r="B11" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,34 +1629,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468844</v>
+        <v>468803</v>
       </c>
       <c r="R11" t="n">
-        <v>7064978</v>
+        <v>7065369</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1681,6 +1696,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1689,21 +1709,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1720,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129059710</v>
+        <v>129060024</v>
       </c>
       <c r="B12" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,34 +1736,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468844</v>
+        <v>469131</v>
       </c>
       <c r="R12" t="n">
-        <v>7064978</v>
+        <v>7065083</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1793,6 +1803,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1801,21 +1816,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129060037</v>
+        <v>129060045</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>80139</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,39 +2047,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468874</v>
+        <v>469013</v>
       </c>
       <c r="R15" t="n">
-        <v>7064975</v>
+        <v>7065018</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129060045</v>
+        <v>129060022</v>
       </c>
       <c r="B16" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,34 +2144,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469013</v>
+        <v>468893</v>
       </c>
       <c r="R16" t="n">
-        <v>7065018</v>
+        <v>7065289</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,6 +2209,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129060022</v>
+        <v>129060037</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,27 +2251,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2275,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468893</v>
+        <v>468874</v>
       </c>
       <c r="R17" t="n">
-        <v>7065289</v>
+        <v>7064975</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2311,11 +2316,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129060007</v>
+        <v>129059708</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>83015</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,39 +2353,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469364</v>
+        <v>468783</v>
       </c>
       <c r="R18" t="n">
-        <v>7065232</v>
+        <v>7065001</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2420,11 +2415,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2433,6 +2423,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2449,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129059685</v>
+        <v>129060003</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>91523</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2460,39 +2465,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468878</v>
+        <v>469006</v>
       </c>
       <c r="R19" t="n">
-        <v>7065401</v>
+        <v>7065358</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2525,11 +2525,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2668,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129059708</v>
+        <v>129060039</v>
       </c>
       <c r="B21" t="n">
-        <v>83015</v>
+        <v>80140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2679,21 +2674,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468783</v>
+        <v>469139</v>
       </c>
       <c r="R21" t="n">
-        <v>7065001</v>
+        <v>7065094</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2749,21 +2744,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2780,10 +2760,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129060003</v>
+        <v>129060007</v>
       </c>
       <c r="B22" t="n">
-        <v>91520</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2791,34 +2771,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469006</v>
+        <v>469364</v>
       </c>
       <c r="R22" t="n">
-        <v>7065358</v>
+        <v>7065232</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2851,6 +2836,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2877,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129060039</v>
+        <v>129059685</v>
       </c>
       <c r="B23" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2888,34 +2878,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469139</v>
+        <v>468878</v>
       </c>
       <c r="R23" t="n">
-        <v>7065094</v>
+        <v>7065401</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,6 +2943,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3290,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129060048</v>
+        <v>129060046</v>
       </c>
       <c r="B27" t="n">
-        <v>91538</v>
+        <v>91519</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3301,21 +3301,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469135</v>
+        <v>469215</v>
       </c>
       <c r="R27" t="n">
-        <v>7065166</v>
+        <v>7065278</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3387,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129060046</v>
+        <v>129060035</v>
       </c>
       <c r="B28" t="n">
-        <v>91516</v>
+        <v>57883</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3398,34 +3398,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469215</v>
+        <v>469149</v>
       </c>
       <c r="R28" t="n">
-        <v>7065278</v>
+        <v>7065169</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,10 +3493,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129060035</v>
+        <v>129060048</v>
       </c>
       <c r="B29" t="n">
-        <v>57883</v>
+        <v>91541</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3495,43 +3504,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469149</v>
+        <v>469135</v>
       </c>
       <c r="R29" t="n">
-        <v>7065169</v>
+        <v>7065166</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3593,7 +3593,7 @@
         <v>129060006</v>
       </c>
       <c r="B30" t="n">
-        <v>92218</v>
+        <v>92223</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3794,32 +3794,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129059691</v>
+        <v>129059690</v>
       </c>
       <c r="B32" t="n">
-        <v>79034</v>
+        <v>83008</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468992</v>
+        <v>468887</v>
       </c>
       <c r="R32" t="n">
-        <v>7065224</v>
+        <v>7065318</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3891,45 +3891,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129059690</v>
+        <v>129059681</v>
       </c>
       <c r="B33" t="n">
-        <v>83008</v>
+        <v>57723</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>468887</v>
+        <v>469043</v>
       </c>
       <c r="R33" t="n">
-        <v>7065318</v>
+        <v>7065365</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3962,6 +3967,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3988,10 +3998,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129059681</v>
+        <v>129059691</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3999,39 +4009,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>469043</v>
+        <v>468992</v>
       </c>
       <c r="R34" t="n">
-        <v>7065365</v>
+        <v>7065224</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4064,11 +4069,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4207,10 +4207,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129060009</v>
+        <v>129059700</v>
       </c>
       <c r="B36" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4218,39 +4218,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>469298</v>
+        <v>469036</v>
       </c>
       <c r="R36" t="n">
-        <v>7065235</v>
+        <v>7065082</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4285,11 +4280,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4298,6 +4288,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4314,10 +4319,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129059700</v>
+        <v>129060009</v>
       </c>
       <c r="B37" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4325,34 +4330,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>469036</v>
+        <v>469298</v>
       </c>
       <c r="R37" t="n">
-        <v>7065082</v>
+        <v>7065235</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4387,6 +4397,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4395,21 +4410,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4429,7 +4429,7 @@
         <v>129060001</v>
       </c>
       <c r="B38" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4523,10 +4523,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129060002</v>
+        <v>129059684</v>
       </c>
       <c r="B39" t="n">
-        <v>91520</v>
+        <v>57723</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4534,34 +4534,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>469031</v>
+        <v>468895</v>
       </c>
       <c r="R39" t="n">
-        <v>7065017</v>
+        <v>7065399</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4594,6 +4599,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4620,7 +4630,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129059684</v>
+        <v>129060026</v>
       </c>
       <c r="B40" t="n">
         <v>57723</v>
@@ -4660,10 +4670,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>468895</v>
+        <v>468886</v>
       </c>
       <c r="R40" t="n">
-        <v>7065399</v>
+        <v>7065015</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4727,7 +4737,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129060026</v>
+        <v>129059715</v>
       </c>
       <c r="B41" t="n">
         <v>57723</v>
@@ -4767,10 +4777,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468886</v>
+        <v>469047</v>
       </c>
       <c r="R41" t="n">
-        <v>7065015</v>
+        <v>7064912</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4834,10 +4844,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129059715</v>
+        <v>129060002</v>
       </c>
       <c r="B42" t="n">
-        <v>57723</v>
+        <v>91523</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4845,39 +4855,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469047</v>
+        <v>469031</v>
       </c>
       <c r="R42" t="n">
-        <v>7064912</v>
+        <v>7065017</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4910,11 +4915,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5041,7 +5041,7 @@
         <v>129060049</v>
       </c>
       <c r="B44" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5543,32 +5543,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129060042</v>
+        <v>129059702</v>
       </c>
       <c r="B49" t="n">
-        <v>80043</v>
+        <v>91523</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>469356</v>
+        <v>468889</v>
       </c>
       <c r="R49" t="n">
-        <v>7065233</v>
+        <v>7065025</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5640,10 +5640,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129059697</v>
+        <v>129059709</v>
       </c>
       <c r="B50" t="n">
-        <v>80139</v>
+        <v>83005</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5651,21 +5651,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>310</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>469114</v>
+        <v>468844</v>
       </c>
       <c r="R50" t="n">
-        <v>7065083</v>
+        <v>7064978</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5752,32 +5752,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129059702</v>
+        <v>129060042</v>
       </c>
       <c r="B51" t="n">
-        <v>91520</v>
+        <v>80043</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>468889</v>
+        <v>469356</v>
       </c>
       <c r="R51" t="n">
-        <v>7065025</v>
+        <v>7065233</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5849,10 +5849,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129059709</v>
+        <v>129059697</v>
       </c>
       <c r="B52" t="n">
-        <v>83005</v>
+        <v>80139</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5860,21 +5860,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>310</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5884,10 +5884,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>468844</v>
+        <v>469114</v>
       </c>
       <c r="R52" t="n">
-        <v>7064978</v>
+        <v>7065083</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6175,10 +6175,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129060041</v>
+        <v>129060036</v>
       </c>
       <c r="B55" t="n">
-        <v>80140</v>
+        <v>57883</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6186,34 +6186,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>469143</v>
+        <v>468801</v>
       </c>
       <c r="R55" t="n">
-        <v>7065030</v>
+        <v>7065038</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6272,10 +6277,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129060036</v>
+        <v>129060041</v>
       </c>
       <c r="B56" t="n">
-        <v>57883</v>
+        <v>80140</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6283,39 +6288,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>468801</v>
+        <v>469143</v>
       </c>
       <c r="R56" t="n">
-        <v>7065038</v>
+        <v>7065030</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6377,7 +6377,7 @@
         <v>129060005</v>
       </c>
       <c r="B57" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>129059693</v>
       </c>
       <c r="B58" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>129059675</v>
       </c>
       <c r="B60" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>129059682</v>
       </c>
       <c r="B69" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7817,10 +7817,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129060051</v>
+        <v>129060011</v>
       </c>
       <c r="B71" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7828,34 +7828,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>469121</v>
+        <v>469245</v>
       </c>
       <c r="R71" t="n">
-        <v>7064885</v>
+        <v>7065256</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7892,7 +7897,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Med apotechier</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7919,10 +7924,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129060011</v>
+        <v>129060051</v>
       </c>
       <c r="B72" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7930,39 +7935,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>469245</v>
+        <v>469121</v>
       </c>
       <c r="R72" t="n">
-        <v>7065256</v>
+        <v>7064885</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8029,7 +8029,7 @@
         <v>129060047</v>
       </c>
       <c r="B73" t="n">
-        <v>91881</v>
+        <v>91884</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>129059696</v>
       </c>
       <c r="B82" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129059689</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129059683</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129060044</v>
+        <v>129060012</v>
       </c>
       <c r="B4" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469111</v>
+        <v>469235</v>
       </c>
       <c r="R4" t="n">
-        <v>7065086</v>
+        <v>7065256</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129059711</v>
+        <v>129060023</v>
       </c>
       <c r="B5" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +987,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468844</v>
+        <v>469142</v>
       </c>
       <c r="R5" t="n">
-        <v>7064978</v>
+        <v>7065079</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1039,6 +1054,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1047,21 +1067,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1078,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129059710</v>
+        <v>129060033</v>
       </c>
       <c r="B6" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,34 +1094,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468844</v>
+        <v>469047</v>
       </c>
       <c r="R6" t="n">
-        <v>7064978</v>
+        <v>7064905</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,6 +1161,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1159,21 +1174,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129060012</v>
+        <v>129060008</v>
       </c>
       <c r="B7" t="n">
         <v>57723</v>
@@ -1221,7 +1221,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469235</v>
+        <v>469327</v>
       </c>
       <c r="R7" t="n">
-        <v>7065256</v>
+        <v>7065224</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129060023</v>
+        <v>129060020</v>
       </c>
       <c r="B8" t="n">
         <v>57723</v>
@@ -1328,7 +1328,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469142</v>
+        <v>468803</v>
       </c>
       <c r="R8" t="n">
-        <v>7065079</v>
+        <v>7065369</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129060033</v>
+        <v>129060024</v>
       </c>
       <c r="B9" t="n">
         <v>57723</v>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469047</v>
+        <v>469131</v>
       </c>
       <c r="R9" t="n">
-        <v>7064905</v>
+        <v>7065083</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129060008</v>
+        <v>129059710</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,39 +1522,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469327</v>
+        <v>468844</v>
       </c>
       <c r="R10" t="n">
-        <v>7065224</v>
+        <v>7064978</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,11 +1584,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1602,6 +1592,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1618,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129060020</v>
+        <v>129060044</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,39 +1634,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468803</v>
+        <v>469111</v>
       </c>
       <c r="R11" t="n">
-        <v>7065369</v>
+        <v>7065086</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,11 +1694,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129060024</v>
+        <v>129059711</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,39 +1731,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469131</v>
+        <v>468844</v>
       </c>
       <c r="R12" t="n">
-        <v>7065083</v>
+        <v>7064978</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1803,11 +1793,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1816,6 +1801,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129059678</v>
+        <v>129060015</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,34 +1843,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469160</v>
+        <v>469142</v>
       </c>
       <c r="R13" t="n">
-        <v>7065329</v>
+        <v>7065300</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,6 +1908,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129060015</v>
+        <v>129059678</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1940,39 +1950,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469142</v>
+        <v>469160</v>
       </c>
       <c r="R14" t="n">
-        <v>7065300</v>
+        <v>7065329</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,11 +2010,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129060045</v>
+        <v>129060037</v>
       </c>
       <c r="B15" t="n">
-        <v>80139</v>
+        <v>57883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,34 +2047,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469013</v>
+        <v>468874</v>
       </c>
       <c r="R15" t="n">
-        <v>7065018</v>
+        <v>7064975</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129060022</v>
+        <v>129060045</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2144,39 +2149,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468893</v>
+        <v>469013</v>
       </c>
       <c r="R16" t="n">
-        <v>7065289</v>
+        <v>7065018</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,11 +2209,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2240,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129060037</v>
+        <v>129060022</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,27 +2246,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2280,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468874</v>
+        <v>468893</v>
       </c>
       <c r="R17" t="n">
-        <v>7064975</v>
+        <v>7065289</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,6 +2311,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129059708</v>
+        <v>129060038</v>
       </c>
       <c r="B18" t="n">
-        <v>83015</v>
+        <v>57883</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,34 +2353,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1467</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468783</v>
+        <v>469007</v>
       </c>
       <c r="R18" t="n">
-        <v>7065001</v>
+        <v>7064930</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2423,21 +2428,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2454,10 +2444,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129060003</v>
+        <v>129059708</v>
       </c>
       <c r="B19" t="n">
-        <v>91523</v>
+        <v>83016</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,21 +2455,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469006</v>
+        <v>468783</v>
       </c>
       <c r="R19" t="n">
-        <v>7065358</v>
+        <v>7065001</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,6 +2525,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2551,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129059695</v>
+        <v>129060039</v>
       </c>
       <c r="B20" t="n">
-        <v>80139</v>
+        <v>80141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,21 +2567,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2586,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469141</v>
+        <v>469139</v>
       </c>
       <c r="R20" t="n">
-        <v>7065114</v>
+        <v>7065094</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2632,21 +2637,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2663,10 +2653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129060039</v>
+        <v>129060003</v>
       </c>
       <c r="B21" t="n">
-        <v>80140</v>
+        <v>91526</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,21 +2664,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2698,10 +2688,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469139</v>
+        <v>469006</v>
       </c>
       <c r="R21" t="n">
-        <v>7065094</v>
+        <v>7065358</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2760,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129060007</v>
+        <v>129059695</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2771,39 +2761,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469364</v>
+        <v>469141</v>
       </c>
       <c r="R22" t="n">
-        <v>7065232</v>
+        <v>7065114</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2838,11 +2823,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2851,6 +2831,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2867,7 +2862,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129059685</v>
+        <v>129060007</v>
       </c>
       <c r="B23" t="n">
         <v>57723</v>
@@ -2907,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468878</v>
+        <v>469364</v>
       </c>
       <c r="R23" t="n">
-        <v>7065401</v>
+        <v>7065232</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2974,10 +2969,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129060038</v>
+        <v>129059685</v>
       </c>
       <c r="B24" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2985,27 +2980,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3014,10 +3009,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469007</v>
+        <v>468878</v>
       </c>
       <c r="R24" t="n">
-        <v>7064930</v>
+        <v>7065401</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3050,6 +3045,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3293,7 +3293,7 @@
         <v>129060046</v>
       </c>
       <c r="B27" t="n">
-        <v>91519</v>
+        <v>91522</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,54 +3387,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129060035</v>
+        <v>129060006</v>
       </c>
       <c r="B28" t="n">
-        <v>57883</v>
+        <v>92226</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469149</v>
+        <v>469045</v>
       </c>
       <c r="R28" t="n">
-        <v>7065169</v>
+        <v>7065011</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3496,7 +3487,7 @@
         <v>129060048</v>
       </c>
       <c r="B29" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3590,45 +3581,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129060006</v>
+        <v>129060035</v>
       </c>
       <c r="B30" t="n">
-        <v>92223</v>
+        <v>57883</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469045</v>
+        <v>469149</v>
       </c>
       <c r="R30" t="n">
-        <v>7065011</v>
+        <v>7065169</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3794,32 +3794,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129059690</v>
+        <v>129059691</v>
       </c>
       <c r="B32" t="n">
-        <v>83008</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468887</v>
+        <v>468992</v>
       </c>
       <c r="R32" t="n">
-        <v>7065318</v>
+        <v>7065224</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3891,50 +3891,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129059681</v>
+        <v>129059690</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>83009</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>469043</v>
+        <v>468887</v>
       </c>
       <c r="R33" t="n">
-        <v>7065365</v>
+        <v>7065318</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3967,11 +3962,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3998,10 +3988,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129059691</v>
+        <v>129059681</v>
       </c>
       <c r="B34" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4009,34 +3999,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>468992</v>
+        <v>469043</v>
       </c>
       <c r="R34" t="n">
-        <v>7065224</v>
+        <v>7065365</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4069,6 +4064,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4098,7 +4098,7 @@
         <v>129059694</v>
       </c>
       <c r="B35" t="n">
-        <v>83002</v>
+        <v>83003</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>129059700</v>
       </c>
       <c r="B36" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4426,32 +4426,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129060001</v>
+        <v>129060002</v>
       </c>
       <c r="B38" t="n">
-        <v>91488</v>
+        <v>91526</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4461,10 +4461,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>468967</v>
+        <v>469031</v>
       </c>
       <c r="R38" t="n">
-        <v>7065256</v>
+        <v>7065017</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4523,50 +4523,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129059684</v>
+        <v>129060001</v>
       </c>
       <c r="B39" t="n">
-        <v>57723</v>
+        <v>91491</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468895</v>
+        <v>468967</v>
       </c>
       <c r="R39" t="n">
-        <v>7065399</v>
+        <v>7065256</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4599,11 +4594,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4630,7 +4620,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129060026</v>
+        <v>129059684</v>
       </c>
       <c r="B40" t="n">
         <v>57723</v>
@@ -4670,10 +4660,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>468886</v>
+        <v>468895</v>
       </c>
       <c r="R40" t="n">
-        <v>7065015</v>
+        <v>7065399</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4737,7 +4727,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129059715</v>
+        <v>129060026</v>
       </c>
       <c r="B41" t="n">
         <v>57723</v>
@@ -4777,10 +4767,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>469047</v>
+        <v>468886</v>
       </c>
       <c r="R41" t="n">
-        <v>7064912</v>
+        <v>7065015</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4844,10 +4834,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129060002</v>
+        <v>129059715</v>
       </c>
       <c r="B42" t="n">
-        <v>91523</v>
+        <v>57723</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4855,34 +4845,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469031</v>
+        <v>469047</v>
       </c>
       <c r="R42" t="n">
-        <v>7065017</v>
+        <v>7064912</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4915,6 +4910,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4944,7 +4944,7 @@
         <v>129059671</v>
       </c>
       <c r="B43" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>129060049</v>
       </c>
       <c r="B44" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5135,10 +5135,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129059703</v>
+        <v>129060018</v>
       </c>
       <c r="B45" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5146,34 +5146,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>468883</v>
+        <v>469093</v>
       </c>
       <c r="R45" t="n">
-        <v>7065026</v>
+        <v>7065345</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5206,6 +5211,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5232,10 +5242,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129059699</v>
+        <v>129060017</v>
       </c>
       <c r="B46" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5243,34 +5253,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469071</v>
+        <v>469122</v>
       </c>
       <c r="R46" t="n">
-        <v>7065075</v>
+        <v>7065303</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5303,6 +5318,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5329,10 +5349,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129060018</v>
+        <v>129059703</v>
       </c>
       <c r="B47" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5340,39 +5360,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>469093</v>
+        <v>468883</v>
       </c>
       <c r="R47" t="n">
-        <v>7065345</v>
+        <v>7065026</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5405,11 +5420,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5436,10 +5446,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129060017</v>
+        <v>129059699</v>
       </c>
       <c r="B48" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5447,39 +5457,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>469122</v>
+        <v>469071</v>
       </c>
       <c r="R48" t="n">
-        <v>7065303</v>
+        <v>7065075</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5512,11 +5517,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5546,7 +5546,7 @@
         <v>129059702</v>
       </c>
       <c r="B49" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>129059709</v>
       </c>
       <c r="B50" t="n">
-        <v>83005</v>
+        <v>83006</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>129060042</v>
       </c>
       <c r="B51" t="n">
-        <v>80043</v>
+        <v>80044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>129059697</v>
       </c>
       <c r="B52" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>129060041</v>
       </c>
       <c r="B56" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>129060005</v>
       </c>
       <c r="B57" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>129059693</v>
       </c>
       <c r="B58" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6675,10 +6675,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129059675</v>
+        <v>129059674</v>
       </c>
       <c r="B60" t="n">
-        <v>91519</v>
+        <v>79035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6686,21 +6686,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>469197</v>
+        <v>469226</v>
       </c>
       <c r="R60" t="n">
-        <v>7065308</v>
+        <v>7065299</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6772,32 +6772,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129059674</v>
+        <v>129060043</v>
       </c>
       <c r="B61" t="n">
-        <v>79034</v>
+        <v>75027</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6807,10 +6807,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>469226</v>
+        <v>469011</v>
       </c>
       <c r="R61" t="n">
-        <v>7065299</v>
+        <v>7065022</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6869,32 +6869,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129060043</v>
+        <v>129060050</v>
       </c>
       <c r="B62" t="n">
-        <v>75027</v>
+        <v>79035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6904,10 +6904,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>469011</v>
+        <v>469118</v>
       </c>
       <c r="R62" t="n">
-        <v>7065022</v>
+        <v>7065190</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6940,6 +6940,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6966,10 +6971,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129060050</v>
+        <v>129060029</v>
       </c>
       <c r="B63" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6977,34 +6982,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>469118</v>
+        <v>468970</v>
       </c>
       <c r="R63" t="n">
-        <v>7065190</v>
+        <v>7064946</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7041,7 +7051,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7068,10 +7078,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129059686</v>
+        <v>129060021</v>
       </c>
       <c r="B64" t="n">
-        <v>83005</v>
+        <v>57723</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7079,34 +7089,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>468843</v>
+        <v>468788</v>
       </c>
       <c r="R64" t="n">
-        <v>7065390</v>
+        <v>7065344</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7141,6 +7156,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7149,21 +7169,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7180,10 +7185,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129059687</v>
+        <v>129060025</v>
       </c>
       <c r="B65" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7191,34 +7196,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>468843</v>
+        <v>469101</v>
       </c>
       <c r="R65" t="n">
-        <v>7065390</v>
+        <v>7065026</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7253,6 +7263,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7261,21 +7276,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7292,10 +7292,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129060029</v>
+        <v>129059686</v>
       </c>
       <c r="B66" t="n">
-        <v>57723</v>
+        <v>83006</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7303,39 +7303,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>310</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468970</v>
+        <v>468843</v>
       </c>
       <c r="R66" t="n">
-        <v>7064946</v>
+        <v>7065390</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7370,11 +7365,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7383,6 +7373,21 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -7399,10 +7404,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129060021</v>
+        <v>129059687</v>
       </c>
       <c r="B67" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7410,39 +7415,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468788</v>
+        <v>468843</v>
       </c>
       <c r="R67" t="n">
-        <v>7065344</v>
+        <v>7065390</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7477,11 +7477,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7490,6 +7485,21 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -7506,10 +7516,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129060025</v>
+        <v>129059675</v>
       </c>
       <c r="B68" t="n">
-        <v>57723</v>
+        <v>91522</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7517,39 +7527,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>469101</v>
+        <v>469197</v>
       </c>
       <c r="R68" t="n">
-        <v>7065026</v>
+        <v>7065308</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7582,11 +7587,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7613,10 +7613,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129059682</v>
+        <v>129059670</v>
       </c>
       <c r="B69" t="n">
-        <v>91523</v>
+        <v>57723</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7624,34 +7624,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>468990</v>
+        <v>469326</v>
       </c>
       <c r="R69" t="n">
-        <v>7065370</v>
+        <v>7065255</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7684,6 +7689,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7710,10 +7720,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129059670</v>
+        <v>129059682</v>
       </c>
       <c r="B70" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7721,39 +7731,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>469326</v>
+        <v>468990</v>
       </c>
       <c r="R70" t="n">
-        <v>7065255</v>
+        <v>7065370</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7786,11 +7791,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7817,10 +7817,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129060011</v>
+        <v>129060051</v>
       </c>
       <c r="B71" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7828,39 +7828,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>469245</v>
+        <v>469121</v>
       </c>
       <c r="R71" t="n">
-        <v>7065256</v>
+        <v>7064885</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7897,7 +7892,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7924,10 +7919,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129060051</v>
+        <v>129060011</v>
       </c>
       <c r="B72" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7935,34 +7930,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>469121</v>
+        <v>469245</v>
       </c>
       <c r="R72" t="n">
-        <v>7064885</v>
+        <v>7065256</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Med apotechier</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8026,32 +8026,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129060047</v>
+        <v>129059698</v>
       </c>
       <c r="B73" t="n">
-        <v>91884</v>
+        <v>80141</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2063</v>
+        <v>2081</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>469012</v>
+        <v>469120</v>
       </c>
       <c r="R73" t="n">
-        <v>7065037</v>
+        <v>7065078</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8107,6 +8107,21 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8123,10 +8138,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129059698</v>
+        <v>129060040</v>
       </c>
       <c r="B74" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8158,10 +8173,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>469120</v>
+        <v>469148</v>
       </c>
       <c r="R74" t="n">
-        <v>7065078</v>
+        <v>7065056</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8204,21 +8219,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8235,32 +8235,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129060040</v>
+        <v>129060047</v>
       </c>
       <c r="B75" t="n">
-        <v>80140</v>
+        <v>91887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>469148</v>
+        <v>469012</v>
       </c>
       <c r="R75" t="n">
-        <v>7065056</v>
+        <v>7065037</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8549,7 +8549,7 @@
         <v>129059677</v>
       </c>
       <c r="B78" t="n">
-        <v>78047</v>
+        <v>78048</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8964,10 +8964,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129059696</v>
+        <v>129059706</v>
       </c>
       <c r="B82" t="n">
-        <v>91541</v>
+        <v>80141</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8975,21 +8975,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8999,10 +8999,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>469141</v>
+        <v>468850</v>
       </c>
       <c r="R82" t="n">
-        <v>7065095</v>
+        <v>7065034</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9045,6 +9045,21 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9061,10 +9076,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129059676</v>
+        <v>129059696</v>
       </c>
       <c r="B83" t="n">
-        <v>83010</v>
+        <v>91544</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9072,21 +9087,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9096,10 +9111,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>469160</v>
+        <v>469141</v>
       </c>
       <c r="R83" t="n">
-        <v>7065329</v>
+        <v>7065095</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9158,10 +9173,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129059712</v>
+        <v>129059676</v>
       </c>
       <c r="B84" t="n">
-        <v>79034</v>
+        <v>83011</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9169,21 +9184,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9193,10 +9208,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>468868</v>
+        <v>469160</v>
       </c>
       <c r="R84" t="n">
-        <v>7064989</v>
+        <v>7065329</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9255,10 +9270,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129059706</v>
+        <v>129059712</v>
       </c>
       <c r="B85" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9266,21 +9281,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9290,10 +9305,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>468850</v>
+        <v>468868</v>
       </c>
       <c r="R85" t="n">
-        <v>7065034</v>
+        <v>7064989</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9336,21 +9351,6 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129059689</v>
+        <v>129059710</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>80141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468887</v>
+        <v>468844</v>
       </c>
       <c r="R2" t="n">
-        <v>7065318</v>
+        <v>7064978</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,6 +756,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -772,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129059683</v>
+        <v>129059689</v>
       </c>
       <c r="B3" t="n">
         <v>79035</v>
@@ -807,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468964</v>
+        <v>468887</v>
       </c>
       <c r="R3" t="n">
-        <v>7065331</v>
+        <v>7065318</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129060012</v>
+        <v>129059683</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469235</v>
+        <v>468964</v>
       </c>
       <c r="R4" t="n">
-        <v>7065256</v>
+        <v>7065331</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129060023</v>
+        <v>129060044</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,39 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469142</v>
+        <v>469111</v>
       </c>
       <c r="R5" t="n">
-        <v>7065079</v>
+        <v>7065086</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,11 +1052,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129060033</v>
+        <v>129059711</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,39 +1089,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469047</v>
+        <v>468844</v>
       </c>
       <c r="R6" t="n">
-        <v>7064905</v>
+        <v>7064978</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,11 +1151,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1174,6 +1159,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129060008</v>
+        <v>129060012</v>
       </c>
       <c r="B7" t="n">
         <v>57723</v>
@@ -1221,7 +1221,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469327</v>
+        <v>469235</v>
       </c>
       <c r="R7" t="n">
-        <v>7065224</v>
+        <v>7065256</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129060020</v>
+        <v>129060023</v>
       </c>
       <c r="B8" t="n">
         <v>57723</v>
@@ -1328,7 +1328,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468803</v>
+        <v>469142</v>
       </c>
       <c r="R8" t="n">
-        <v>7065369</v>
+        <v>7065079</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129060024</v>
+        <v>129060033</v>
       </c>
       <c r="B9" t="n">
         <v>57723</v>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469131</v>
+        <v>469047</v>
       </c>
       <c r="R9" t="n">
-        <v>7065083</v>
+        <v>7064905</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129059710</v>
+        <v>129060008</v>
       </c>
       <c r="B10" t="n">
-        <v>80141</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,34 +1522,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468844</v>
+        <v>469327</v>
       </c>
       <c r="R10" t="n">
-        <v>7064978</v>
+        <v>7065224</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,6 +1589,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1592,21 +1602,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1623,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129060044</v>
+        <v>129060020</v>
       </c>
       <c r="B11" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1634,34 +1629,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469111</v>
+        <v>468803</v>
       </c>
       <c r="R11" t="n">
-        <v>7065086</v>
+        <v>7065369</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,6 +1694,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129059711</v>
+        <v>129060024</v>
       </c>
       <c r="B12" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,34 +1736,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468844</v>
+        <v>469131</v>
       </c>
       <c r="R12" t="n">
-        <v>7064978</v>
+        <v>7065083</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1793,6 +1803,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1801,21 +1816,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129060037</v>
+        <v>129060022</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,27 +2047,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468874</v>
+        <v>468893</v>
       </c>
       <c r="R15" t="n">
-        <v>7064975</v>
+        <v>7065289</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,6 +2112,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2235,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129060022</v>
+        <v>129060037</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,27 +2251,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2275,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468893</v>
+        <v>468874</v>
       </c>
       <c r="R17" t="n">
-        <v>7065289</v>
+        <v>7064975</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2311,11 +2316,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129060038</v>
+        <v>129059708</v>
       </c>
       <c r="B18" t="n">
-        <v>57883</v>
+        <v>83016</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,39 +2353,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>1467</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469007</v>
+        <v>468783</v>
       </c>
       <c r="R18" t="n">
-        <v>7064930</v>
+        <v>7065001</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2428,6 +2423,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2444,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129059708</v>
+        <v>129060039</v>
       </c>
       <c r="B19" t="n">
-        <v>83016</v>
+        <v>80141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2455,21 +2465,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2479,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468783</v>
+        <v>469139</v>
       </c>
       <c r="R19" t="n">
-        <v>7065001</v>
+        <v>7065094</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2525,21 +2535,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2556,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129060039</v>
+        <v>129060003</v>
       </c>
       <c r="B20" t="n">
-        <v>80141</v>
+        <v>91526</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2567,21 +2562,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2591,10 +2586,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469139</v>
+        <v>469006</v>
       </c>
       <c r="R20" t="n">
-        <v>7065094</v>
+        <v>7065358</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,10 +2648,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129060003</v>
+        <v>129060007</v>
       </c>
       <c r="B21" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2664,34 +2659,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469006</v>
+        <v>469364</v>
       </c>
       <c r="R21" t="n">
-        <v>7065358</v>
+        <v>7065232</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,6 +2724,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2750,10 +2755,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129059695</v>
+        <v>129059685</v>
       </c>
       <c r="B22" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,34 +2766,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469141</v>
+        <v>468878</v>
       </c>
       <c r="R22" t="n">
-        <v>7065114</v>
+        <v>7065401</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2823,6 +2833,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2831,21 +2846,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2862,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129060007</v>
+        <v>129060038</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2873,27 +2873,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469364</v>
+        <v>469007</v>
       </c>
       <c r="R23" t="n">
-        <v>7065232</v>
+        <v>7064930</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2938,11 +2938,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2969,10 +2964,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129059685</v>
+        <v>129059695</v>
       </c>
       <c r="B24" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2980,39 +2975,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>468878</v>
+        <v>469141</v>
       </c>
       <c r="R24" t="n">
-        <v>7065401</v>
+        <v>7065114</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3047,11 +3037,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3060,6 +3045,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3387,32 +3387,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129060006</v>
+        <v>129060048</v>
       </c>
       <c r="B28" t="n">
-        <v>92226</v>
+        <v>91544</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469045</v>
+        <v>469135</v>
       </c>
       <c r="R28" t="n">
-        <v>7065011</v>
+        <v>7065166</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,32 +3484,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129060048</v>
+        <v>129060006</v>
       </c>
       <c r="B29" t="n">
-        <v>91544</v>
+        <v>92226</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3519,10 +3519,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469135</v>
+        <v>469045</v>
       </c>
       <c r="R29" t="n">
-        <v>7065166</v>
+        <v>7065011</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3581,10 +3581,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129060035</v>
+        <v>129060027</v>
       </c>
       <c r="B30" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3592,31 +3592,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3625,10 +3621,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469149</v>
+        <v>468896</v>
       </c>
       <c r="R30" t="n">
-        <v>7065169</v>
+        <v>7064986</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3661,6 +3657,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3687,10 +3688,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129060027</v>
+        <v>129060035</v>
       </c>
       <c r="B31" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3698,27 +3699,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3727,10 +3732,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>468896</v>
+        <v>469149</v>
       </c>
       <c r="R31" t="n">
-        <v>7064986</v>
+        <v>7065169</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3763,11 +3768,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3794,10 +3794,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129059691</v>
+        <v>129059681</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3805,34 +3805,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468992</v>
+        <v>469043</v>
       </c>
       <c r="R32" t="n">
-        <v>7065224</v>
+        <v>7065365</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3865,6 +3870,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3891,32 +3901,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129059690</v>
+        <v>129059691</v>
       </c>
       <c r="B33" t="n">
-        <v>83009</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3926,10 +3936,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>468887</v>
+        <v>468992</v>
       </c>
       <c r="R33" t="n">
-        <v>7065318</v>
+        <v>7065224</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3988,50 +3998,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129059681</v>
+        <v>129059690</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>83009</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>469043</v>
+        <v>468887</v>
       </c>
       <c r="R34" t="n">
-        <v>7065365</v>
+        <v>7065318</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4064,11 +4069,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4095,10 +4095,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129059694</v>
+        <v>129059700</v>
       </c>
       <c r="B35" t="n">
-        <v>83003</v>
+        <v>80141</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4106,21 +4106,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>469141</v>
+        <v>469036</v>
       </c>
       <c r="R35" t="n">
-        <v>7065114</v>
+        <v>7065082</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4179,17 +4179,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälgticka</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Phellinopsis conchata</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129059700</v>
+        <v>129059694</v>
       </c>
       <c r="B36" t="n">
-        <v>80141</v>
+        <v>83003</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4218,21 +4218,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4242,10 +4242,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>469036</v>
+        <v>469141</v>
       </c>
       <c r="R36" t="n">
-        <v>7065082</v>
+        <v>7065114</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4291,17 +4291,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>sälgticka</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Phellinopsis conchata</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4523,45 +4523,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129060001</v>
+        <v>129059684</v>
       </c>
       <c r="B39" t="n">
-        <v>91491</v>
+        <v>57723</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468967</v>
+        <v>468895</v>
       </c>
       <c r="R39" t="n">
-        <v>7065256</v>
+        <v>7065399</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4594,6 +4599,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4620,7 +4630,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129059684</v>
+        <v>129060026</v>
       </c>
       <c r="B40" t="n">
         <v>57723</v>
@@ -4660,10 +4670,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>468895</v>
+        <v>468886</v>
       </c>
       <c r="R40" t="n">
-        <v>7065399</v>
+        <v>7065015</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4727,7 +4737,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129060026</v>
+        <v>129059715</v>
       </c>
       <c r="B41" t="n">
         <v>57723</v>
@@ -4767,10 +4777,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468886</v>
+        <v>469047</v>
       </c>
       <c r="R41" t="n">
-        <v>7065015</v>
+        <v>7064912</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4834,50 +4844,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129059715</v>
+        <v>129060001</v>
       </c>
       <c r="B42" t="n">
-        <v>57723</v>
+        <v>91491</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469047</v>
+        <v>468967</v>
       </c>
       <c r="R42" t="n">
-        <v>7064912</v>
+        <v>7065256</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4910,11 +4915,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5038,10 +5038,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129060049</v>
+        <v>129060018</v>
       </c>
       <c r="B44" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,34 +5049,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>469012</v>
+        <v>469093</v>
       </c>
       <c r="R44" t="n">
-        <v>7065037</v>
+        <v>7065345</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5109,6 +5114,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5135,7 +5145,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129060018</v>
+        <v>129060017</v>
       </c>
       <c r="B45" t="n">
         <v>57723</v>
@@ -5175,10 +5185,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>469093</v>
+        <v>469122</v>
       </c>
       <c r="R45" t="n">
-        <v>7065345</v>
+        <v>7065303</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5242,10 +5252,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129060017</v>
+        <v>129060049</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5253,39 +5263,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469122</v>
+        <v>469012</v>
       </c>
       <c r="R46" t="n">
-        <v>7065303</v>
+        <v>7065037</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5318,11 +5323,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6675,10 +6675,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129059674</v>
+        <v>129059675</v>
       </c>
       <c r="B60" t="n">
-        <v>79035</v>
+        <v>91522</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6686,21 +6686,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>469226</v>
+        <v>469197</v>
       </c>
       <c r="R60" t="n">
-        <v>7065299</v>
+        <v>7065308</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6772,32 +6772,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129060043</v>
+        <v>129059686</v>
       </c>
       <c r="B61" t="n">
-        <v>75027</v>
+        <v>83006</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6428</v>
+        <v>310</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6807,10 +6807,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>469011</v>
+        <v>468843</v>
       </c>
       <c r="R61" t="n">
-        <v>7065022</v>
+        <v>7065390</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6853,6 +6853,21 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6869,10 +6884,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129060050</v>
+        <v>129059687</v>
       </c>
       <c r="B62" t="n">
-        <v>79035</v>
+        <v>80141</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6880,21 +6895,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6904,10 +6919,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>469118</v>
+        <v>468843</v>
       </c>
       <c r="R62" t="n">
-        <v>7065190</v>
+        <v>7065390</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6942,11 +6957,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -6955,6 +6965,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -6971,10 +6996,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129060029</v>
+        <v>129059674</v>
       </c>
       <c r="B63" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6982,39 +7007,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>468970</v>
+        <v>469226</v>
       </c>
       <c r="R63" t="n">
-        <v>7064946</v>
+        <v>7065299</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7047,11 +7067,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7078,50 +7093,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129060021</v>
+        <v>129060043</v>
       </c>
       <c r="B64" t="n">
-        <v>57723</v>
+        <v>75027</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>468788</v>
+        <v>469011</v>
       </c>
       <c r="R64" t="n">
-        <v>7065344</v>
+        <v>7065022</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7154,11 +7164,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7185,10 +7190,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129060025</v>
+        <v>129060050</v>
       </c>
       <c r="B65" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7196,39 +7201,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>469101</v>
+        <v>469118</v>
       </c>
       <c r="R65" t="n">
-        <v>7065026</v>
+        <v>7065190</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7292,10 +7292,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129059686</v>
+        <v>129060029</v>
       </c>
       <c r="B66" t="n">
-        <v>83006</v>
+        <v>57723</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7303,34 +7303,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468843</v>
+        <v>468970</v>
       </c>
       <c r="R66" t="n">
-        <v>7065390</v>
+        <v>7064946</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7365,6 +7370,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7373,21 +7383,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -7404,10 +7399,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129059687</v>
+        <v>129060021</v>
       </c>
       <c r="B67" t="n">
-        <v>80141</v>
+        <v>57723</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7415,34 +7410,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468843</v>
+        <v>468788</v>
       </c>
       <c r="R67" t="n">
-        <v>7065390</v>
+        <v>7065344</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7477,6 +7477,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7485,21 +7490,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -7516,10 +7506,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129059675</v>
+        <v>129060025</v>
       </c>
       <c r="B68" t="n">
-        <v>91522</v>
+        <v>57723</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7527,34 +7517,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>469197</v>
+        <v>469101</v>
       </c>
       <c r="R68" t="n">
-        <v>7065308</v>
+        <v>7065026</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7587,6 +7582,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7613,10 +7613,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129059670</v>
+        <v>129059682</v>
       </c>
       <c r="B69" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7624,39 +7624,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>469326</v>
+        <v>468990</v>
       </c>
       <c r="R69" t="n">
-        <v>7065255</v>
+        <v>7065370</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7689,11 +7684,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7720,10 +7710,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129059682</v>
+        <v>129059670</v>
       </c>
       <c r="B70" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7731,34 +7721,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468990</v>
+        <v>469326</v>
       </c>
       <c r="R70" t="n">
-        <v>7065370</v>
+        <v>7065255</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7791,6 +7786,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9076,10 +9076,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129059696</v>
+        <v>129059676</v>
       </c>
       <c r="B83" t="n">
-        <v>91544</v>
+        <v>83011</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9087,21 +9087,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>469141</v>
+        <v>469160</v>
       </c>
       <c r="R83" t="n">
-        <v>7065095</v>
+        <v>7065329</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9173,10 +9173,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129059676</v>
+        <v>129059712</v>
       </c>
       <c r="B84" t="n">
-        <v>83011</v>
+        <v>79035</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9184,21 +9184,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9208,10 +9208,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>469160</v>
+        <v>468868</v>
       </c>
       <c r="R84" t="n">
-        <v>7065329</v>
+        <v>7064989</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9270,10 +9270,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129059712</v>
+        <v>129059696</v>
       </c>
       <c r="B85" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9281,21 +9281,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9305,10 +9305,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>468868</v>
+        <v>469141</v>
       </c>
       <c r="R85" t="n">
-        <v>7064989</v>
+        <v>7065095</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129060015</v>
+        <v>129059678</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,39 +1843,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469142</v>
+        <v>469160</v>
       </c>
       <c r="R13" t="n">
-        <v>7065300</v>
+        <v>7065329</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,11 +1903,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129059678</v>
+        <v>129060015</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1950,34 +1940,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469160</v>
+        <v>469142</v>
       </c>
       <c r="R14" t="n">
-        <v>7065329</v>
+        <v>7065300</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,6 +2005,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129060022</v>
+        <v>129060045</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,39 +2047,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468893</v>
+        <v>469013</v>
       </c>
       <c r="R15" t="n">
-        <v>7065289</v>
+        <v>7065018</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,11 +2107,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2143,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129060045</v>
+        <v>129060022</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2154,34 +2144,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469013</v>
+        <v>468893</v>
       </c>
       <c r="R16" t="n">
-        <v>7065018</v>
+        <v>7065289</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,6 +2209,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2648,10 +2648,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129060007</v>
+        <v>129059695</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2659,39 +2659,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469364</v>
+        <v>469141</v>
       </c>
       <c r="R21" t="n">
-        <v>7065232</v>
+        <v>7065114</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2726,11 +2721,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2739,6 +2729,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2755,7 +2760,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129059685</v>
+        <v>129060007</v>
       </c>
       <c r="B22" t="n">
         <v>57723</v>
@@ -2795,10 +2800,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468878</v>
+        <v>469364</v>
       </c>
       <c r="R22" t="n">
-        <v>7065401</v>
+        <v>7065232</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2862,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129060038</v>
+        <v>129059685</v>
       </c>
       <c r="B23" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2873,27 +2878,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2902,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469007</v>
+        <v>468878</v>
       </c>
       <c r="R23" t="n">
-        <v>7064930</v>
+        <v>7065401</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2938,6 +2943,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2964,10 +2974,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129059695</v>
+        <v>129060038</v>
       </c>
       <c r="B24" t="n">
-        <v>80140</v>
+        <v>57883</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2975,34 +2985,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469141</v>
+        <v>469007</v>
       </c>
       <c r="R24" t="n">
-        <v>7065114</v>
+        <v>7064930</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,21 +3060,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3290,32 +3290,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129060046</v>
+        <v>129060006</v>
       </c>
       <c r="B27" t="n">
-        <v>91522</v>
+        <v>92226</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469215</v>
+        <v>469045</v>
       </c>
       <c r="R27" t="n">
-        <v>7065278</v>
+        <v>7065011</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3387,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129060048</v>
+        <v>129060046</v>
       </c>
       <c r="B28" t="n">
-        <v>91544</v>
+        <v>91522</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3398,21 +3398,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469135</v>
+        <v>469215</v>
       </c>
       <c r="R28" t="n">
-        <v>7065166</v>
+        <v>7065278</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,32 +3484,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129060006</v>
+        <v>129060048</v>
       </c>
       <c r="B29" t="n">
-        <v>92226</v>
+        <v>91544</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3519,10 +3519,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469045</v>
+        <v>469135</v>
       </c>
       <c r="R29" t="n">
-        <v>7065011</v>
+        <v>7065166</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4426,10 +4426,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129060002</v>
+        <v>129059684</v>
       </c>
       <c r="B38" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4437,34 +4437,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>469031</v>
+        <v>468895</v>
       </c>
       <c r="R38" t="n">
-        <v>7065017</v>
+        <v>7065399</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4497,6 +4502,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4523,7 +4533,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129059684</v>
+        <v>129060026</v>
       </c>
       <c r="B39" t="n">
         <v>57723</v>
@@ -4563,10 +4573,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468895</v>
+        <v>468886</v>
       </c>
       <c r="R39" t="n">
-        <v>7065399</v>
+        <v>7065015</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4630,7 +4640,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129060026</v>
+        <v>129059715</v>
       </c>
       <c r="B40" t="n">
         <v>57723</v>
@@ -4670,10 +4680,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>468886</v>
+        <v>469047</v>
       </c>
       <c r="R40" t="n">
-        <v>7065015</v>
+        <v>7064912</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4737,50 +4747,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129059715</v>
+        <v>129060001</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>91491</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>469047</v>
+        <v>468967</v>
       </c>
       <c r="R41" t="n">
-        <v>7064912</v>
+        <v>7065256</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4813,11 +4818,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4844,32 +4844,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129060001</v>
+        <v>129060002</v>
       </c>
       <c r="B42" t="n">
-        <v>91491</v>
+        <v>91526</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>468967</v>
+        <v>469031</v>
       </c>
       <c r="R42" t="n">
-        <v>7065256</v>
+        <v>7065017</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5640,10 +5640,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129059709</v>
+        <v>129059704</v>
       </c>
       <c r="B50" t="n">
-        <v>83006</v>
+        <v>57723</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5651,34 +5651,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>468844</v>
+        <v>468883</v>
       </c>
       <c r="R50" t="n">
-        <v>7064978</v>
+        <v>7065026</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5713,6 +5718,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5721,21 +5731,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5752,45 +5747,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129060042</v>
+        <v>129060031</v>
       </c>
       <c r="B51" t="n">
-        <v>80044</v>
+        <v>57723</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>469356</v>
+        <v>469014</v>
       </c>
       <c r="R51" t="n">
-        <v>7065233</v>
+        <v>7064913</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5823,6 +5823,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5849,10 +5854,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129059697</v>
+        <v>129059709</v>
       </c>
       <c r="B52" t="n">
-        <v>80140</v>
+        <v>83006</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5860,21 +5865,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>310</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5884,10 +5889,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>469114</v>
+        <v>468844</v>
       </c>
       <c r="R52" t="n">
-        <v>7065083</v>
+        <v>7064978</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5961,50 +5966,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129059704</v>
+        <v>129060042</v>
       </c>
       <c r="B53" t="n">
-        <v>57723</v>
+        <v>80044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>468883</v>
+        <v>469356</v>
       </c>
       <c r="R53" t="n">
-        <v>7065026</v>
+        <v>7065233</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6037,11 +6037,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6068,10 +6063,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129060031</v>
+        <v>129059697</v>
       </c>
       <c r="B54" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6079,39 +6074,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>469014</v>
+        <v>469114</v>
       </c>
       <c r="R54" t="n">
-        <v>7064913</v>
+        <v>7065083</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6146,11 +6136,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6159,6 +6144,21 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6772,10 +6772,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129059686</v>
+        <v>129059674</v>
       </c>
       <c r="B61" t="n">
-        <v>83006</v>
+        <v>79035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6783,21 +6783,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6807,10 +6807,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468843</v>
+        <v>469226</v>
       </c>
       <c r="R61" t="n">
-        <v>7065390</v>
+        <v>7065299</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6853,21 +6853,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6884,32 +6869,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129059687</v>
+        <v>129060043</v>
       </c>
       <c r="B62" t="n">
-        <v>80141</v>
+        <v>75027</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>6428</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6919,10 +6904,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468843</v>
+        <v>469011</v>
       </c>
       <c r="R62" t="n">
-        <v>7065390</v>
+        <v>7065022</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6965,21 +6950,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -6996,7 +6966,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129059674</v>
+        <v>129060050</v>
       </c>
       <c r="B63" t="n">
         <v>79035</v>
@@ -7031,10 +7001,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>469226</v>
+        <v>469118</v>
       </c>
       <c r="R63" t="n">
-        <v>7065299</v>
+        <v>7065190</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7067,6 +7037,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7093,45 +7068,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129060043</v>
+        <v>129060029</v>
       </c>
       <c r="B64" t="n">
-        <v>75027</v>
+        <v>57723</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>469011</v>
+        <v>468970</v>
       </c>
       <c r="R64" t="n">
-        <v>7065022</v>
+        <v>7064946</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7164,6 +7144,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7190,10 +7175,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129060050</v>
+        <v>129060021</v>
       </c>
       <c r="B65" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7201,34 +7186,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>469118</v>
+        <v>468788</v>
       </c>
       <c r="R65" t="n">
-        <v>7065190</v>
+        <v>7065344</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7265,7 +7255,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7292,7 +7282,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129060029</v>
+        <v>129060025</v>
       </c>
       <c r="B66" t="n">
         <v>57723</v>
@@ -7332,10 +7322,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468970</v>
+        <v>469101</v>
       </c>
       <c r="R66" t="n">
-        <v>7064946</v>
+        <v>7065026</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7399,10 +7389,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129060021</v>
+        <v>129059687</v>
       </c>
       <c r="B67" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7410,39 +7400,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468788</v>
+        <v>468843</v>
       </c>
       <c r="R67" t="n">
-        <v>7065344</v>
+        <v>7065390</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7477,11 +7462,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7490,6 +7470,21 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -7506,10 +7501,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129060025</v>
+        <v>129059686</v>
       </c>
       <c r="B68" t="n">
-        <v>57723</v>
+        <v>83006</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7517,39 +7512,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>310</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>469101</v>
+        <v>468843</v>
       </c>
       <c r="R68" t="n">
-        <v>7065026</v>
+        <v>7065390</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7584,11 +7574,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7597,6 +7582,21 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129059710</v>
+        <v>129060012</v>
       </c>
       <c r="B2" t="n">
-        <v>80141</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468844</v>
+        <v>469235</v>
       </c>
       <c r="R2" t="n">
-        <v>7064978</v>
+        <v>7065256</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,6 +753,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -756,21 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129059689</v>
+        <v>129060023</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468887</v>
+        <v>469142</v>
       </c>
       <c r="R3" t="n">
-        <v>7065318</v>
+        <v>7065079</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129059683</v>
+        <v>129060033</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468964</v>
+        <v>469047</v>
       </c>
       <c r="R4" t="n">
-        <v>7065331</v>
+        <v>7064905</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129060044</v>
+        <v>129060020</v>
       </c>
       <c r="B5" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469111</v>
+        <v>468803</v>
       </c>
       <c r="R5" t="n">
-        <v>7065086</v>
+        <v>7065369</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129059711</v>
+        <v>129059689</v>
       </c>
       <c r="B6" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468844</v>
+        <v>468887</v>
       </c>
       <c r="R6" t="n">
-        <v>7064978</v>
+        <v>7065318</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,21 +1184,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1190,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129060012</v>
+        <v>129059683</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,39 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469235</v>
+        <v>468964</v>
       </c>
       <c r="R7" t="n">
-        <v>7065256</v>
+        <v>7065331</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129060023</v>
+        <v>129060044</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,39 +1308,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469142</v>
+        <v>469111</v>
       </c>
       <c r="R8" t="n">
-        <v>7065079</v>
+        <v>7065086</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,11 +1368,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129060033</v>
+        <v>129059711</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,39 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469047</v>
+        <v>468844</v>
       </c>
       <c r="R9" t="n">
-        <v>7064905</v>
+        <v>7064978</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1482,11 +1467,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1495,6 +1475,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1511,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129060008</v>
+        <v>129060024</v>
       </c>
       <c r="B10" t="n">
         <v>57723</v>
@@ -1551,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469327</v>
+        <v>469131</v>
       </c>
       <c r="R10" t="n">
-        <v>7065224</v>
+        <v>7065083</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1613,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129060020</v>
+        <v>129060008</v>
       </c>
       <c r="B11" t="n">
         <v>57723</v>
@@ -1649,7 +1644,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1658,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468803</v>
+        <v>469327</v>
       </c>
       <c r="R11" t="n">
-        <v>7065369</v>
+        <v>7065224</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129060024</v>
+        <v>129059710</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,39 +1731,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469131</v>
+        <v>468844</v>
       </c>
       <c r="R12" t="n">
-        <v>7065083</v>
+        <v>7064978</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1803,11 +1793,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1816,6 +1801,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129059678</v>
+        <v>129060015</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,34 +1843,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469160</v>
+        <v>469142</v>
       </c>
       <c r="R13" t="n">
-        <v>7065329</v>
+        <v>7065300</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,6 +1908,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129060015</v>
+        <v>129059678</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1940,39 +1950,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469142</v>
+        <v>469160</v>
       </c>
       <c r="R14" t="n">
-        <v>7065300</v>
+        <v>7065329</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,11 +2010,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129060045</v>
+        <v>129060037</v>
       </c>
       <c r="B15" t="n">
-        <v>80140</v>
+        <v>57883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,34 +2047,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469013</v>
+        <v>468874</v>
       </c>
       <c r="R15" t="n">
-        <v>7065018</v>
+        <v>7064975</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129060022</v>
+        <v>129060045</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2144,39 +2149,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468893</v>
+        <v>469013</v>
       </c>
       <c r="R16" t="n">
-        <v>7065289</v>
+        <v>7065018</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,11 +2209,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2240,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129060037</v>
+        <v>129060022</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,27 +2246,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2280,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468874</v>
+        <v>468893</v>
       </c>
       <c r="R17" t="n">
-        <v>7064975</v>
+        <v>7065289</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,6 +2311,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129059708</v>
+        <v>129060039</v>
       </c>
       <c r="B18" t="n">
-        <v>83016</v>
+        <v>80141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468783</v>
+        <v>469139</v>
       </c>
       <c r="R18" t="n">
-        <v>7065001</v>
+        <v>7065094</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2423,21 +2423,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2454,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129060039</v>
+        <v>129059708</v>
       </c>
       <c r="B19" t="n">
-        <v>80141</v>
+        <v>83016</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,21 +2450,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469139</v>
+        <v>468783</v>
       </c>
       <c r="R19" t="n">
-        <v>7065094</v>
+        <v>7065001</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,6 +2520,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2551,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129060003</v>
+        <v>129059695</v>
       </c>
       <c r="B20" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,21 +2562,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469006</v>
+        <v>469141</v>
       </c>
       <c r="R20" t="n">
-        <v>7065358</v>
+        <v>7065114</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2632,6 +2632,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2648,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129059695</v>
+        <v>129060007</v>
       </c>
       <c r="B21" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2659,34 +2674,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469141</v>
+        <v>469364</v>
       </c>
       <c r="R21" t="n">
-        <v>7065114</v>
+        <v>7065232</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2721,6 +2741,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2729,21 +2754,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2760,7 +2770,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129060007</v>
+        <v>129059685</v>
       </c>
       <c r="B22" t="n">
         <v>57723</v>
@@ -2800,10 +2810,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469364</v>
+        <v>468878</v>
       </c>
       <c r="R22" t="n">
-        <v>7065232</v>
+        <v>7065401</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2867,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129059685</v>
+        <v>129060003</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2878,39 +2888,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468878</v>
+        <v>469006</v>
       </c>
       <c r="R23" t="n">
-        <v>7065401</v>
+        <v>7065358</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2943,11 +2948,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3290,45 +3290,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129060006</v>
+        <v>129060027</v>
       </c>
       <c r="B27" t="n">
-        <v>92226</v>
+        <v>57723</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469045</v>
+        <v>468896</v>
       </c>
       <c r="R27" t="n">
-        <v>7065011</v>
+        <v>7064986</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3361,6 +3366,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3387,10 +3397,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129060046</v>
+        <v>129060048</v>
       </c>
       <c r="B28" t="n">
-        <v>91522</v>
+        <v>91544</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3398,21 +3408,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3422,10 +3432,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469215</v>
+        <v>469135</v>
       </c>
       <c r="R28" t="n">
-        <v>7065278</v>
+        <v>7065166</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,32 +3494,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129060048</v>
+        <v>129060006</v>
       </c>
       <c r="B29" t="n">
-        <v>91544</v>
+        <v>92226</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3519,10 +3529,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469135</v>
+        <v>469045</v>
       </c>
       <c r="R29" t="n">
-        <v>7065166</v>
+        <v>7065011</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3581,10 +3591,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129060027</v>
+        <v>129060046</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>91522</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3592,39 +3602,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>468896</v>
+        <v>469215</v>
       </c>
       <c r="R30" t="n">
-        <v>7064986</v>
+        <v>7065278</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3657,11 +3662,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3794,10 +3794,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129059681</v>
+        <v>129059691</v>
       </c>
       <c r="B32" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3805,39 +3805,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>469043</v>
+        <v>468992</v>
       </c>
       <c r="R32" t="n">
-        <v>7065365</v>
+        <v>7065224</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3870,11 +3865,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3901,10 +3891,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129059691</v>
+        <v>129059681</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3912,34 +3902,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>468992</v>
+        <v>469043</v>
       </c>
       <c r="R33" t="n">
-        <v>7065224</v>
+        <v>7065365</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3972,6 +3967,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4207,10 +4207,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129059694</v>
+        <v>129060009</v>
       </c>
       <c r="B36" t="n">
-        <v>83003</v>
+        <v>57723</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4218,34 +4218,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>469141</v>
+        <v>469298</v>
       </c>
       <c r="R36" t="n">
-        <v>7065114</v>
+        <v>7065235</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4280,6 +4285,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4288,21 +4298,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>sälgticka</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Phellinopsis conchata</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4319,10 +4314,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129060009</v>
+        <v>129059694</v>
       </c>
       <c r="B37" t="n">
-        <v>57723</v>
+        <v>83003</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4330,39 +4325,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>469298</v>
+        <v>469141</v>
       </c>
       <c r="R37" t="n">
-        <v>7065235</v>
+        <v>7065114</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4397,11 +4387,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4410,6 +4395,21 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälgticka</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Phellinopsis conchata</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4426,10 +4426,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129059684</v>
+        <v>129060002</v>
       </c>
       <c r="B38" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4437,39 +4437,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>468895</v>
+        <v>469031</v>
       </c>
       <c r="R38" t="n">
-        <v>7065399</v>
+        <v>7065017</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4502,11 +4497,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4533,50 +4523,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129060026</v>
+        <v>129060001</v>
       </c>
       <c r="B39" t="n">
-        <v>57723</v>
+        <v>91491</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468886</v>
+        <v>468967</v>
       </c>
       <c r="R39" t="n">
-        <v>7065015</v>
+        <v>7065256</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4609,11 +4594,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4640,7 +4620,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129059715</v>
+        <v>129060026</v>
       </c>
       <c r="B40" t="n">
         <v>57723</v>
@@ -4680,10 +4660,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>469047</v>
+        <v>468886</v>
       </c>
       <c r="R40" t="n">
-        <v>7064912</v>
+        <v>7065015</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4747,45 +4727,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129060001</v>
+        <v>129059684</v>
       </c>
       <c r="B41" t="n">
-        <v>91491</v>
+        <v>57723</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468967</v>
+        <v>468895</v>
       </c>
       <c r="R41" t="n">
-        <v>7065256</v>
+        <v>7065399</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4818,6 +4803,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4844,10 +4834,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129060002</v>
+        <v>129059715</v>
       </c>
       <c r="B42" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4855,34 +4845,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469031</v>
+        <v>469047</v>
       </c>
       <c r="R42" t="n">
-        <v>7065017</v>
+        <v>7064912</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4915,6 +4910,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5038,10 +5038,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129060018</v>
+        <v>129059703</v>
       </c>
       <c r="B44" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,39 +5049,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>469093</v>
+        <v>468883</v>
       </c>
       <c r="R44" t="n">
-        <v>7065345</v>
+        <v>7065026</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5114,11 +5109,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5145,10 +5135,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129060017</v>
+        <v>129059699</v>
       </c>
       <c r="B45" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5156,39 +5146,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>469122</v>
+        <v>469071</v>
       </c>
       <c r="R45" t="n">
-        <v>7065303</v>
+        <v>7065075</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5221,11 +5206,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5349,10 +5329,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129059703</v>
+        <v>129060018</v>
       </c>
       <c r="B47" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5360,34 +5340,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>468883</v>
+        <v>469093</v>
       </c>
       <c r="R47" t="n">
-        <v>7065026</v>
+        <v>7065345</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5420,6 +5405,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5446,10 +5436,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129059699</v>
+        <v>129060017</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5457,34 +5447,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>469071</v>
+        <v>469122</v>
       </c>
       <c r="R48" t="n">
-        <v>7065075</v>
+        <v>7065303</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5517,6 +5512,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5543,10 +5543,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129059702</v>
+        <v>129059709</v>
       </c>
       <c r="B49" t="n">
-        <v>91526</v>
+        <v>83006</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>310</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>468889</v>
+        <v>468844</v>
       </c>
       <c r="R49" t="n">
-        <v>7065025</v>
+        <v>7064978</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5624,6 +5624,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5640,10 +5655,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129059704</v>
+        <v>129059697</v>
       </c>
       <c r="B50" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5651,39 +5666,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>468883</v>
+        <v>469114</v>
       </c>
       <c r="R50" t="n">
-        <v>7065026</v>
+        <v>7065083</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5718,11 +5728,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5731,6 +5736,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5747,10 +5767,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129060031</v>
+        <v>129059702</v>
       </c>
       <c r="B51" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5758,39 +5778,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>469014</v>
+        <v>468889</v>
       </c>
       <c r="R51" t="n">
-        <v>7064913</v>
+        <v>7065025</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5823,11 +5838,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5854,32 +5864,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129059709</v>
+        <v>129060042</v>
       </c>
       <c r="B52" t="n">
-        <v>83006</v>
+        <v>80044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>310</v>
+        <v>6456</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5889,10 +5899,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>468844</v>
+        <v>469356</v>
       </c>
       <c r="R52" t="n">
-        <v>7064978</v>
+        <v>7065233</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5935,21 +5945,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -5966,45 +5961,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129060042</v>
+        <v>129060031</v>
       </c>
       <c r="B53" t="n">
-        <v>80044</v>
+        <v>57723</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>469356</v>
+        <v>469014</v>
       </c>
       <c r="R53" t="n">
-        <v>7065233</v>
+        <v>7064913</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6037,6 +6037,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6063,10 +6068,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129059697</v>
+        <v>129059704</v>
       </c>
       <c r="B54" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6074,34 +6079,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>469114</v>
+        <v>468883</v>
       </c>
       <c r="R54" t="n">
-        <v>7065083</v>
+        <v>7065026</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6136,6 +6146,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6144,21 +6159,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6175,10 +6175,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129060036</v>
+        <v>129060041</v>
       </c>
       <c r="B55" t="n">
-        <v>57883</v>
+        <v>80141</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6186,39 +6186,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>468801</v>
+        <v>469143</v>
       </c>
       <c r="R55" t="n">
-        <v>7065038</v>
+        <v>7065030</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6277,10 +6272,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129060041</v>
+        <v>129060036</v>
       </c>
       <c r="B56" t="n">
-        <v>80141</v>
+        <v>57883</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6288,34 +6283,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>469143</v>
+        <v>468801</v>
       </c>
       <c r="R56" t="n">
-        <v>7065030</v>
+        <v>7065038</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6675,10 +6675,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129059675</v>
+        <v>129059686</v>
       </c>
       <c r="B60" t="n">
-        <v>91522</v>
+        <v>83006</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6686,21 +6686,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>310</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>469197</v>
+        <v>468843</v>
       </c>
       <c r="R60" t="n">
-        <v>7065308</v>
+        <v>7065390</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6756,6 +6756,21 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6772,10 +6787,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129059674</v>
+        <v>129059687</v>
       </c>
       <c r="B61" t="n">
-        <v>79035</v>
+        <v>80141</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6783,21 +6798,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6807,10 +6822,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>469226</v>
+        <v>468843</v>
       </c>
       <c r="R61" t="n">
-        <v>7065299</v>
+        <v>7065390</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6853,6 +6868,21 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6869,32 +6899,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129060043</v>
+        <v>129059674</v>
       </c>
       <c r="B62" t="n">
-        <v>75027</v>
+        <v>79035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6904,10 +6934,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>469011</v>
+        <v>469226</v>
       </c>
       <c r="R62" t="n">
-        <v>7065022</v>
+        <v>7065299</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7068,10 +7098,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129060029</v>
+        <v>129059675</v>
       </c>
       <c r="B64" t="n">
-        <v>57723</v>
+        <v>91522</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7079,39 +7109,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>468970</v>
+        <v>469197</v>
       </c>
       <c r="R64" t="n">
-        <v>7064946</v>
+        <v>7065308</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7144,11 +7169,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7175,50 +7195,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129060021</v>
+        <v>129060043</v>
       </c>
       <c r="B65" t="n">
-        <v>57723</v>
+        <v>75027</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>468788</v>
+        <v>469011</v>
       </c>
       <c r="R65" t="n">
-        <v>7065344</v>
+        <v>7065022</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7251,11 +7266,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7282,7 +7292,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129060025</v>
+        <v>129060029</v>
       </c>
       <c r="B66" t="n">
         <v>57723</v>
@@ -7322,10 +7332,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>469101</v>
+        <v>468970</v>
       </c>
       <c r="R66" t="n">
-        <v>7065026</v>
+        <v>7064946</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7389,10 +7399,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129059687</v>
+        <v>129060025</v>
       </c>
       <c r="B67" t="n">
-        <v>80141</v>
+        <v>57723</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7400,34 +7410,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468843</v>
+        <v>469101</v>
       </c>
       <c r="R67" t="n">
-        <v>7065390</v>
+        <v>7065026</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7462,6 +7477,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7470,21 +7490,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -7501,10 +7506,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129059686</v>
+        <v>129060021</v>
       </c>
       <c r="B68" t="n">
-        <v>83006</v>
+        <v>57723</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7512,34 +7517,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>468843</v>
+        <v>468788</v>
       </c>
       <c r="R68" t="n">
-        <v>7065390</v>
+        <v>7065344</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7574,6 +7584,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7582,21 +7597,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8026,10 +8026,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129059698</v>
+        <v>129059714</v>
       </c>
       <c r="B73" t="n">
-        <v>80141</v>
+        <v>57723</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8037,34 +8037,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>469120</v>
+        <v>468946</v>
       </c>
       <c r="R73" t="n">
-        <v>7065078</v>
+        <v>7064969</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8099,6 +8104,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -8107,21 +8117,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8138,10 +8133,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129060040</v>
+        <v>129059701</v>
       </c>
       <c r="B74" t="n">
-        <v>80141</v>
+        <v>57723</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8149,31 +8144,36 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>469148</v>
+        <v>468991</v>
       </c>
       <c r="R74" t="n">
         <v>7065056</v>
@@ -8209,6 +8209,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8235,32 +8240,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129060047</v>
+        <v>129059698</v>
       </c>
       <c r="B75" t="n">
-        <v>91887</v>
+        <v>80141</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2063</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8270,10 +8275,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>469012</v>
+        <v>469120</v>
       </c>
       <c r="R75" t="n">
-        <v>7065037</v>
+        <v>7065078</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8316,6 +8321,21 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8332,10 +8352,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129059714</v>
+        <v>129060040</v>
       </c>
       <c r="B76" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8343,39 +8363,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>468946</v>
+        <v>469148</v>
       </c>
       <c r="R76" t="n">
-        <v>7064969</v>
+        <v>7065056</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8408,11 +8423,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8439,50 +8449,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129059701</v>
+        <v>129060047</v>
       </c>
       <c r="B77" t="n">
-        <v>57723</v>
+        <v>91887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>468991</v>
+        <v>469012</v>
       </c>
       <c r="R77" t="n">
-        <v>7065056</v>
+        <v>7065037</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8515,11 +8520,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8643,7 +8643,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129059680</v>
+        <v>129060016</v>
       </c>
       <c r="B79" t="n">
         <v>57723</v>
@@ -8683,10 +8683,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>469094</v>
+        <v>469152</v>
       </c>
       <c r="R79" t="n">
-        <v>7065363</v>
+        <v>7065299</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8750,7 +8750,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129060016</v>
+        <v>129060014</v>
       </c>
       <c r="B80" t="n">
         <v>57723</v>
@@ -8781,7 +8781,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -8790,10 +8790,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>469152</v>
+        <v>469198</v>
       </c>
       <c r="R80" t="n">
-        <v>7065299</v>
+        <v>7065284</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8857,7 +8857,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129060014</v>
+        <v>129059680</v>
       </c>
       <c r="B81" t="n">
         <v>57723</v>
@@ -8888,7 +8888,7 @@
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -8897,10 +8897,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>469198</v>
+        <v>469094</v>
       </c>
       <c r="R81" t="n">
-        <v>7065284</v>
+        <v>7065363</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9076,10 +9076,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129059676</v>
+        <v>129059696</v>
       </c>
       <c r="B83" t="n">
-        <v>83011</v>
+        <v>91544</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9087,21 +9087,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>469160</v>
+        <v>469141</v>
       </c>
       <c r="R83" t="n">
-        <v>7065329</v>
+        <v>7065095</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9173,10 +9173,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129059712</v>
+        <v>129059676</v>
       </c>
       <c r="B84" t="n">
-        <v>79035</v>
+        <v>83011</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9184,21 +9184,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9208,10 +9208,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>468868</v>
+        <v>469160</v>
       </c>
       <c r="R84" t="n">
-        <v>7064989</v>
+        <v>7065329</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9270,10 +9270,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129059696</v>
+        <v>129059692</v>
       </c>
       <c r="B85" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9281,34 +9281,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>469141</v>
+        <v>469137</v>
       </c>
       <c r="R85" t="n">
-        <v>7065095</v>
+        <v>7065206</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9341,6 +9346,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9581,10 +9591,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129059692</v>
+        <v>129059712</v>
       </c>
       <c r="B88" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9592,39 +9602,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>469137</v>
+        <v>468868</v>
       </c>
       <c r="R88" t="n">
-        <v>7065206</v>
+        <v>7064989</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9657,11 +9662,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129060012</v>
+        <v>129059689</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469235</v>
+        <v>468887</v>
       </c>
       <c r="R2" t="n">
-        <v>7065256</v>
+        <v>7065318</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129060023</v>
+        <v>129059683</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469142</v>
+        <v>468964</v>
       </c>
       <c r="R3" t="n">
-        <v>7065079</v>
+        <v>7065331</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129060033</v>
+        <v>129060044</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>80144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,39 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469047</v>
+        <v>469111</v>
       </c>
       <c r="R4" t="n">
-        <v>7064905</v>
+        <v>7065086</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129060020</v>
+        <v>129059711</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>80144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,39 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468803</v>
+        <v>468844</v>
       </c>
       <c r="R5" t="n">
-        <v>7065369</v>
+        <v>7064978</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,11 +1039,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1087,6 +1047,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1103,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129059689</v>
+        <v>129059710</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>80145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468887</v>
+        <v>468844</v>
       </c>
       <c r="R6" t="n">
-        <v>7065318</v>
+        <v>7064978</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,6 +1159,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1200,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129059683</v>
+        <v>129060012</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,34 +1201,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468964</v>
+        <v>469235</v>
       </c>
       <c r="R7" t="n">
-        <v>7065331</v>
+        <v>7065256</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129060044</v>
+        <v>129060023</v>
       </c>
       <c r="B8" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,34 +1308,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469111</v>
+        <v>469142</v>
       </c>
       <c r="R8" t="n">
-        <v>7065086</v>
+        <v>7065079</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,6 +1373,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129059711</v>
+        <v>129060033</v>
       </c>
       <c r="B9" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,34 +1415,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468844</v>
+        <v>469047</v>
       </c>
       <c r="R9" t="n">
-        <v>7064978</v>
+        <v>7064905</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,6 +1482,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1475,21 +1495,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1506,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129060024</v>
+        <v>129060008</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1546,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469131</v>
+        <v>469327</v>
       </c>
       <c r="R10" t="n">
-        <v>7065083</v>
+        <v>7065224</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129060008</v>
+        <v>129060020</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,7 +1649,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1653,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469327</v>
+        <v>468803</v>
       </c>
       <c r="R11" t="n">
-        <v>7065224</v>
+        <v>7065369</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129059710</v>
+        <v>129060024</v>
       </c>
       <c r="B12" t="n">
-        <v>80141</v>
+        <v>57725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,34 +1736,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468844</v>
+        <v>469131</v>
       </c>
       <c r="R12" t="n">
-        <v>7064978</v>
+        <v>7065083</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1793,6 +1803,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1801,21 +1816,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129060015</v>
+        <v>129059678</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,39 +1843,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469142</v>
+        <v>469160</v>
       </c>
       <c r="R13" t="n">
-        <v>7065300</v>
+        <v>7065329</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,11 +1903,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129059678</v>
+        <v>129060015</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1950,34 +1940,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469160</v>
+        <v>469142</v>
       </c>
       <c r="R14" t="n">
-        <v>7065329</v>
+        <v>7065300</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,6 +2005,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129060037</v>
+        <v>129060045</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>80144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,39 +2047,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468874</v>
+        <v>469013</v>
       </c>
       <c r="R15" t="n">
-        <v>7064975</v>
+        <v>7065018</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129060045</v>
+        <v>129060022</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,34 +2144,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469013</v>
+        <v>468893</v>
       </c>
       <c r="R16" t="n">
-        <v>7065018</v>
+        <v>7065289</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,6 +2209,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129060022</v>
+        <v>129060037</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>57885</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,27 +2251,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2275,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468893</v>
+        <v>468874</v>
       </c>
       <c r="R17" t="n">
-        <v>7065289</v>
+        <v>7064975</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2311,11 +2316,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129060039</v>
+        <v>129060003</v>
       </c>
       <c r="B18" t="n">
-        <v>80141</v>
+        <v>91533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469139</v>
+        <v>469006</v>
       </c>
       <c r="R18" t="n">
-        <v>7065094</v>
+        <v>7065358</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2439,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129059708</v>
+        <v>129060007</v>
       </c>
       <c r="B19" t="n">
-        <v>83016</v>
+        <v>57725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2450,34 +2450,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468783</v>
+        <v>469364</v>
       </c>
       <c r="R19" t="n">
-        <v>7065001</v>
+        <v>7065232</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,6 +2517,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2520,21 +2530,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2551,10 +2546,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129059695</v>
+        <v>129059685</v>
       </c>
       <c r="B20" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,34 +2557,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469141</v>
+        <v>468878</v>
       </c>
       <c r="R20" t="n">
-        <v>7065114</v>
+        <v>7065401</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2624,6 +2624,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2632,21 +2637,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2663,10 +2653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129060007</v>
+        <v>129059708</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>83020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,39 +2664,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469364</v>
+        <v>468783</v>
       </c>
       <c r="R21" t="n">
-        <v>7065232</v>
+        <v>7065001</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2741,11 +2726,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2754,6 +2734,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2770,10 +2765,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129059685</v>
+        <v>129060039</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>80145</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2781,39 +2776,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468878</v>
+        <v>469139</v>
       </c>
       <c r="R22" t="n">
-        <v>7065401</v>
+        <v>7065094</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,11 +2836,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2877,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129060003</v>
+        <v>129059695</v>
       </c>
       <c r="B23" t="n">
-        <v>91526</v>
+        <v>80144</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2888,21 +2873,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2912,10 +2897,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469006</v>
+        <v>469141</v>
       </c>
       <c r="R23" t="n">
-        <v>7065358</v>
+        <v>7065114</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2958,6 +2943,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -2977,7 +2977,7 @@
         <v>129060038</v>
       </c>
       <c r="B24" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>129060013</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>129060010</v>
       </c>
       <c r="B26" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>129060027</v>
       </c>
       <c r="B27" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3397,10 +3397,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129060048</v>
+        <v>129060046</v>
       </c>
       <c r="B28" t="n">
-        <v>91544</v>
+        <v>91529</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3408,21 +3408,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469135</v>
+        <v>469215</v>
       </c>
       <c r="R28" t="n">
-        <v>7065166</v>
+        <v>7065278</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3494,32 +3494,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129060006</v>
+        <v>129060048</v>
       </c>
       <c r="B29" t="n">
-        <v>92226</v>
+        <v>91551</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469045</v>
+        <v>469135</v>
       </c>
       <c r="R29" t="n">
-        <v>7065011</v>
+        <v>7065166</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3591,32 +3591,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129060046</v>
+        <v>129060006</v>
       </c>
       <c r="B30" t="n">
-        <v>91522</v>
+        <v>92233</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469215</v>
+        <v>469045</v>
       </c>
       <c r="R30" t="n">
-        <v>7065278</v>
+        <v>7065011</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3691,7 +3691,7 @@
         <v>129060035</v>
       </c>
       <c r="B31" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>129059691</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3891,50 +3891,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129059681</v>
+        <v>129059690</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>83013</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>469043</v>
+        <v>468887</v>
       </c>
       <c r="R33" t="n">
-        <v>7065365</v>
+        <v>7065318</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3967,11 +3962,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3998,45 +3988,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129059690</v>
+        <v>129059681</v>
       </c>
       <c r="B34" t="n">
-        <v>83009</v>
+        <v>57725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>468887</v>
+        <v>469043</v>
       </c>
       <c r="R34" t="n">
-        <v>7065318</v>
+        <v>7065365</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4069,6 +4064,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4095,10 +4095,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129059700</v>
+        <v>129059694</v>
       </c>
       <c r="B35" t="n">
-        <v>80141</v>
+        <v>83007</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4106,21 +4106,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>469036</v>
+        <v>469141</v>
       </c>
       <c r="R35" t="n">
-        <v>7065082</v>
+        <v>7065114</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4179,17 +4179,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>sälgticka</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Phellinopsis conchata</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129060009</v>
+        <v>129059700</v>
       </c>
       <c r="B36" t="n">
-        <v>57723</v>
+        <v>80145</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4218,39 +4218,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>469298</v>
+        <v>469036</v>
       </c>
       <c r="R36" t="n">
-        <v>7065235</v>
+        <v>7065082</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4285,11 +4280,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4298,6 +4288,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4314,10 +4319,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129059694</v>
+        <v>129060009</v>
       </c>
       <c r="B37" t="n">
-        <v>83003</v>
+        <v>57725</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4325,34 +4330,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>469141</v>
+        <v>469298</v>
       </c>
       <c r="R37" t="n">
-        <v>7065114</v>
+        <v>7065235</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4387,6 +4397,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4395,21 +4410,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälgticka</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Phellinopsis conchata</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4429,7 +4429,7 @@
         <v>129060002</v>
       </c>
       <c r="B38" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>129060001</v>
       </c>
       <c r="B39" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4620,10 +4620,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129060026</v>
+        <v>129059684</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>468886</v>
+        <v>468895</v>
       </c>
       <c r="R40" t="n">
-        <v>7065015</v>
+        <v>7065399</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4727,10 +4727,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129059684</v>
+        <v>129060026</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4767,10 +4767,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468895</v>
+        <v>468886</v>
       </c>
       <c r="R41" t="n">
-        <v>7065399</v>
+        <v>7065015</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4837,7 +4837,7 @@
         <v>129059715</v>
       </c>
       <c r="B42" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>129059671</v>
       </c>
       <c r="B43" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>129059703</v>
       </c>
       <c r="B44" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>129059699</v>
       </c>
       <c r="B45" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5232,10 +5232,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129060049</v>
+        <v>129060018</v>
       </c>
       <c r="B46" t="n">
-        <v>91544</v>
+        <v>57725</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5243,34 +5243,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469012</v>
+        <v>469093</v>
       </c>
       <c r="R46" t="n">
-        <v>7065037</v>
+        <v>7065345</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5303,6 +5308,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5329,10 +5339,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129060018</v>
+        <v>129060017</v>
       </c>
       <c r="B47" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5369,10 +5379,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>469093</v>
+        <v>469122</v>
       </c>
       <c r="R47" t="n">
-        <v>7065345</v>
+        <v>7065303</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5436,10 +5446,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129060017</v>
+        <v>129060049</v>
       </c>
       <c r="B48" t="n">
-        <v>57723</v>
+        <v>91551</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5447,39 +5457,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>469122</v>
+        <v>469012</v>
       </c>
       <c r="R48" t="n">
-        <v>7065303</v>
+        <v>7065037</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5512,11 +5517,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5543,10 +5543,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129059709</v>
+        <v>129059704</v>
       </c>
       <c r="B49" t="n">
-        <v>83006</v>
+        <v>57725</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5554,34 +5554,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>468844</v>
+        <v>468883</v>
       </c>
       <c r="R49" t="n">
-        <v>7064978</v>
+        <v>7065026</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5616,6 +5621,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5624,21 +5634,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5655,10 +5650,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129059697</v>
+        <v>129060031</v>
       </c>
       <c r="B50" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5666,34 +5661,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>469114</v>
+        <v>469014</v>
       </c>
       <c r="R50" t="n">
-        <v>7065083</v>
+        <v>7064913</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5728,6 +5728,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5736,21 +5741,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5767,10 +5757,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129059702</v>
+        <v>129059709</v>
       </c>
       <c r="B51" t="n">
-        <v>91526</v>
+        <v>83010</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5778,21 +5768,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>310</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5802,10 +5792,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>468889</v>
+        <v>468844</v>
       </c>
       <c r="R51" t="n">
-        <v>7065025</v>
+        <v>7064978</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5848,6 +5838,21 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -5864,32 +5869,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129060042</v>
+        <v>129059702</v>
       </c>
       <c r="B52" t="n">
-        <v>80044</v>
+        <v>91533</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5899,10 +5904,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>469356</v>
+        <v>468889</v>
       </c>
       <c r="R52" t="n">
-        <v>7065233</v>
+        <v>7065025</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5961,50 +5966,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129060031</v>
+        <v>129060042</v>
       </c>
       <c r="B53" t="n">
-        <v>57723</v>
+        <v>80048</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>469014</v>
+        <v>469356</v>
       </c>
       <c r="R53" t="n">
-        <v>7064913</v>
+        <v>7065233</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6037,11 +6037,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6068,10 +6063,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129059704</v>
+        <v>129059697</v>
       </c>
       <c r="B54" t="n">
-        <v>57723</v>
+        <v>80144</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6079,39 +6074,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>468883</v>
+        <v>469114</v>
       </c>
       <c r="R54" t="n">
-        <v>7065026</v>
+        <v>7065083</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6146,11 +6136,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6159,6 +6144,21 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6175,10 +6175,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129060041</v>
+        <v>129060036</v>
       </c>
       <c r="B55" t="n">
-        <v>80141</v>
+        <v>57885</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6186,34 +6186,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>469143</v>
+        <v>468801</v>
       </c>
       <c r="R55" t="n">
-        <v>7065030</v>
+        <v>7065038</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6272,10 +6277,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129060036</v>
+        <v>129060041</v>
       </c>
       <c r="B56" t="n">
-        <v>57883</v>
+        <v>80145</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6283,39 +6288,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>468801</v>
+        <v>469143</v>
       </c>
       <c r="R56" t="n">
-        <v>7065038</v>
+        <v>7065030</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6377,7 +6377,7 @@
         <v>129060005</v>
       </c>
       <c r="B57" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>129059693</v>
       </c>
       <c r="B58" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>129060032</v>
       </c>
       <c r="B59" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6675,10 +6675,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129059686</v>
+        <v>129059675</v>
       </c>
       <c r="B60" t="n">
-        <v>83006</v>
+        <v>91529</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6686,21 +6686,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>310</v>
+        <v>1108</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>468843</v>
+        <v>469197</v>
       </c>
       <c r="R60" t="n">
-        <v>7065390</v>
+        <v>7065308</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6756,21 +6756,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6790,7 +6775,7 @@
         <v>129059687</v>
       </c>
       <c r="B61" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6899,10 +6884,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129059674</v>
+        <v>129059686</v>
       </c>
       <c r="B62" t="n">
-        <v>79035</v>
+        <v>83010</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6910,21 +6895,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6934,10 +6919,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>469226</v>
+        <v>468843</v>
       </c>
       <c r="R62" t="n">
-        <v>7065299</v>
+        <v>7065390</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6980,6 +6965,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -6996,10 +6996,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129060050</v>
+        <v>129059674</v>
       </c>
       <c r="B63" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>469118</v>
+        <v>469226</v>
       </c>
       <c r="R63" t="n">
-        <v>7065190</v>
+        <v>7065299</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7067,11 +7067,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7098,32 +7093,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129059675</v>
+        <v>129060043</v>
       </c>
       <c r="B64" t="n">
-        <v>91522</v>
+        <v>75029</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>6428</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7133,10 +7128,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>469197</v>
+        <v>469011</v>
       </c>
       <c r="R64" t="n">
-        <v>7065308</v>
+        <v>7065022</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7195,32 +7190,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129060043</v>
+        <v>129060050</v>
       </c>
       <c r="B65" t="n">
-        <v>75027</v>
+        <v>79039</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7230,10 +7225,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>469011</v>
+        <v>469118</v>
       </c>
       <c r="R65" t="n">
-        <v>7065022</v>
+        <v>7065190</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7266,6 +7261,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7295,7 +7295,7 @@
         <v>129060029</v>
       </c>
       <c r="B66" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7399,10 +7399,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129060025</v>
+        <v>129060021</v>
       </c>
       <c r="B67" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7439,10 +7439,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>469101</v>
+        <v>468788</v>
       </c>
       <c r="R67" t="n">
-        <v>7065026</v>
+        <v>7065344</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7506,10 +7506,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129060021</v>
+        <v>129060025</v>
       </c>
       <c r="B68" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7546,10 +7546,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>468788</v>
+        <v>469101</v>
       </c>
       <c r="R68" t="n">
-        <v>7065344</v>
+        <v>7065026</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7613,10 +7613,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129059682</v>
+        <v>129059670</v>
       </c>
       <c r="B69" t="n">
-        <v>91526</v>
+        <v>57725</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7624,34 +7624,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>468990</v>
+        <v>469326</v>
       </c>
       <c r="R69" t="n">
-        <v>7065370</v>
+        <v>7065255</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7684,6 +7689,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7710,10 +7720,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129059670</v>
+        <v>129059682</v>
       </c>
       <c r="B70" t="n">
-        <v>57723</v>
+        <v>91533</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7721,39 +7731,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>469326</v>
+        <v>468990</v>
       </c>
       <c r="R70" t="n">
-        <v>7065255</v>
+        <v>7065370</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7786,11 +7791,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7820,7 +7820,7 @@
         <v>129060051</v>
       </c>
       <c r="B71" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>129060011</v>
       </c>
       <c r="B72" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8026,50 +8026,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129059714</v>
+        <v>129060047</v>
       </c>
       <c r="B73" t="n">
-        <v>57723</v>
+        <v>91894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>468946</v>
+        <v>469012</v>
       </c>
       <c r="R73" t="n">
-        <v>7064969</v>
+        <v>7065037</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8102,11 +8097,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8133,10 +8123,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129059701</v>
+        <v>129059698</v>
       </c>
       <c r="B74" t="n">
-        <v>57723</v>
+        <v>80145</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8144,39 +8134,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>468991</v>
+        <v>469120</v>
       </c>
       <c r="R74" t="n">
-        <v>7065056</v>
+        <v>7065078</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8211,11 +8196,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8224,6 +8204,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8240,10 +8235,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129059698</v>
+        <v>129060040</v>
       </c>
       <c r="B75" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8275,10 +8270,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>469120</v>
+        <v>469148</v>
       </c>
       <c r="R75" t="n">
-        <v>7065078</v>
+        <v>7065056</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8321,21 +8316,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8352,10 +8332,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129060040</v>
+        <v>129059714</v>
       </c>
       <c r="B76" t="n">
-        <v>80141</v>
+        <v>57725</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8363,34 +8343,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>469148</v>
+        <v>468946</v>
       </c>
       <c r="R76" t="n">
-        <v>7065056</v>
+        <v>7064969</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8423,6 +8408,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8449,45 +8439,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129060047</v>
+        <v>129059701</v>
       </c>
       <c r="B77" t="n">
-        <v>91887</v>
+        <v>57725</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>469012</v>
+        <v>468991</v>
       </c>
       <c r="R77" t="n">
-        <v>7065037</v>
+        <v>7065056</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8520,6 +8515,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8549,7 +8549,7 @@
         <v>129059677</v>
       </c>
       <c r="B78" t="n">
-        <v>78048</v>
+        <v>78052</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8643,10 +8643,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129060016</v>
+        <v>129059680</v>
       </c>
       <c r="B79" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8683,10 +8683,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>469152</v>
+        <v>469094</v>
       </c>
       <c r="R79" t="n">
-        <v>7065299</v>
+        <v>7065363</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8750,10 +8750,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129060014</v>
+        <v>129060016</v>
       </c>
       <c r="B80" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -8790,10 +8790,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>469198</v>
+        <v>469152</v>
       </c>
       <c r="R80" t="n">
-        <v>7065284</v>
+        <v>7065299</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8857,10 +8857,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129059680</v>
+        <v>129060014</v>
       </c>
       <c r="B81" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -8897,10 +8897,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>469094</v>
+        <v>469198</v>
       </c>
       <c r="R81" t="n">
-        <v>7065363</v>
+        <v>7065284</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8964,10 +8964,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129059706</v>
+        <v>129059696</v>
       </c>
       <c r="B82" t="n">
-        <v>80141</v>
+        <v>91551</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8975,21 +8975,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8999,10 +8999,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>468850</v>
+        <v>469141</v>
       </c>
       <c r="R82" t="n">
-        <v>7065034</v>
+        <v>7065095</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9045,21 +9045,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9076,10 +9061,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129059696</v>
+        <v>129059676</v>
       </c>
       <c r="B83" t="n">
-        <v>91544</v>
+        <v>83015</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9087,21 +9072,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9111,10 +9096,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>469141</v>
+        <v>469160</v>
       </c>
       <c r="R83" t="n">
-        <v>7065095</v>
+        <v>7065329</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9173,10 +9158,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129059676</v>
+        <v>129059712</v>
       </c>
       <c r="B84" t="n">
-        <v>83011</v>
+        <v>79039</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9184,21 +9169,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9208,10 +9193,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>469160</v>
+        <v>468868</v>
       </c>
       <c r="R84" t="n">
-        <v>7065329</v>
+        <v>7064989</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9270,10 +9255,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129059692</v>
+        <v>129059706</v>
       </c>
       <c r="B85" t="n">
-        <v>57723</v>
+        <v>80145</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9281,39 +9266,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>469137</v>
+        <v>468850</v>
       </c>
       <c r="R85" t="n">
-        <v>7065206</v>
+        <v>7065034</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9348,11 +9328,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9361,6 +9336,21 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -9380,7 +9370,7 @@
         <v>129059679</v>
       </c>
       <c r="B86" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9487,7 +9477,7 @@
         <v>129059713</v>
       </c>
       <c r="B87" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9591,10 +9581,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129059712</v>
+        <v>129059692</v>
       </c>
       <c r="B88" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9602,34 +9592,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>468868</v>
+        <v>469137</v>
       </c>
       <c r="R88" t="n">
-        <v>7064989</v>
+        <v>7065206</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9662,6 +9657,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -3290,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129060027</v>
+        <v>129060046</v>
       </c>
       <c r="B27" t="n">
-        <v>57725</v>
+        <v>91529</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3301,39 +3301,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>468896</v>
+        <v>469215</v>
       </c>
       <c r="R27" t="n">
-        <v>7064986</v>
+        <v>7065278</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3366,11 +3361,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3397,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129060046</v>
+        <v>129060048</v>
       </c>
       <c r="B28" t="n">
-        <v>91529</v>
+        <v>91551</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3408,21 +3398,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3432,10 +3422,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469215</v>
+        <v>469135</v>
       </c>
       <c r="R28" t="n">
-        <v>7065278</v>
+        <v>7065166</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3494,32 +3484,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129060048</v>
+        <v>129060006</v>
       </c>
       <c r="B29" t="n">
-        <v>91551</v>
+        <v>92233</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3529,10 +3519,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469135</v>
+        <v>469045</v>
       </c>
       <c r="R29" t="n">
-        <v>7065166</v>
+        <v>7065011</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3591,45 +3581,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129060006</v>
+        <v>129060035</v>
       </c>
       <c r="B30" t="n">
-        <v>92233</v>
+        <v>57885</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469045</v>
+        <v>469149</v>
       </c>
       <c r="R30" t="n">
-        <v>7065011</v>
+        <v>7065169</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3688,10 +3687,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129060035</v>
+        <v>129060027</v>
       </c>
       <c r="B31" t="n">
-        <v>57885</v>
+        <v>57725</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3699,31 +3698,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3732,10 +3727,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469149</v>
+        <v>468896</v>
       </c>
       <c r="R31" t="n">
-        <v>7065169</v>
+        <v>7064986</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3768,6 +3763,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -6675,10 +6675,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129059675</v>
+        <v>129059687</v>
       </c>
       <c r="B60" t="n">
-        <v>91529</v>
+        <v>80145</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6686,21 +6686,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>469197</v>
+        <v>468843</v>
       </c>
       <c r="R60" t="n">
-        <v>7065308</v>
+        <v>7065390</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6756,6 +6756,21 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6772,10 +6787,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129059687</v>
+        <v>129059674</v>
       </c>
       <c r="B61" t="n">
-        <v>80145</v>
+        <v>79039</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6783,21 +6798,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6807,10 +6822,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468843</v>
+        <v>469226</v>
       </c>
       <c r="R61" t="n">
-        <v>7065390</v>
+        <v>7065299</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6853,21 +6868,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6884,32 +6884,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129059686</v>
+        <v>129060043</v>
       </c>
       <c r="B62" t="n">
-        <v>83010</v>
+        <v>75029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>310</v>
+        <v>6428</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468843</v>
+        <v>469011</v>
       </c>
       <c r="R62" t="n">
-        <v>7065390</v>
+        <v>7065022</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6965,21 +6965,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -6996,7 +6981,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129059674</v>
+        <v>129060050</v>
       </c>
       <c r="B63" t="n">
         <v>79039</v>
@@ -7031,10 +7016,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>469226</v>
+        <v>469118</v>
       </c>
       <c r="R63" t="n">
-        <v>7065299</v>
+        <v>7065190</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7067,6 +7052,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7093,45 +7083,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129060043</v>
+        <v>129060029</v>
       </c>
       <c r="B64" t="n">
-        <v>75029</v>
+        <v>57725</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>469011</v>
+        <v>468970</v>
       </c>
       <c r="R64" t="n">
-        <v>7065022</v>
+        <v>7064946</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7164,6 +7159,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7190,10 +7190,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129060050</v>
+        <v>129060021</v>
       </c>
       <c r="B65" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7201,34 +7201,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>469118</v>
+        <v>468788</v>
       </c>
       <c r="R65" t="n">
-        <v>7065190</v>
+        <v>7065344</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7265,7 +7270,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7292,7 +7297,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129060029</v>
+        <v>129060025</v>
       </c>
       <c r="B66" t="n">
         <v>57725</v>
@@ -7332,10 +7337,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468970</v>
+        <v>469101</v>
       </c>
       <c r="R66" t="n">
-        <v>7064946</v>
+        <v>7065026</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7399,10 +7404,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129060021</v>
+        <v>129059686</v>
       </c>
       <c r="B67" t="n">
-        <v>57725</v>
+        <v>83010</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7410,39 +7415,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>310</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468788</v>
+        <v>468843</v>
       </c>
       <c r="R67" t="n">
-        <v>7065344</v>
+        <v>7065390</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7477,11 +7477,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7490,6 +7485,21 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -7506,10 +7516,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129060025</v>
+        <v>129059675</v>
       </c>
       <c r="B68" t="n">
-        <v>57725</v>
+        <v>91529</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7517,39 +7527,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>469101</v>
+        <v>469197</v>
       </c>
       <c r="R68" t="n">
-        <v>7065026</v>
+        <v>7065308</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7582,11 +7587,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129059689</v>
+        <v>129060044</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>80144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468887</v>
+        <v>469111</v>
       </c>
       <c r="R2" t="n">
-        <v>7065318</v>
+        <v>7065086</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129060044</v>
+        <v>129059711</v>
       </c>
       <c r="B4" t="n">
         <v>80144</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469111</v>
+        <v>468844</v>
       </c>
       <c r="R4" t="n">
-        <v>7065086</v>
+        <v>7064978</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,6 +950,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -966,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129059711</v>
+        <v>129059689</v>
       </c>
       <c r="B5" t="n">
-        <v>80144</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468844</v>
+        <v>468887</v>
       </c>
       <c r="R5" t="n">
-        <v>7064978</v>
+        <v>7065318</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,21 +1062,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -2345,7 +2345,7 @@
         <v>129060003</v>
       </c>
       <c r="B18" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>129059708</v>
       </c>
       <c r="B21" t="n">
-        <v>83020</v>
+        <v>83010</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>129060046</v>
       </c>
       <c r="B27" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,32 +3387,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129060048</v>
+        <v>129060006</v>
       </c>
       <c r="B28" t="n">
-        <v>91551</v>
+        <v>92240</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469135</v>
+        <v>469045</v>
       </c>
       <c r="R28" t="n">
-        <v>7065166</v>
+        <v>7065011</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,32 +3484,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129060006</v>
+        <v>129060048</v>
       </c>
       <c r="B29" t="n">
-        <v>92233</v>
+        <v>91558</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3519,10 +3519,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469045</v>
+        <v>469135</v>
       </c>
       <c r="R29" t="n">
-        <v>7065011</v>
+        <v>7065166</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3581,10 +3581,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129060035</v>
+        <v>129060027</v>
       </c>
       <c r="B30" t="n">
-        <v>57885</v>
+        <v>57725</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3592,31 +3592,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3625,10 +3621,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469149</v>
+        <v>468896</v>
       </c>
       <c r="R30" t="n">
-        <v>7065169</v>
+        <v>7064986</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3661,6 +3657,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3687,10 +3688,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129060027</v>
+        <v>129060035</v>
       </c>
       <c r="B31" t="n">
-        <v>57725</v>
+        <v>57885</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3698,27 +3699,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3727,10 +3732,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>468896</v>
+        <v>469149</v>
       </c>
       <c r="R31" t="n">
-        <v>7064986</v>
+        <v>7065169</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3763,11 +3768,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3794,10 +3794,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129059691</v>
+        <v>129059681</v>
       </c>
       <c r="B32" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3805,34 +3805,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468992</v>
+        <v>469043</v>
       </c>
       <c r="R32" t="n">
-        <v>7065224</v>
+        <v>7065365</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3865,6 +3870,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3891,32 +3901,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129059690</v>
+        <v>129059691</v>
       </c>
       <c r="B33" t="n">
-        <v>83013</v>
+        <v>79039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3926,10 +3936,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>468887</v>
+        <v>468992</v>
       </c>
       <c r="R33" t="n">
-        <v>7065318</v>
+        <v>7065224</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3988,50 +3998,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129059681</v>
+        <v>129059690</v>
       </c>
       <c r="B34" t="n">
-        <v>57725</v>
+        <v>83003</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>469043</v>
+        <v>468887</v>
       </c>
       <c r="R34" t="n">
-        <v>7065365</v>
+        <v>7065318</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4064,11 +4069,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4098,7 +4098,7 @@
         <v>129059694</v>
       </c>
       <c r="B35" t="n">
-        <v>83007</v>
+        <v>82997</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4426,10 +4426,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129060002</v>
+        <v>129060026</v>
       </c>
       <c r="B38" t="n">
-        <v>91533</v>
+        <v>57725</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4437,34 +4437,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>469031</v>
+        <v>468886</v>
       </c>
       <c r="R38" t="n">
-        <v>7065017</v>
+        <v>7065015</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4497,6 +4502,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4523,32 +4533,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129060001</v>
+        <v>129060002</v>
       </c>
       <c r="B39" t="n">
-        <v>91497</v>
+        <v>91540</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4558,10 +4568,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468967</v>
+        <v>469031</v>
       </c>
       <c r="R39" t="n">
-        <v>7065256</v>
+        <v>7065017</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4620,50 +4630,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129059684</v>
+        <v>129060001</v>
       </c>
       <c r="B40" t="n">
-        <v>57725</v>
+        <v>91504</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>468895</v>
+        <v>468967</v>
       </c>
       <c r="R40" t="n">
-        <v>7065399</v>
+        <v>7065256</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4696,11 +4701,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4727,7 +4727,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129060026</v>
+        <v>129059684</v>
       </c>
       <c r="B41" t="n">
         <v>57725</v>
@@ -4767,10 +4767,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468886</v>
+        <v>468895</v>
       </c>
       <c r="R41" t="n">
-        <v>7065015</v>
+        <v>7065399</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5038,10 +5038,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129059703</v>
+        <v>129060049</v>
       </c>
       <c r="B44" t="n">
-        <v>79039</v>
+        <v>91558</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,21 +5049,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>468883</v>
+        <v>469012</v>
       </c>
       <c r="R44" t="n">
-        <v>7065026</v>
+        <v>7065037</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5232,10 +5232,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129060018</v>
+        <v>129059703</v>
       </c>
       <c r="B46" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5243,39 +5243,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469093</v>
+        <v>468883</v>
       </c>
       <c r="R46" t="n">
-        <v>7065345</v>
+        <v>7065026</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5308,11 +5303,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5339,7 +5329,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129060017</v>
+        <v>129060018</v>
       </c>
       <c r="B47" t="n">
         <v>57725</v>
@@ -5379,10 +5369,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>469122</v>
+        <v>469093</v>
       </c>
       <c r="R47" t="n">
-        <v>7065303</v>
+        <v>7065345</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5446,10 +5436,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129060049</v>
+        <v>129060017</v>
       </c>
       <c r="B48" t="n">
-        <v>91551</v>
+        <v>57725</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5457,34 +5447,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>469012</v>
+        <v>469122</v>
       </c>
       <c r="R48" t="n">
-        <v>7065037</v>
+        <v>7065303</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5517,6 +5512,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5760,7 +5760,7 @@
         <v>129059709</v>
       </c>
       <c r="B51" t="n">
-        <v>83010</v>
+        <v>83000</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>129059702</v>
       </c>
       <c r="B52" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5966,32 +5966,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129060042</v>
+        <v>129059697</v>
       </c>
       <c r="B53" t="n">
-        <v>80048</v>
+        <v>80144</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6001,10 +6001,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>469356</v>
+        <v>469114</v>
       </c>
       <c r="R53" t="n">
-        <v>7065233</v>
+        <v>7065083</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6047,6 +6047,21 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6063,32 +6078,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129059697</v>
+        <v>129060042</v>
       </c>
       <c r="B54" t="n">
-        <v>80144</v>
+        <v>80048</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6098,10 +6113,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>469114</v>
+        <v>469356</v>
       </c>
       <c r="R54" t="n">
-        <v>7065083</v>
+        <v>7065233</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6144,21 +6159,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6175,10 +6175,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129060036</v>
+        <v>129060041</v>
       </c>
       <c r="B55" t="n">
-        <v>57885</v>
+        <v>80145</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6186,39 +6186,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>468801</v>
+        <v>469143</v>
       </c>
       <c r="R55" t="n">
-        <v>7065038</v>
+        <v>7065030</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6277,10 +6272,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129060041</v>
+        <v>129060036</v>
       </c>
       <c r="B56" t="n">
-        <v>80145</v>
+        <v>57885</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6288,34 +6283,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>469143</v>
+        <v>468801</v>
       </c>
       <c r="R56" t="n">
-        <v>7065030</v>
+        <v>7065038</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6377,7 +6377,7 @@
         <v>129060005</v>
       </c>
       <c r="B57" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>129059693</v>
       </c>
       <c r="B58" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6675,10 +6675,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129059687</v>
+        <v>129060025</v>
       </c>
       <c r="B60" t="n">
-        <v>80145</v>
+        <v>57725</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6686,34 +6686,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>468843</v>
+        <v>469101</v>
       </c>
       <c r="R60" t="n">
-        <v>7065390</v>
+        <v>7065026</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6748,6 +6753,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6756,21 +6766,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6787,10 +6782,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129059674</v>
+        <v>129059686</v>
       </c>
       <c r="B61" t="n">
-        <v>79039</v>
+        <v>83000</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6798,21 +6793,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6822,10 +6817,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>469226</v>
+        <v>468843</v>
       </c>
       <c r="R61" t="n">
-        <v>7065299</v>
+        <v>7065390</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6868,6 +6863,21 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6884,32 +6894,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129060043</v>
+        <v>129059687</v>
       </c>
       <c r="B62" t="n">
-        <v>75029</v>
+        <v>80145</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6428</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6919,10 +6929,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>469011</v>
+        <v>468843</v>
       </c>
       <c r="R62" t="n">
-        <v>7065022</v>
+        <v>7065390</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6965,6 +6975,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -6981,10 +7006,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129060050</v>
+        <v>129059675</v>
       </c>
       <c r="B63" t="n">
-        <v>79039</v>
+        <v>91536</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6992,21 +7017,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7016,10 +7041,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>469118</v>
+        <v>469197</v>
       </c>
       <c r="R63" t="n">
-        <v>7065190</v>
+        <v>7065308</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7052,11 +7077,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7297,50 +7317,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129060025</v>
+        <v>129060043</v>
       </c>
       <c r="B66" t="n">
-        <v>57725</v>
+        <v>75029</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>469101</v>
+        <v>469011</v>
       </c>
       <c r="R66" t="n">
-        <v>7065026</v>
+        <v>7065022</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7373,11 +7388,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7404,10 +7414,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129059686</v>
+        <v>129059674</v>
       </c>
       <c r="B67" t="n">
-        <v>83010</v>
+        <v>79039</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7415,21 +7425,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7439,10 +7449,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468843</v>
+        <v>469226</v>
       </c>
       <c r="R67" t="n">
-        <v>7065390</v>
+        <v>7065299</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7485,21 +7495,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -7516,10 +7511,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129059675</v>
+        <v>129060050</v>
       </c>
       <c r="B68" t="n">
-        <v>91529</v>
+        <v>79039</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7527,21 +7522,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7551,10 +7546,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>469197</v>
+        <v>469118</v>
       </c>
       <c r="R68" t="n">
-        <v>7065308</v>
+        <v>7065190</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7587,6 +7582,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7613,10 +7613,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129059670</v>
+        <v>129059682</v>
       </c>
       <c r="B69" t="n">
-        <v>57725</v>
+        <v>91540</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7624,39 +7624,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>469326</v>
+        <v>468990</v>
       </c>
       <c r="R69" t="n">
-        <v>7065255</v>
+        <v>7065370</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7689,11 +7684,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7720,10 +7710,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129059682</v>
+        <v>129059670</v>
       </c>
       <c r="B70" t="n">
-        <v>91533</v>
+        <v>57725</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7731,34 +7721,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468990</v>
+        <v>469326</v>
       </c>
       <c r="R70" t="n">
-        <v>7065370</v>
+        <v>7065255</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7791,6 +7786,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8029,7 +8029,7 @@
         <v>129060047</v>
       </c>
       <c r="B73" t="n">
-        <v>91894</v>
+        <v>91901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8964,10 +8964,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129059696</v>
+        <v>129059706</v>
       </c>
       <c r="B82" t="n">
-        <v>91551</v>
+        <v>80145</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8975,21 +8975,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8999,10 +8999,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>469141</v>
+        <v>468850</v>
       </c>
       <c r="R82" t="n">
-        <v>7065095</v>
+        <v>7065034</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9045,6 +9045,21 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9061,10 +9076,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129059676</v>
+        <v>129059696</v>
       </c>
       <c r="B83" t="n">
-        <v>83015</v>
+        <v>91558</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9072,21 +9087,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9096,10 +9111,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>469160</v>
+        <v>469141</v>
       </c>
       <c r="R83" t="n">
-        <v>7065329</v>
+        <v>7065095</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9158,10 +9173,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129059712</v>
+        <v>129059679</v>
       </c>
       <c r="B84" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9169,34 +9184,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>468868</v>
+        <v>469108</v>
       </c>
       <c r="R84" t="n">
-        <v>7064989</v>
+        <v>7065364</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9229,6 +9249,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9255,10 +9280,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129059706</v>
+        <v>129059713</v>
       </c>
       <c r="B85" t="n">
-        <v>80145</v>
+        <v>57725</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9266,34 +9291,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>468850</v>
+        <v>468922</v>
       </c>
       <c r="R85" t="n">
-        <v>7065034</v>
+        <v>7064998</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9328,6 +9358,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9336,21 +9371,6 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -9367,7 +9387,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129059679</v>
+        <v>129059692</v>
       </c>
       <c r="B86" t="n">
         <v>57725</v>
@@ -9407,10 +9427,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>469108</v>
+        <v>469137</v>
       </c>
       <c r="R86" t="n">
-        <v>7065364</v>
+        <v>7065206</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9474,10 +9494,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129059713</v>
+        <v>129059676</v>
       </c>
       <c r="B87" t="n">
-        <v>57725</v>
+        <v>83005</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9485,39 +9505,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>468922</v>
+        <v>469160</v>
       </c>
       <c r="R87" t="n">
-        <v>7064998</v>
+        <v>7065329</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9550,11 +9565,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9581,10 +9591,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129059692</v>
+        <v>129059712</v>
       </c>
       <c r="B88" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9592,39 +9602,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>469137</v>
+        <v>468868</v>
       </c>
       <c r="R88" t="n">
-        <v>7065206</v>
+        <v>7064989</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9657,11 +9662,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129060044</v>
+        <v>129060012</v>
       </c>
       <c r="B2" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469111</v>
+        <v>469235</v>
       </c>
       <c r="R2" t="n">
-        <v>7065086</v>
+        <v>7065256</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129059683</v>
+        <v>129060023</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468964</v>
+        <v>469142</v>
       </c>
       <c r="R3" t="n">
-        <v>7065331</v>
+        <v>7065079</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129059711</v>
+        <v>129060033</v>
       </c>
       <c r="B4" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468844</v>
+        <v>469047</v>
       </c>
       <c r="R4" t="n">
-        <v>7064978</v>
+        <v>7064905</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -942,6 +967,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -950,21 +980,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -981,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129059689</v>
+        <v>129060008</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468887</v>
+        <v>469327</v>
       </c>
       <c r="R5" t="n">
-        <v>7065318</v>
+        <v>7065224</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129059710</v>
+        <v>129060020</v>
       </c>
       <c r="B6" t="n">
-        <v>80145</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468844</v>
+        <v>468803</v>
       </c>
       <c r="R6" t="n">
-        <v>7064978</v>
+        <v>7065369</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,6 +1181,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1159,21 +1194,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1190,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129060012</v>
+        <v>129060024</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,7 +1241,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1230,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469235</v>
+        <v>469131</v>
       </c>
       <c r="R7" t="n">
-        <v>7065256</v>
+        <v>7065083</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129060023</v>
+        <v>129060044</v>
       </c>
       <c r="B8" t="n">
-        <v>57725</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,39 +1328,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469142</v>
+        <v>469111</v>
       </c>
       <c r="R8" t="n">
-        <v>7065079</v>
+        <v>7065086</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129060033</v>
+        <v>129059683</v>
       </c>
       <c r="B9" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,39 +1425,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469047</v>
+        <v>468964</v>
       </c>
       <c r="R9" t="n">
-        <v>7064905</v>
+        <v>7065331</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,11 +1485,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129060008</v>
+        <v>129059711</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>80146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,39 +1522,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469327</v>
+        <v>468844</v>
       </c>
       <c r="R10" t="n">
-        <v>7065224</v>
+        <v>7064978</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,11 +1584,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1602,6 +1592,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1618,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129060020</v>
+        <v>129059689</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,39 +1634,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468803</v>
+        <v>468887</v>
       </c>
       <c r="R11" t="n">
-        <v>7065369</v>
+        <v>7065318</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,11 +1694,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129060024</v>
+        <v>129059710</v>
       </c>
       <c r="B12" t="n">
-        <v>57725</v>
+        <v>80147</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,39 +1731,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469131</v>
+        <v>468844</v>
       </c>
       <c r="R12" t="n">
-        <v>7065083</v>
+        <v>7064978</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1803,11 +1793,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1816,6 +1801,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129059678</v>
+        <v>129060015</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,34 +1843,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469160</v>
+        <v>469142</v>
       </c>
       <c r="R13" t="n">
-        <v>7065329</v>
+        <v>7065300</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,6 +1908,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129060015</v>
+        <v>129059678</v>
       </c>
       <c r="B14" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1940,39 +1950,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469142</v>
+        <v>469160</v>
       </c>
       <c r="R14" t="n">
-        <v>7065300</v>
+        <v>7065329</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,11 +2010,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129060045</v>
+        <v>129060022</v>
       </c>
       <c r="B15" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,34 +2047,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469013</v>
+        <v>468893</v>
       </c>
       <c r="R15" t="n">
-        <v>7065018</v>
+        <v>7065289</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,6 +2112,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2133,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129060022</v>
+        <v>129060037</v>
       </c>
       <c r="B16" t="n">
-        <v>57725</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2144,27 +2154,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2173,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468893</v>
+        <v>468874</v>
       </c>
       <c r="R16" t="n">
-        <v>7065289</v>
+        <v>7064975</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,11 +2219,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2240,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129060037</v>
+        <v>129060045</v>
       </c>
       <c r="B17" t="n">
-        <v>57885</v>
+        <v>80146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,39 +2256,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468874</v>
+        <v>469013</v>
       </c>
       <c r="R17" t="n">
-        <v>7064975</v>
+        <v>7065018</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129060003</v>
+        <v>129059708</v>
       </c>
       <c r="B18" t="n">
-        <v>91540</v>
+        <v>83012</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469006</v>
+        <v>468783</v>
       </c>
       <c r="R18" t="n">
-        <v>7065358</v>
+        <v>7065001</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2423,6 +2423,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2439,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129060007</v>
+        <v>129060039</v>
       </c>
       <c r="B19" t="n">
-        <v>57725</v>
+        <v>80147</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2450,39 +2465,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469364</v>
+        <v>469139</v>
       </c>
       <c r="R19" t="n">
-        <v>7065232</v>
+        <v>7065094</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2515,11 +2525,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2546,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129059685</v>
+        <v>129060003</v>
       </c>
       <c r="B20" t="n">
-        <v>57725</v>
+        <v>91542</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2557,39 +2562,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468878</v>
+        <v>469006</v>
       </c>
       <c r="R20" t="n">
-        <v>7065401</v>
+        <v>7065358</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,11 +2622,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2653,10 +2648,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129059708</v>
+        <v>129060038</v>
       </c>
       <c r="B21" t="n">
-        <v>83010</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2664,34 +2659,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1467</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468783</v>
+        <v>469007</v>
       </c>
       <c r="R21" t="n">
-        <v>7065001</v>
+        <v>7064930</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,21 +2734,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2765,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129060039</v>
+        <v>129060007</v>
       </c>
       <c r="B22" t="n">
-        <v>80145</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2776,34 +2761,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469139</v>
+        <v>469364</v>
       </c>
       <c r="R22" t="n">
-        <v>7065094</v>
+        <v>7065232</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2836,6 +2826,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2862,10 +2857,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129059695</v>
+        <v>129059685</v>
       </c>
       <c r="B23" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2873,34 +2868,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469141</v>
+        <v>468878</v>
       </c>
       <c r="R23" t="n">
-        <v>7065114</v>
+        <v>7065401</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2935,6 +2935,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2943,21 +2948,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -2974,10 +2964,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129060038</v>
+        <v>129059695</v>
       </c>
       <c r="B24" t="n">
-        <v>57885</v>
+        <v>80146</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2985,39 +2975,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469007</v>
+        <v>469141</v>
       </c>
       <c r="R24" t="n">
-        <v>7064930</v>
+        <v>7065114</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3060,6 +3045,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3079,7 +3079,7 @@
         <v>129060013</v>
       </c>
       <c r="B25" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>129060010</v>
       </c>
       <c r="B26" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3290,32 +3290,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129060046</v>
+        <v>129060006</v>
       </c>
       <c r="B27" t="n">
-        <v>91536</v>
+        <v>92242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469215</v>
+        <v>469045</v>
       </c>
       <c r="R27" t="n">
-        <v>7065278</v>
+        <v>7065011</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3387,32 +3387,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129060006</v>
+        <v>129060048</v>
       </c>
       <c r="B28" t="n">
-        <v>92240</v>
+        <v>91560</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469045</v>
+        <v>469135</v>
       </c>
       <c r="R28" t="n">
-        <v>7065011</v>
+        <v>7065166</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,10 +3484,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129060048</v>
+        <v>129060046</v>
       </c>
       <c r="B29" t="n">
-        <v>91558</v>
+        <v>91538</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3495,21 +3495,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3519,10 +3519,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469135</v>
+        <v>469215</v>
       </c>
       <c r="R29" t="n">
-        <v>7065166</v>
+        <v>7065278</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3584,7 +3584,7 @@
         <v>129060027</v>
       </c>
       <c r="B30" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>129060035</v>
       </c>
       <c r="B31" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>129059681</v>
       </c>
       <c r="B32" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>129059691</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>129059690</v>
       </c>
       <c r="B34" t="n">
-        <v>83003</v>
+        <v>83005</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4095,10 +4095,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129059694</v>
+        <v>129059700</v>
       </c>
       <c r="B35" t="n">
-        <v>82997</v>
+        <v>80147</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4106,21 +4106,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>469141</v>
+        <v>469036</v>
       </c>
       <c r="R35" t="n">
-        <v>7065114</v>
+        <v>7065082</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4179,17 +4179,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälgticka</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Phellinopsis conchata</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129059700</v>
+        <v>129060009</v>
       </c>
       <c r="B36" t="n">
-        <v>80145</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4218,34 +4218,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>469036</v>
+        <v>469298</v>
       </c>
       <c r="R36" t="n">
-        <v>7065082</v>
+        <v>7065235</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4280,6 +4285,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4288,21 +4298,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4319,10 +4314,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129060009</v>
+        <v>129059694</v>
       </c>
       <c r="B37" t="n">
-        <v>57725</v>
+        <v>82999</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4330,39 +4325,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>469298</v>
+        <v>469141</v>
       </c>
       <c r="R37" t="n">
-        <v>7065235</v>
+        <v>7065114</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4397,11 +4387,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4410,6 +4395,21 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälgticka</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Phellinopsis conchata</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4426,10 +4426,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129060026</v>
+        <v>129060002</v>
       </c>
       <c r="B38" t="n">
-        <v>57725</v>
+        <v>91542</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4437,39 +4437,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>468886</v>
+        <v>469031</v>
       </c>
       <c r="R38" t="n">
-        <v>7065015</v>
+        <v>7065017</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4502,11 +4497,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4533,32 +4523,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129060002</v>
+        <v>129060001</v>
       </c>
       <c r="B39" t="n">
-        <v>91540</v>
+        <v>91506</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4568,10 +4558,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>469031</v>
+        <v>468967</v>
       </c>
       <c r="R39" t="n">
-        <v>7065017</v>
+        <v>7065256</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4630,45 +4620,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129060001</v>
+        <v>129059684</v>
       </c>
       <c r="B40" t="n">
-        <v>91504</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>468967</v>
+        <v>468895</v>
       </c>
       <c r="R40" t="n">
-        <v>7065256</v>
+        <v>7065399</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4701,6 +4696,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4727,10 +4727,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129059684</v>
+        <v>129060026</v>
       </c>
       <c r="B41" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4767,10 +4767,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468895</v>
+        <v>468886</v>
       </c>
       <c r="R41" t="n">
-        <v>7065399</v>
+        <v>7065015</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4837,7 +4837,7 @@
         <v>129059715</v>
       </c>
       <c r="B42" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>129059671</v>
       </c>
       <c r="B43" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5038,10 +5038,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129060049</v>
+        <v>129060018</v>
       </c>
       <c r="B44" t="n">
-        <v>91558</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,34 +5049,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>469012</v>
+        <v>469093</v>
       </c>
       <c r="R44" t="n">
-        <v>7065037</v>
+        <v>7065345</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5109,6 +5114,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5135,10 +5145,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129059699</v>
+        <v>129060017</v>
       </c>
       <c r="B45" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5146,34 +5156,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>469071</v>
+        <v>469122</v>
       </c>
       <c r="R45" t="n">
-        <v>7065075</v>
+        <v>7065303</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5206,6 +5221,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5232,10 +5252,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129059703</v>
+        <v>129060049</v>
       </c>
       <c r="B46" t="n">
-        <v>79039</v>
+        <v>91560</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5243,21 +5263,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5267,10 +5287,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>468883</v>
+        <v>469012</v>
       </c>
       <c r="R46" t="n">
-        <v>7065026</v>
+        <v>7065037</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5329,10 +5349,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129060018</v>
+        <v>129059699</v>
       </c>
       <c r="B47" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5340,39 +5360,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>469093</v>
+        <v>469071</v>
       </c>
       <c r="R47" t="n">
-        <v>7065345</v>
+        <v>7065075</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5405,11 +5420,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5436,10 +5446,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129060017</v>
+        <v>129059703</v>
       </c>
       <c r="B48" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5447,39 +5457,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>469122</v>
+        <v>468883</v>
       </c>
       <c r="R48" t="n">
-        <v>7065303</v>
+        <v>7065026</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5512,11 +5517,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5543,10 +5543,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129059704</v>
+        <v>129059709</v>
       </c>
       <c r="B49" t="n">
-        <v>57725</v>
+        <v>83002</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5554,39 +5554,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>310</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>468883</v>
+        <v>468844</v>
       </c>
       <c r="R49" t="n">
-        <v>7065026</v>
+        <v>7064978</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5621,11 +5616,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5634,6 +5624,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5650,10 +5655,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129060031</v>
+        <v>129059702</v>
       </c>
       <c r="B50" t="n">
-        <v>57725</v>
+        <v>91542</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5661,39 +5666,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>469014</v>
+        <v>468889</v>
       </c>
       <c r="R50" t="n">
-        <v>7064913</v>
+        <v>7065025</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5726,11 +5726,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5757,10 +5752,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129059709</v>
+        <v>129059704</v>
       </c>
       <c r="B51" t="n">
-        <v>83000</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5768,34 +5763,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>468844</v>
+        <v>468883</v>
       </c>
       <c r="R51" t="n">
-        <v>7064978</v>
+        <v>7065026</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5830,6 +5830,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5838,21 +5843,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -5869,10 +5859,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129059702</v>
+        <v>129060031</v>
       </c>
       <c r="B52" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5880,34 +5870,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>468889</v>
+        <v>469014</v>
       </c>
       <c r="R52" t="n">
-        <v>7065025</v>
+        <v>7064913</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5940,6 +5935,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5969,7 +5969,7 @@
         <v>129059697</v>
       </c>
       <c r="B53" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>129060042</v>
       </c>
       <c r="B54" t="n">
-        <v>80048</v>
+        <v>80050</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>129060041</v>
       </c>
       <c r="B55" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>129060036</v>
       </c>
       <c r="B56" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>129060005</v>
       </c>
       <c r="B57" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6471,10 +6471,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129059693</v>
+        <v>129060032</v>
       </c>
       <c r="B58" t="n">
-        <v>91558</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6482,34 +6482,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>469137</v>
+        <v>469043</v>
       </c>
       <c r="R58" t="n">
-        <v>7065120</v>
+        <v>7064905</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6542,6 +6547,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6568,10 +6578,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129060032</v>
+        <v>129059693</v>
       </c>
       <c r="B59" t="n">
-        <v>57725</v>
+        <v>91560</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6579,39 +6589,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>469043</v>
+        <v>469137</v>
       </c>
       <c r="R59" t="n">
-        <v>7064905</v>
+        <v>7065120</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6644,11 +6649,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6675,10 +6675,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129060025</v>
+        <v>129059686</v>
       </c>
       <c r="B60" t="n">
-        <v>57725</v>
+        <v>83002</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6686,39 +6686,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>310</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>469101</v>
+        <v>468843</v>
       </c>
       <c r="R60" t="n">
-        <v>7065026</v>
+        <v>7065390</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6753,11 +6748,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6766,6 +6756,21 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6782,10 +6787,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129059686</v>
+        <v>129060029</v>
       </c>
       <c r="B61" t="n">
-        <v>83000</v>
+        <v>57727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6793,34 +6798,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468843</v>
+        <v>468970</v>
       </c>
       <c r="R61" t="n">
-        <v>7065390</v>
+        <v>7064946</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6855,6 +6865,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -6863,21 +6878,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6894,10 +6894,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129059687</v>
+        <v>129060021</v>
       </c>
       <c r="B62" t="n">
-        <v>80145</v>
+        <v>57727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6905,34 +6905,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468843</v>
+        <v>468788</v>
       </c>
       <c r="R62" t="n">
-        <v>7065390</v>
+        <v>7065344</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6967,6 +6972,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -6975,21 +6985,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7006,10 +7001,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129059675</v>
+        <v>129060025</v>
       </c>
       <c r="B63" t="n">
-        <v>91536</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7017,34 +7012,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>469197</v>
+        <v>469101</v>
       </c>
       <c r="R63" t="n">
-        <v>7065308</v>
+        <v>7065026</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7077,6 +7077,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7103,10 +7108,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129060029</v>
+        <v>129059674</v>
       </c>
       <c r="B64" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7114,39 +7119,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>468970</v>
+        <v>469226</v>
       </c>
       <c r="R64" t="n">
-        <v>7064946</v>
+        <v>7065299</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7179,11 +7179,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7210,10 +7205,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129060021</v>
+        <v>129059687</v>
       </c>
       <c r="B65" t="n">
-        <v>57725</v>
+        <v>80147</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7221,39 +7216,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>468788</v>
+        <v>468843</v>
       </c>
       <c r="R65" t="n">
-        <v>7065344</v>
+        <v>7065390</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7288,11 +7278,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7301,6 +7286,21 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7317,32 +7317,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129060043</v>
+        <v>129059675</v>
       </c>
       <c r="B66" t="n">
-        <v>75029</v>
+        <v>91538</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6428</v>
+        <v>1108</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>469011</v>
+        <v>469197</v>
       </c>
       <c r="R66" t="n">
-        <v>7065022</v>
+        <v>7065308</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7414,10 +7414,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129059674</v>
+        <v>129060050</v>
       </c>
       <c r="B67" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7449,10 +7449,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>469226</v>
+        <v>469118</v>
       </c>
       <c r="R67" t="n">
-        <v>7065299</v>
+        <v>7065190</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7485,6 +7485,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7511,32 +7516,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129060050</v>
+        <v>129060043</v>
       </c>
       <c r="B68" t="n">
-        <v>79039</v>
+        <v>75031</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7546,10 +7551,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>469118</v>
+        <v>469011</v>
       </c>
       <c r="R68" t="n">
-        <v>7065190</v>
+        <v>7065022</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7582,11 +7587,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7616,7 +7616,7 @@
         <v>129059682</v>
       </c>
       <c r="B69" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>129059670</v>
       </c>
       <c r="B70" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7817,10 +7817,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129060051</v>
+        <v>129060011</v>
       </c>
       <c r="B71" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7828,34 +7828,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>469121</v>
+        <v>469245</v>
       </c>
       <c r="R71" t="n">
-        <v>7064885</v>
+        <v>7065256</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7892,7 +7897,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Med apotechier</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7919,10 +7924,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129060011</v>
+        <v>129060051</v>
       </c>
       <c r="B72" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7930,39 +7935,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>469245</v>
+        <v>469121</v>
       </c>
       <c r="R72" t="n">
-        <v>7065256</v>
+        <v>7064885</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8026,32 +8026,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129060047</v>
+        <v>129059698</v>
       </c>
       <c r="B73" t="n">
-        <v>91901</v>
+        <v>80147</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2063</v>
+        <v>2081</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>469012</v>
+        <v>469120</v>
       </c>
       <c r="R73" t="n">
-        <v>7065037</v>
+        <v>7065078</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8107,6 +8107,21 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8123,10 +8138,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129059698</v>
+        <v>129060040</v>
       </c>
       <c r="B74" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8158,10 +8173,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>469120</v>
+        <v>469148</v>
       </c>
       <c r="R74" t="n">
-        <v>7065078</v>
+        <v>7065056</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8204,21 +8219,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8235,32 +8235,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129060040</v>
+        <v>129060047</v>
       </c>
       <c r="B75" t="n">
-        <v>80145</v>
+        <v>91903</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>469148</v>
+        <v>469012</v>
       </c>
       <c r="R75" t="n">
-        <v>7065056</v>
+        <v>7065037</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8335,7 +8335,7 @@
         <v>129059714</v>
       </c>
       <c r="B76" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>129059701</v>
       </c>
       <c r="B77" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>129059677</v>
       </c>
       <c r="B78" t="n">
-        <v>78052</v>
+        <v>78054</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>129059680</v>
       </c>
       <c r="B79" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>129060016</v>
       </c>
       <c r="B80" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>129060014</v>
       </c>
       <c r="B81" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>129059706</v>
       </c>
       <c r="B82" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9076,10 +9076,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129059696</v>
+        <v>129059679</v>
       </c>
       <c r="B83" t="n">
-        <v>91558</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9087,34 +9087,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>469141</v>
+        <v>469108</v>
       </c>
       <c r="R83" t="n">
-        <v>7065095</v>
+        <v>7065364</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9147,6 +9152,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9173,10 +9183,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129059679</v>
+        <v>129059713</v>
       </c>
       <c r="B84" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9213,10 +9223,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>469108</v>
+        <v>468922</v>
       </c>
       <c r="R84" t="n">
-        <v>7065364</v>
+        <v>7064998</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9280,10 +9290,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129059713</v>
+        <v>129059692</v>
       </c>
       <c r="B85" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9320,10 +9330,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>468922</v>
+        <v>469137</v>
       </c>
       <c r="R85" t="n">
-        <v>7064998</v>
+        <v>7065206</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9387,10 +9397,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129059692</v>
+        <v>129059696</v>
       </c>
       <c r="B86" t="n">
-        <v>57725</v>
+        <v>91560</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9398,39 +9408,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>469137</v>
+        <v>469141</v>
       </c>
       <c r="R86" t="n">
-        <v>7065206</v>
+        <v>7065095</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9463,11 +9468,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9494,10 +9494,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129059676</v>
+        <v>129059712</v>
       </c>
       <c r="B87" t="n">
-        <v>83005</v>
+        <v>79041</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9505,21 +9505,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9529,10 +9529,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>469160</v>
+        <v>468868</v>
       </c>
       <c r="R87" t="n">
-        <v>7065329</v>
+        <v>7064989</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9591,10 +9591,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129059712</v>
+        <v>129059676</v>
       </c>
       <c r="B88" t="n">
-        <v>79039</v>
+        <v>83007</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9602,21 +9602,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>468868</v>
+        <v>469160</v>
       </c>
       <c r="R88" t="n">
-        <v>7064989</v>
+        <v>7065329</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129060012</v>
+        <v>129059710</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469235</v>
+        <v>468844</v>
       </c>
       <c r="R2" t="n">
-        <v>7065256</v>
+        <v>7064978</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,11 +748,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -766,6 +756,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129060023</v>
+        <v>129059689</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469142</v>
+        <v>468887</v>
       </c>
       <c r="R3" t="n">
-        <v>7065079</v>
+        <v>7065318</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129060033</v>
+        <v>129059683</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,39 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469047</v>
+        <v>468964</v>
       </c>
       <c r="R4" t="n">
-        <v>7064905</v>
+        <v>7065331</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129060008</v>
+        <v>129060044</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,39 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469327</v>
+        <v>469111</v>
       </c>
       <c r="R5" t="n">
-        <v>7065224</v>
+        <v>7065086</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1052,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129060020</v>
+        <v>129059711</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,39 +1089,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468803</v>
+        <v>468844</v>
       </c>
       <c r="R6" t="n">
-        <v>7065369</v>
+        <v>7064978</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,11 +1151,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1194,6 +1159,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1210,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129060024</v>
+        <v>129060012</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1241,7 +1221,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1250,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469131</v>
+        <v>469235</v>
       </c>
       <c r="R7" t="n">
-        <v>7065083</v>
+        <v>7065256</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129060044</v>
+        <v>129060023</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,34 +1308,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469111</v>
+        <v>469142</v>
       </c>
       <c r="R8" t="n">
-        <v>7065086</v>
+        <v>7065079</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1373,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129059683</v>
+        <v>129060033</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1425,34 +1415,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468964</v>
+        <v>469047</v>
       </c>
       <c r="R9" t="n">
-        <v>7065331</v>
+        <v>7064905</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,6 +1480,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129059711</v>
+        <v>129060008</v>
       </c>
       <c r="B10" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,34 +1522,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468844</v>
+        <v>469327</v>
       </c>
       <c r="R10" t="n">
-        <v>7064978</v>
+        <v>7065224</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,6 +1589,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1592,21 +1602,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1623,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129059689</v>
+        <v>129060020</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1634,34 +1629,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468887</v>
+        <v>468803</v>
       </c>
       <c r="R11" t="n">
-        <v>7065318</v>
+        <v>7065369</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,6 +1694,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129059710</v>
+        <v>129060024</v>
       </c>
       <c r="B12" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,34 +1736,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468844</v>
+        <v>469131</v>
       </c>
       <c r="R12" t="n">
-        <v>7064978</v>
+        <v>7065083</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1793,6 +1803,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1801,21 +1816,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129060022</v>
+        <v>129060045</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,39 +2047,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468893</v>
+        <v>469013</v>
       </c>
       <c r="R15" t="n">
-        <v>7065289</v>
+        <v>7065018</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,11 +2107,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2143,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129060037</v>
+        <v>129060022</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2154,27 +2144,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2183,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468874</v>
+        <v>468893</v>
       </c>
       <c r="R16" t="n">
-        <v>7064975</v>
+        <v>7065289</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,6 +2209,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2245,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129060045</v>
+        <v>129060037</v>
       </c>
       <c r="B17" t="n">
-        <v>80146</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,34 +2251,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>469013</v>
+        <v>468874</v>
       </c>
       <c r="R17" t="n">
-        <v>7065018</v>
+        <v>7064975</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2551,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129060003</v>
+        <v>129059695</v>
       </c>
       <c r="B20" t="n">
-        <v>91542</v>
+        <v>80146</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,21 +2562,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469006</v>
+        <v>469141</v>
       </c>
       <c r="R20" t="n">
-        <v>7065358</v>
+        <v>7065114</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2632,6 +2632,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2750,10 +2765,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129060007</v>
+        <v>129060003</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,39 +2776,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469364</v>
+        <v>469006</v>
       </c>
       <c r="R22" t="n">
-        <v>7065232</v>
+        <v>7065358</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,11 +2836,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2857,7 +2862,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129059685</v>
+        <v>129060007</v>
       </c>
       <c r="B23" t="n">
         <v>57727</v>
@@ -2897,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468878</v>
+        <v>469364</v>
       </c>
       <c r="R23" t="n">
-        <v>7065401</v>
+        <v>7065232</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2964,10 +2969,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129059695</v>
+        <v>129059685</v>
       </c>
       <c r="B24" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2975,34 +2980,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469141</v>
+        <v>468878</v>
       </c>
       <c r="R24" t="n">
-        <v>7065114</v>
+        <v>7065401</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3037,6 +3047,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3045,21 +3060,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3290,32 +3290,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129060006</v>
+        <v>129060046</v>
       </c>
       <c r="B27" t="n">
-        <v>92242</v>
+        <v>91538</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469045</v>
+        <v>469215</v>
       </c>
       <c r="R27" t="n">
-        <v>7065011</v>
+        <v>7065278</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3387,32 +3387,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129060048</v>
+        <v>129060006</v>
       </c>
       <c r="B28" t="n">
-        <v>91560</v>
+        <v>92242</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469135</v>
+        <v>469045</v>
       </c>
       <c r="R28" t="n">
-        <v>7065166</v>
+        <v>7065011</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,10 +3484,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129060046</v>
+        <v>129060048</v>
       </c>
       <c r="B29" t="n">
-        <v>91538</v>
+        <v>91560</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3495,21 +3495,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3519,10 +3519,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469215</v>
+        <v>469135</v>
       </c>
       <c r="R29" t="n">
-        <v>7065278</v>
+        <v>7065166</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4523,45 +4523,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129060001</v>
+        <v>129059684</v>
       </c>
       <c r="B39" t="n">
-        <v>91506</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468967</v>
+        <v>468895</v>
       </c>
       <c r="R39" t="n">
-        <v>7065256</v>
+        <v>7065399</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4594,6 +4599,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4620,7 +4630,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129059684</v>
+        <v>129060026</v>
       </c>
       <c r="B40" t="n">
         <v>57727</v>
@@ -4660,10 +4670,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>468895</v>
+        <v>468886</v>
       </c>
       <c r="R40" t="n">
-        <v>7065399</v>
+        <v>7065015</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4727,7 +4737,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129060026</v>
+        <v>129059715</v>
       </c>
       <c r="B41" t="n">
         <v>57727</v>
@@ -4767,10 +4777,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468886</v>
+        <v>469047</v>
       </c>
       <c r="R41" t="n">
-        <v>7065015</v>
+        <v>7064912</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4834,50 +4844,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129059715</v>
+        <v>129060001</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>91506</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469047</v>
+        <v>468967</v>
       </c>
       <c r="R42" t="n">
-        <v>7064912</v>
+        <v>7065256</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4910,11 +4915,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5038,10 +5038,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129060018</v>
+        <v>129060049</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>91560</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,39 +5049,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>469093</v>
+        <v>469012</v>
       </c>
       <c r="R44" t="n">
-        <v>7065345</v>
+        <v>7065037</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5114,11 +5109,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5145,10 +5135,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129060017</v>
+        <v>129059703</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5156,39 +5146,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>469122</v>
+        <v>468883</v>
       </c>
       <c r="R45" t="n">
-        <v>7065303</v>
+        <v>7065026</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5221,11 +5206,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5252,10 +5232,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129060049</v>
+        <v>129059699</v>
       </c>
       <c r="B46" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5263,21 +5243,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5287,10 +5267,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469012</v>
+        <v>469071</v>
       </c>
       <c r="R46" t="n">
-        <v>7065037</v>
+        <v>7065075</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5349,10 +5329,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129059699</v>
+        <v>129060018</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5360,34 +5340,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>469071</v>
+        <v>469093</v>
       </c>
       <c r="R47" t="n">
-        <v>7065075</v>
+        <v>7065345</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5420,6 +5405,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5446,10 +5436,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129059703</v>
+        <v>129060017</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5457,34 +5447,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>468883</v>
+        <v>469122</v>
       </c>
       <c r="R48" t="n">
-        <v>7065026</v>
+        <v>7065303</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5517,6 +5512,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5543,10 +5543,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129059709</v>
+        <v>129059704</v>
       </c>
       <c r="B49" t="n">
-        <v>83002</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5554,34 +5554,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>468844</v>
+        <v>468883</v>
       </c>
       <c r="R49" t="n">
-        <v>7064978</v>
+        <v>7065026</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5616,6 +5621,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5624,21 +5634,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5655,10 +5650,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129059702</v>
+        <v>129060031</v>
       </c>
       <c r="B50" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5666,34 +5661,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>468889</v>
+        <v>469014</v>
       </c>
       <c r="R50" t="n">
-        <v>7065025</v>
+        <v>7064913</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5726,6 +5726,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5752,10 +5757,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129059704</v>
+        <v>129059709</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>83002</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5763,39 +5768,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>310</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>468883</v>
+        <v>468844</v>
       </c>
       <c r="R51" t="n">
-        <v>7065026</v>
+        <v>7064978</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5830,11 +5830,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5843,6 +5838,21 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -5859,10 +5869,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129060031</v>
+        <v>129059702</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5870,39 +5880,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>469014</v>
+        <v>468889</v>
       </c>
       <c r="R52" t="n">
-        <v>7064913</v>
+        <v>7065025</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5935,11 +5940,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5966,32 +5966,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129059697</v>
+        <v>129060042</v>
       </c>
       <c r="B53" t="n">
-        <v>80146</v>
+        <v>80050</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6001,10 +6001,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>469114</v>
+        <v>469356</v>
       </c>
       <c r="R53" t="n">
-        <v>7065083</v>
+        <v>7065233</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6047,21 +6047,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6078,32 +6063,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129060042</v>
+        <v>129059697</v>
       </c>
       <c r="B54" t="n">
-        <v>80050</v>
+        <v>80146</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6113,10 +6098,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>469356</v>
+        <v>469114</v>
       </c>
       <c r="R54" t="n">
-        <v>7065233</v>
+        <v>7065083</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6159,6 +6144,21 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6374,10 +6374,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129060005</v>
+        <v>129059693</v>
       </c>
       <c r="B57" t="n">
-        <v>91542</v>
+        <v>91560</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6385,21 +6385,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6409,10 +6409,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>468821</v>
+        <v>469137</v>
       </c>
       <c r="R57" t="n">
-        <v>7065043</v>
+        <v>7065120</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6471,10 +6471,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129060032</v>
+        <v>129060005</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6482,39 +6482,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>469043</v>
+        <v>468821</v>
       </c>
       <c r="R58" t="n">
-        <v>7064905</v>
+        <v>7065043</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6547,11 +6542,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6578,10 +6568,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129059693</v>
+        <v>129060032</v>
       </c>
       <c r="B59" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6589,34 +6579,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>469137</v>
+        <v>469043</v>
       </c>
       <c r="R59" t="n">
-        <v>7065120</v>
+        <v>7064905</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6649,6 +6644,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6675,10 +6675,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129059686</v>
+        <v>129059687</v>
       </c>
       <c r="B60" t="n">
-        <v>83002</v>
+        <v>80147</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6686,21 +6686,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>310</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6787,10 +6787,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129060029</v>
+        <v>129059675</v>
       </c>
       <c r="B61" t="n">
-        <v>57727</v>
+        <v>91538</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6798,39 +6798,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468970</v>
+        <v>469197</v>
       </c>
       <c r="R61" t="n">
-        <v>7064946</v>
+        <v>7065308</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6863,11 +6858,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6894,10 +6884,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129060021</v>
+        <v>129059674</v>
       </c>
       <c r="B62" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6905,39 +6895,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468788</v>
+        <v>469226</v>
       </c>
       <c r="R62" t="n">
-        <v>7065344</v>
+        <v>7065299</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6970,11 +6955,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7001,50 +6981,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129060025</v>
+        <v>129060043</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>75031</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>469101</v>
+        <v>469011</v>
       </c>
       <c r="R63" t="n">
-        <v>7065026</v>
+        <v>7065022</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7077,11 +7052,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7108,7 +7078,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129059674</v>
+        <v>129060050</v>
       </c>
       <c r="B64" t="n">
         <v>79041</v>
@@ -7143,10 +7113,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>469226</v>
+        <v>469118</v>
       </c>
       <c r="R64" t="n">
-        <v>7065299</v>
+        <v>7065190</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7179,6 +7149,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7205,10 +7180,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129059687</v>
+        <v>129060029</v>
       </c>
       <c r="B65" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7216,34 +7191,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>468843</v>
+        <v>468970</v>
       </c>
       <c r="R65" t="n">
-        <v>7065390</v>
+        <v>7064946</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7278,6 +7258,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7286,21 +7271,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7317,10 +7287,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129059675</v>
+        <v>129060021</v>
       </c>
       <c r="B66" t="n">
-        <v>91538</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7328,34 +7298,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>469197</v>
+        <v>468788</v>
       </c>
       <c r="R66" t="n">
-        <v>7065308</v>
+        <v>7065344</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7388,6 +7363,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7414,10 +7394,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129060050</v>
+        <v>129060025</v>
       </c>
       <c r="B67" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7425,34 +7405,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>469118</v>
+        <v>469101</v>
       </c>
       <c r="R67" t="n">
-        <v>7065190</v>
+        <v>7065026</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7489,7 +7474,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7516,32 +7501,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129060043</v>
+        <v>129059686</v>
       </c>
       <c r="B68" t="n">
-        <v>75031</v>
+        <v>83002</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6428</v>
+        <v>310</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7551,10 +7536,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>469011</v>
+        <v>468843</v>
       </c>
       <c r="R68" t="n">
-        <v>7065022</v>
+        <v>7065390</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7597,6 +7582,21 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -7817,10 +7817,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129060011</v>
+        <v>129060051</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7828,39 +7828,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>469245</v>
+        <v>469121</v>
       </c>
       <c r="R71" t="n">
-        <v>7065256</v>
+        <v>7064885</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7897,7 +7892,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7924,10 +7919,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129060051</v>
+        <v>129060011</v>
       </c>
       <c r="B72" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7935,34 +7930,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>469121</v>
+        <v>469245</v>
       </c>
       <c r="R72" t="n">
-        <v>7064885</v>
+        <v>7065256</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Med apotechier</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8026,7 +8026,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129059698</v>
+        <v>129060040</v>
       </c>
       <c r="B73" t="n">
         <v>80147</v>
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>469120</v>
+        <v>469148</v>
       </c>
       <c r="R73" t="n">
-        <v>7065078</v>
+        <v>7065056</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8107,21 +8107,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8138,10 +8123,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129060040</v>
+        <v>129059677</v>
       </c>
       <c r="B74" t="n">
-        <v>80147</v>
+        <v>78054</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8149,21 +8134,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8173,10 +8158,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>469148</v>
+        <v>469160</v>
       </c>
       <c r="R74" t="n">
-        <v>7065056</v>
+        <v>7065329</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8332,10 +8317,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129059714</v>
+        <v>129059698</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8343,39 +8328,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>468946</v>
+        <v>469120</v>
       </c>
       <c r="R76" t="n">
-        <v>7064969</v>
+        <v>7065078</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8410,11 +8390,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8423,6 +8398,21 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8439,7 +8429,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129059701</v>
+        <v>129059714</v>
       </c>
       <c r="B77" t="n">
         <v>57727</v>
@@ -8479,10 +8469,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>468991</v>
+        <v>468946</v>
       </c>
       <c r="R77" t="n">
-        <v>7065056</v>
+        <v>7064969</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8546,10 +8536,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129059677</v>
+        <v>129059701</v>
       </c>
       <c r="B78" t="n">
-        <v>78054</v>
+        <v>57727</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8557,34 +8547,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>469160</v>
+        <v>468991</v>
       </c>
       <c r="R78" t="n">
-        <v>7065329</v>
+        <v>7065056</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8617,6 +8612,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8964,10 +8964,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129059706</v>
+        <v>129059676</v>
       </c>
       <c r="B82" t="n">
-        <v>80147</v>
+        <v>83007</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8975,21 +8975,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8999,10 +8999,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>468850</v>
+        <v>469160</v>
       </c>
       <c r="R82" t="n">
-        <v>7065034</v>
+        <v>7065329</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9045,21 +9045,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9076,10 +9061,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129059679</v>
+        <v>129059712</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9087,39 +9072,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>469108</v>
+        <v>468868</v>
       </c>
       <c r="R83" t="n">
-        <v>7065364</v>
+        <v>7064989</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9152,11 +9132,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9183,10 +9158,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129059713</v>
+        <v>129059706</v>
       </c>
       <c r="B84" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9194,39 +9169,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>468922</v>
+        <v>468850</v>
       </c>
       <c r="R84" t="n">
-        <v>7064998</v>
+        <v>7065034</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9261,11 +9231,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9274,6 +9239,21 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -9290,10 +9270,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129059692</v>
+        <v>129059696</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>91560</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9301,39 +9281,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>469137</v>
+        <v>469141</v>
       </c>
       <c r="R85" t="n">
-        <v>7065206</v>
+        <v>7065095</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9366,11 +9341,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9397,10 +9367,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129059696</v>
+        <v>129059679</v>
       </c>
       <c r="B86" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9408,34 +9378,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>469141</v>
+        <v>469108</v>
       </c>
       <c r="R86" t="n">
-        <v>7065095</v>
+        <v>7065364</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9468,6 +9443,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9494,10 +9474,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129059712</v>
+        <v>129059713</v>
       </c>
       <c r="B87" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9505,34 +9485,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>468868</v>
+        <v>468922</v>
       </c>
       <c r="R87" t="n">
-        <v>7064989</v>
+        <v>7064998</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9565,6 +9550,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9591,10 +9581,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129059676</v>
+        <v>129059692</v>
       </c>
       <c r="B88" t="n">
-        <v>83007</v>
+        <v>57727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9602,34 +9592,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>469160</v>
+        <v>469137</v>
       </c>
       <c r="R88" t="n">
-        <v>7065329</v>
+        <v>7065206</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9662,6 +9657,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129059710</v>
+        <v>129059689</v>
       </c>
       <c r="B2" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468844</v>
+        <v>468887</v>
       </c>
       <c r="R2" t="n">
-        <v>7064978</v>
+        <v>7065318</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,21 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129059689</v>
+        <v>129059683</v>
       </c>
       <c r="B3" t="n">
         <v>79041</v>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468887</v>
+        <v>468964</v>
       </c>
       <c r="R3" t="n">
-        <v>7065318</v>
+        <v>7065331</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129059683</v>
+        <v>129060044</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468964</v>
+        <v>469111</v>
       </c>
       <c r="R4" t="n">
-        <v>7065331</v>
+        <v>7065086</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129060044</v>
+        <v>129059711</v>
       </c>
       <c r="B5" t="n">
         <v>80146</v>
@@ -1016,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469111</v>
+        <v>468844</v>
       </c>
       <c r="R5" t="n">
-        <v>7065086</v>
+        <v>7064978</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1047,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129059711</v>
+        <v>129059710</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129059708</v>
+        <v>129059695</v>
       </c>
       <c r="B18" t="n">
-        <v>83012</v>
+        <v>80146</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1467</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468783</v>
+        <v>469141</v>
       </c>
       <c r="R18" t="n">
-        <v>7065001</v>
+        <v>7065114</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2426,17 +2426,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129060039</v>
+        <v>129060003</v>
       </c>
       <c r="B19" t="n">
-        <v>80147</v>
+        <v>91542</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,21 +2465,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469139</v>
+        <v>469006</v>
       </c>
       <c r="R19" t="n">
-        <v>7065094</v>
+        <v>7065358</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2551,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129059695</v>
+        <v>129059708</v>
       </c>
       <c r="B20" t="n">
-        <v>80146</v>
+        <v>83012</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,21 +2562,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469141</v>
+        <v>468783</v>
       </c>
       <c r="R20" t="n">
-        <v>7065114</v>
+        <v>7065001</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2635,17 +2635,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129060038</v>
+        <v>129060039</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>80147</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,39 +2674,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469007</v>
+        <v>469139</v>
       </c>
       <c r="R21" t="n">
-        <v>7064930</v>
+        <v>7065094</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,10 +2760,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129060003</v>
+        <v>129060007</v>
       </c>
       <c r="B22" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2776,34 +2771,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469006</v>
+        <v>469364</v>
       </c>
       <c r="R22" t="n">
-        <v>7065358</v>
+        <v>7065232</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2836,6 +2836,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2862,7 +2867,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129060007</v>
+        <v>129059685</v>
       </c>
       <c r="B23" t="n">
         <v>57727</v>
@@ -2902,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469364</v>
+        <v>468878</v>
       </c>
       <c r="R23" t="n">
-        <v>7065232</v>
+        <v>7065401</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2969,10 +2974,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129059685</v>
+        <v>129060038</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2980,27 +2985,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3009,10 +3014,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>468878</v>
+        <v>469007</v>
       </c>
       <c r="R24" t="n">
-        <v>7065401</v>
+        <v>7064930</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,11 +3050,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3290,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129060046</v>
+        <v>129060035</v>
       </c>
       <c r="B27" t="n">
-        <v>91538</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3301,34 +3301,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469215</v>
+        <v>469149</v>
       </c>
       <c r="R27" t="n">
-        <v>7065278</v>
+        <v>7065169</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3387,32 +3396,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129060006</v>
+        <v>129060046</v>
       </c>
       <c r="B28" t="n">
-        <v>92242</v>
+        <v>91538</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3422,10 +3431,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469045</v>
+        <v>469215</v>
       </c>
       <c r="R28" t="n">
-        <v>7065011</v>
+        <v>7065278</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,32 +3493,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129060048</v>
+        <v>129060006</v>
       </c>
       <c r="B29" t="n">
-        <v>91560</v>
+        <v>92242</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3519,10 +3528,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469135</v>
+        <v>469045</v>
       </c>
       <c r="R29" t="n">
-        <v>7065166</v>
+        <v>7065011</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3581,10 +3590,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129060027</v>
+        <v>129060048</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>91560</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3592,39 +3601,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>468896</v>
+        <v>469135</v>
       </c>
       <c r="R30" t="n">
-        <v>7064986</v>
+        <v>7065166</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3657,11 +3661,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3688,10 +3687,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129060035</v>
+        <v>129060027</v>
       </c>
       <c r="B31" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3699,31 +3698,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3732,10 +3727,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469149</v>
+        <v>468896</v>
       </c>
       <c r="R31" t="n">
-        <v>7065169</v>
+        <v>7064986</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3768,6 +3763,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -5038,10 +5038,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129060049</v>
+        <v>129059703</v>
       </c>
       <c r="B44" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,21 +5049,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>469012</v>
+        <v>468883</v>
       </c>
       <c r="R44" t="n">
-        <v>7065037</v>
+        <v>7065026</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129059703</v>
+        <v>129059699</v>
       </c>
       <c r="B45" t="n">
         <v>79041</v>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>468883</v>
+        <v>469071</v>
       </c>
       <c r="R45" t="n">
-        <v>7065026</v>
+        <v>7065075</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5232,10 +5232,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129059699</v>
+        <v>129060049</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5243,21 +5243,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469071</v>
+        <v>469012</v>
       </c>
       <c r="R46" t="n">
-        <v>7065075</v>
+        <v>7065037</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6374,10 +6374,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129059693</v>
+        <v>129060032</v>
       </c>
       <c r="B57" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6385,34 +6385,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>469137</v>
+        <v>469043</v>
       </c>
       <c r="R57" t="n">
-        <v>7065120</v>
+        <v>7064905</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6445,6 +6450,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6471,10 +6481,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129060005</v>
+        <v>129059693</v>
       </c>
       <c r="B58" t="n">
-        <v>91542</v>
+        <v>91560</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6482,21 +6492,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6506,10 +6516,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468821</v>
+        <v>469137</v>
       </c>
       <c r="R58" t="n">
-        <v>7065043</v>
+        <v>7065120</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6568,10 +6578,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129060032</v>
+        <v>129060005</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6579,39 +6589,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>469043</v>
+        <v>468821</v>
       </c>
       <c r="R59" t="n">
-        <v>7064905</v>
+        <v>7065043</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6644,11 +6649,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6787,10 +6787,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129059675</v>
+        <v>129059686</v>
       </c>
       <c r="B61" t="n">
-        <v>91538</v>
+        <v>83002</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6798,21 +6798,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>310</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6822,10 +6822,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>469197</v>
+        <v>468843</v>
       </c>
       <c r="R61" t="n">
-        <v>7065308</v>
+        <v>7065390</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6868,6 +6868,21 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6884,10 +6899,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129059674</v>
+        <v>129059675</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>91538</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6895,21 +6910,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6919,10 +6934,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>469226</v>
+        <v>469197</v>
       </c>
       <c r="R62" t="n">
-        <v>7065299</v>
+        <v>7065308</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6981,32 +6996,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129060043</v>
+        <v>129059674</v>
       </c>
       <c r="B63" t="n">
-        <v>75031</v>
+        <v>79041</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7016,10 +7031,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>469011</v>
+        <v>469226</v>
       </c>
       <c r="R63" t="n">
-        <v>7065022</v>
+        <v>7065299</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7078,32 +7093,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129060050</v>
+        <v>129060043</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>75031</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7113,10 +7128,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>469118</v>
+        <v>469011</v>
       </c>
       <c r="R64" t="n">
-        <v>7065190</v>
+        <v>7065022</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7149,11 +7164,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7180,10 +7190,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129060029</v>
+        <v>129060050</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7191,39 +7201,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>468970</v>
+        <v>469118</v>
       </c>
       <c r="R65" t="n">
-        <v>7064946</v>
+        <v>7065190</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7260,7 +7265,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7287,7 +7292,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129060021</v>
+        <v>129060029</v>
       </c>
       <c r="B66" t="n">
         <v>57727</v>
@@ -7318,7 +7323,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7327,10 +7332,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468788</v>
+        <v>468970</v>
       </c>
       <c r="R66" t="n">
-        <v>7065344</v>
+        <v>7064946</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7394,7 +7399,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129060025</v>
+        <v>129060021</v>
       </c>
       <c r="B67" t="n">
         <v>57727</v>
@@ -7425,7 +7430,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7434,10 +7439,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>469101</v>
+        <v>468788</v>
       </c>
       <c r="R67" t="n">
-        <v>7065026</v>
+        <v>7065344</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7501,10 +7506,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129059686</v>
+        <v>129060025</v>
       </c>
       <c r="B68" t="n">
-        <v>83002</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7512,34 +7517,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>468843</v>
+        <v>469101</v>
       </c>
       <c r="R68" t="n">
-        <v>7065390</v>
+        <v>7065026</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7574,6 +7584,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7582,21 +7597,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -7817,10 +7817,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129060051</v>
+        <v>129060011</v>
       </c>
       <c r="B71" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7828,34 +7828,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>469121</v>
+        <v>469245</v>
       </c>
       <c r="R71" t="n">
-        <v>7064885</v>
+        <v>7065256</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7892,7 +7897,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Med apotechier</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7919,10 +7924,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129060011</v>
+        <v>129060051</v>
       </c>
       <c r="B72" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7930,39 +7935,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>469245</v>
+        <v>469121</v>
       </c>
       <c r="R72" t="n">
-        <v>7065256</v>
+        <v>7064885</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129059689</v>
+        <v>129059710</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468887</v>
+        <v>468844</v>
       </c>
       <c r="R2" t="n">
-        <v>7065318</v>
+        <v>7064978</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,6 +756,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -772,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129059683</v>
+        <v>129059689</v>
       </c>
       <c r="B3" t="n">
         <v>79041</v>
@@ -807,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468964</v>
+        <v>468887</v>
       </c>
       <c r="R3" t="n">
-        <v>7065331</v>
+        <v>7065318</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129060044</v>
+        <v>129059683</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469111</v>
+        <v>468964</v>
       </c>
       <c r="R4" t="n">
-        <v>7065086</v>
+        <v>7065331</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129059711</v>
+        <v>129060044</v>
       </c>
       <c r="B5" t="n">
         <v>80146</v>
@@ -1001,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468844</v>
+        <v>469111</v>
       </c>
       <c r="R5" t="n">
-        <v>7064978</v>
+        <v>7065086</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,21 +1062,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129059710</v>
+        <v>129059711</v>
       </c>
       <c r="B6" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129060015</v>
+        <v>129059678</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,39 +1843,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469142</v>
+        <v>469160</v>
       </c>
       <c r="R13" t="n">
-        <v>7065300</v>
+        <v>7065329</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,11 +1903,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129059678</v>
+        <v>129060015</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1950,34 +1940,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469160</v>
+        <v>469142</v>
       </c>
       <c r="R14" t="n">
-        <v>7065329</v>
+        <v>7065300</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,6 +2005,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129060045</v>
+        <v>129060037</v>
       </c>
       <c r="B15" t="n">
-        <v>80146</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,34 +2047,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469013</v>
+        <v>468874</v>
       </c>
       <c r="R15" t="n">
-        <v>7065018</v>
+        <v>7064975</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2240,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129060037</v>
+        <v>129060045</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>80146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,39 +2256,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468874</v>
+        <v>469013</v>
       </c>
       <c r="R17" t="n">
-        <v>7064975</v>
+        <v>7065018</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129059695</v>
+        <v>129060038</v>
       </c>
       <c r="B18" t="n">
-        <v>80146</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,34 +2353,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469141</v>
+        <v>469007</v>
       </c>
       <c r="R18" t="n">
-        <v>7065114</v>
+        <v>7064930</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2423,21 +2428,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2454,10 +2444,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129060003</v>
+        <v>129059708</v>
       </c>
       <c r="B19" t="n">
-        <v>91542</v>
+        <v>83012</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,21 +2455,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469006</v>
+        <v>468783</v>
       </c>
       <c r="R19" t="n">
-        <v>7065358</v>
+        <v>7065001</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,6 +2525,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2551,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129059708</v>
+        <v>129060039</v>
       </c>
       <c r="B20" t="n">
-        <v>83012</v>
+        <v>80147</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,21 +2567,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2586,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468783</v>
+        <v>469139</v>
       </c>
       <c r="R20" t="n">
-        <v>7065001</v>
+        <v>7065094</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2632,21 +2637,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2663,10 +2653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129060039</v>
+        <v>129059695</v>
       </c>
       <c r="B21" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,21 +2664,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2698,10 +2688,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469139</v>
+        <v>469141</v>
       </c>
       <c r="R21" t="n">
-        <v>7065094</v>
+        <v>7065114</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,6 +2734,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2760,10 +2765,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129060007</v>
+        <v>129060003</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2771,39 +2776,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469364</v>
+        <v>469006</v>
       </c>
       <c r="R22" t="n">
-        <v>7065232</v>
+        <v>7065358</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2836,11 +2836,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2867,7 +2862,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129059685</v>
+        <v>129060007</v>
       </c>
       <c r="B23" t="n">
         <v>57727</v>
@@ -2907,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468878</v>
+        <v>469364</v>
       </c>
       <c r="R23" t="n">
-        <v>7065401</v>
+        <v>7065232</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2974,10 +2969,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129060038</v>
+        <v>129059685</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2985,27 +2980,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3014,10 +3009,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469007</v>
+        <v>468878</v>
       </c>
       <c r="R24" t="n">
-        <v>7064930</v>
+        <v>7065401</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3050,6 +3045,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3290,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129060035</v>
+        <v>129060027</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3301,31 +3301,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3334,10 +3330,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469149</v>
+        <v>468896</v>
       </c>
       <c r="R27" t="n">
-        <v>7065169</v>
+        <v>7064986</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3370,6 +3366,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3399,7 +3400,7 @@
         <v>129060046</v>
       </c>
       <c r="B28" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3496,7 +3497,7 @@
         <v>129060006</v>
       </c>
       <c r="B29" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3593,7 +3594,7 @@
         <v>129060048</v>
       </c>
       <c r="B30" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3687,10 +3688,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129060027</v>
+        <v>129060035</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3698,27 +3699,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3727,10 +3732,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>468896</v>
+        <v>469149</v>
       </c>
       <c r="R31" t="n">
-        <v>7064986</v>
+        <v>7065169</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3763,11 +3768,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3794,10 +3794,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129059681</v>
+        <v>129059691</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3805,39 +3805,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>469043</v>
+        <v>468992</v>
       </c>
       <c r="R32" t="n">
-        <v>7065365</v>
+        <v>7065224</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3870,11 +3865,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3901,32 +3891,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129059691</v>
+        <v>129059690</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>83005</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3936,10 +3926,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>468992</v>
+        <v>468887</v>
       </c>
       <c r="R33" t="n">
-        <v>7065224</v>
+        <v>7065318</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3998,45 +3988,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129059690</v>
+        <v>129059681</v>
       </c>
       <c r="B34" t="n">
-        <v>83005</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>468887</v>
+        <v>469043</v>
       </c>
       <c r="R34" t="n">
-        <v>7065318</v>
+        <v>7065365</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4069,6 +4064,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4095,10 +4095,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129059700</v>
+        <v>129060009</v>
       </c>
       <c r="B35" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4106,34 +4106,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>469036</v>
+        <v>469298</v>
       </c>
       <c r="R35" t="n">
-        <v>7065082</v>
+        <v>7065235</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4168,6 +4173,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4176,21 +4186,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4207,10 +4202,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129060009</v>
+        <v>129059700</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4218,39 +4213,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>469298</v>
+        <v>469036</v>
       </c>
       <c r="R36" t="n">
-        <v>7065235</v>
+        <v>7065082</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4285,11 +4275,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4298,6 +4283,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4429,7 +4429,7 @@
         <v>129060002</v>
       </c>
       <c r="B38" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4523,50 +4523,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129059684</v>
+        <v>129060001</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91504</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468895</v>
+        <v>468967</v>
       </c>
       <c r="R39" t="n">
-        <v>7065399</v>
+        <v>7065256</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4599,11 +4594,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4630,7 +4620,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129060026</v>
+        <v>129059684</v>
       </c>
       <c r="B40" t="n">
         <v>57727</v>
@@ -4670,10 +4660,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>468886</v>
+        <v>468895</v>
       </c>
       <c r="R40" t="n">
-        <v>7065015</v>
+        <v>7065399</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4737,7 +4727,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129059715</v>
+        <v>129060026</v>
       </c>
       <c r="B41" t="n">
         <v>57727</v>
@@ -4777,10 +4767,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>469047</v>
+        <v>468886</v>
       </c>
       <c r="R41" t="n">
-        <v>7064912</v>
+        <v>7065015</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4844,45 +4834,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129060001</v>
+        <v>129059715</v>
       </c>
       <c r="B42" t="n">
-        <v>91506</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>468967</v>
+        <v>469047</v>
       </c>
       <c r="R42" t="n">
-        <v>7065256</v>
+        <v>7064912</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4915,6 +4910,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5038,10 +5038,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129059703</v>
+        <v>129060049</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>91558</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,21 +5049,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5073,10 +5073,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>468883</v>
+        <v>469012</v>
       </c>
       <c r="R44" t="n">
-        <v>7065026</v>
+        <v>7065037</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129059699</v>
+        <v>129059703</v>
       </c>
       <c r="B45" t="n">
         <v>79041</v>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>469071</v>
+        <v>468883</v>
       </c>
       <c r="R45" t="n">
-        <v>7065075</v>
+        <v>7065026</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5232,10 +5232,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129060049</v>
+        <v>129059699</v>
       </c>
       <c r="B46" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5243,21 +5243,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469012</v>
+        <v>469071</v>
       </c>
       <c r="R46" t="n">
-        <v>7065037</v>
+        <v>7065075</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129059704</v>
+        <v>129059702</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5554,39 +5554,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>468883</v>
+        <v>468889</v>
       </c>
       <c r="R49" t="n">
-        <v>7065026</v>
+        <v>7065025</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5619,11 +5614,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5650,10 +5640,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129060031</v>
+        <v>129059709</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>83002</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5661,39 +5651,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>310</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>469014</v>
+        <v>468844</v>
       </c>
       <c r="R50" t="n">
-        <v>7064913</v>
+        <v>7064978</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5728,11 +5713,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5741,6 +5721,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5757,10 +5752,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129059709</v>
+        <v>129059704</v>
       </c>
       <c r="B51" t="n">
-        <v>83002</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5768,34 +5763,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>468844</v>
+        <v>468883</v>
       </c>
       <c r="R51" t="n">
-        <v>7064978</v>
+        <v>7065026</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5830,6 +5830,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5838,21 +5843,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -5869,10 +5859,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129059702</v>
+        <v>129060031</v>
       </c>
       <c r="B52" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5880,34 +5870,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>468889</v>
+        <v>469014</v>
       </c>
       <c r="R52" t="n">
-        <v>7065025</v>
+        <v>7064913</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5940,6 +5935,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6175,10 +6175,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129060041</v>
+        <v>129060036</v>
       </c>
       <c r="B55" t="n">
-        <v>80147</v>
+        <v>57887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6186,34 +6186,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>469143</v>
+        <v>468801</v>
       </c>
       <c r="R55" t="n">
-        <v>7065030</v>
+        <v>7065038</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6272,10 +6277,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129060036</v>
+        <v>129060041</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>80147</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6283,39 +6288,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>468801</v>
+        <v>469143</v>
       </c>
       <c r="R56" t="n">
-        <v>7065038</v>
+        <v>7065030</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6374,10 +6374,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129060032</v>
+        <v>129060005</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6385,39 +6385,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>469043</v>
+        <v>468821</v>
       </c>
       <c r="R57" t="n">
-        <v>7064905</v>
+        <v>7065043</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6450,11 +6445,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6484,7 +6474,7 @@
         <v>129059693</v>
       </c>
       <c r="B58" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6578,10 +6568,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129060005</v>
+        <v>129060032</v>
       </c>
       <c r="B59" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6589,34 +6579,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>468821</v>
+        <v>469043</v>
       </c>
       <c r="R59" t="n">
-        <v>7065043</v>
+        <v>7064905</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6649,6 +6644,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6675,10 +6675,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129059687</v>
+        <v>129059675</v>
       </c>
       <c r="B60" t="n">
-        <v>80147</v>
+        <v>91536</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6686,21 +6686,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>468843</v>
+        <v>469197</v>
       </c>
       <c r="R60" t="n">
-        <v>7065390</v>
+        <v>7065308</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6756,21 +6756,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6899,10 +6884,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129059675</v>
+        <v>129059674</v>
       </c>
       <c r="B62" t="n">
-        <v>91538</v>
+        <v>79041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6910,21 +6895,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6934,10 +6919,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>469197</v>
+        <v>469226</v>
       </c>
       <c r="R62" t="n">
-        <v>7065308</v>
+        <v>7065299</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6996,32 +6981,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129059674</v>
+        <v>129060043</v>
       </c>
       <c r="B63" t="n">
-        <v>79041</v>
+        <v>75031</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7031,10 +7016,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>469226</v>
+        <v>469011</v>
       </c>
       <c r="R63" t="n">
-        <v>7065299</v>
+        <v>7065022</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7093,32 +7078,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129060043</v>
+        <v>129060050</v>
       </c>
       <c r="B64" t="n">
-        <v>75031</v>
+        <v>79041</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7128,10 +7113,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>469011</v>
+        <v>469118</v>
       </c>
       <c r="R64" t="n">
-        <v>7065022</v>
+        <v>7065190</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7164,6 +7149,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7190,10 +7180,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129060050</v>
+        <v>129059687</v>
       </c>
       <c r="B65" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7201,21 +7191,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7225,10 +7215,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>469118</v>
+        <v>468843</v>
       </c>
       <c r="R65" t="n">
-        <v>7065190</v>
+        <v>7065390</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7263,11 +7253,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7276,6 +7261,21 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7613,10 +7613,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129059682</v>
+        <v>129059670</v>
       </c>
       <c r="B69" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7624,34 +7624,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>468990</v>
+        <v>469326</v>
       </c>
       <c r="R69" t="n">
-        <v>7065370</v>
+        <v>7065255</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7684,6 +7689,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7710,10 +7720,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129059670</v>
+        <v>129059682</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7721,39 +7731,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>469326</v>
+        <v>468990</v>
       </c>
       <c r="R70" t="n">
-        <v>7065255</v>
+        <v>7065370</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7786,11 +7791,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7817,10 +7817,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129060011</v>
+        <v>129060051</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7828,39 +7828,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>469245</v>
+        <v>469121</v>
       </c>
       <c r="R71" t="n">
-        <v>7065256</v>
+        <v>7064885</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7897,7 +7892,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7924,10 +7919,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129060051</v>
+        <v>129060011</v>
       </c>
       <c r="B72" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7935,34 +7930,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>469121</v>
+        <v>469245</v>
       </c>
       <c r="R72" t="n">
-        <v>7064885</v>
+        <v>7065256</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Med apotechier</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8026,10 +8026,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129060040</v>
+        <v>129059714</v>
       </c>
       <c r="B73" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8037,34 +8037,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>469148</v>
+        <v>468946</v>
       </c>
       <c r="R73" t="n">
-        <v>7065056</v>
+        <v>7064969</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8097,6 +8102,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8123,10 +8133,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129059677</v>
+        <v>129059701</v>
       </c>
       <c r="B74" t="n">
-        <v>78054</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8134,34 +8144,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>469160</v>
+        <v>468991</v>
       </c>
       <c r="R74" t="n">
-        <v>7065329</v>
+        <v>7065056</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8194,6 +8209,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8220,32 +8240,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129060047</v>
+        <v>129059677</v>
       </c>
       <c r="B75" t="n">
-        <v>91903</v>
+        <v>78054</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2063</v>
+        <v>228579</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8255,10 +8275,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>469012</v>
+        <v>469160</v>
       </c>
       <c r="R75" t="n">
-        <v>7065037</v>
+        <v>7065329</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8317,32 +8337,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129059698</v>
+        <v>129060047</v>
       </c>
       <c r="B76" t="n">
-        <v>80147</v>
+        <v>91912</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8352,10 +8372,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>469120</v>
+        <v>469012</v>
       </c>
       <c r="R76" t="n">
-        <v>7065078</v>
+        <v>7065037</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8398,21 +8418,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8429,10 +8434,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129059714</v>
+        <v>129059698</v>
       </c>
       <c r="B77" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8440,39 +8445,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>468946</v>
+        <v>469120</v>
       </c>
       <c r="R77" t="n">
-        <v>7064969</v>
+        <v>7065078</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8507,11 +8507,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8520,6 +8515,21 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -8536,10 +8546,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129059701</v>
+        <v>129060040</v>
       </c>
       <c r="B78" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8547,36 +8557,31 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>468991</v>
+        <v>469148</v>
       </c>
       <c r="R78" t="n">
         <v>7065056</v>
@@ -8612,11 +8617,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9273,7 +9273,7 @@
         <v>129059696</v>
       </c>
       <c r="B85" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129060037</v>
+        <v>129060022</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,27 +2047,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468874</v>
+        <v>468893</v>
       </c>
       <c r="R15" t="n">
-        <v>7064975</v>
+        <v>7065289</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,6 +2112,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2138,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129060022</v>
+        <v>129060045</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,39 +2154,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468893</v>
+        <v>469013</v>
       </c>
       <c r="R16" t="n">
-        <v>7065289</v>
+        <v>7065018</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,11 +2214,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2245,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129060045</v>
+        <v>129060037</v>
       </c>
       <c r="B17" t="n">
-        <v>80146</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,34 +2251,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>469013</v>
+        <v>468874</v>
       </c>
       <c r="R17" t="n">
-        <v>7065018</v>
+        <v>7064975</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129060038</v>
+        <v>129059708</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>83012</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,39 +2353,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>1467</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469007</v>
+        <v>468783</v>
       </c>
       <c r="R18" t="n">
-        <v>7064930</v>
+        <v>7065001</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2428,6 +2423,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2444,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129059708</v>
+        <v>129060003</v>
       </c>
       <c r="B19" t="n">
-        <v>83012</v>
+        <v>91540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2455,21 +2465,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2479,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468783</v>
+        <v>469006</v>
       </c>
       <c r="R19" t="n">
-        <v>7065001</v>
+        <v>7065358</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2525,21 +2535,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2556,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129060039</v>
+        <v>129060007</v>
       </c>
       <c r="B20" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2567,34 +2562,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469139</v>
+        <v>469364</v>
       </c>
       <c r="R20" t="n">
-        <v>7065094</v>
+        <v>7065232</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2627,6 +2627,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2653,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129059695</v>
+        <v>129059685</v>
       </c>
       <c r="B21" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2664,34 +2669,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469141</v>
+        <v>468878</v>
       </c>
       <c r="R21" t="n">
-        <v>7065114</v>
+        <v>7065401</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2726,6 +2736,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2734,21 +2749,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2765,10 +2765,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129060003</v>
+        <v>129060038</v>
       </c>
       <c r="B22" t="n">
-        <v>91540</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2776,34 +2776,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469006</v>
+        <v>469007</v>
       </c>
       <c r="R22" t="n">
-        <v>7065358</v>
+        <v>7064930</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2862,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129060007</v>
+        <v>129060039</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2873,39 +2878,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469364</v>
+        <v>469139</v>
       </c>
       <c r="R23" t="n">
-        <v>7065232</v>
+        <v>7065094</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2938,11 +2938,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2969,10 +2964,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129059685</v>
+        <v>129059695</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2980,39 +2975,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>468878</v>
+        <v>469141</v>
       </c>
       <c r="R24" t="n">
-        <v>7065401</v>
+        <v>7065114</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3047,11 +3037,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3060,6 +3045,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3290,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129060027</v>
+        <v>129060046</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>91536</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3301,39 +3301,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>468896</v>
+        <v>469215</v>
       </c>
       <c r="R27" t="n">
-        <v>7064986</v>
+        <v>7065278</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3366,11 +3361,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3397,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129060046</v>
+        <v>129060048</v>
       </c>
       <c r="B28" t="n">
-        <v>91536</v>
+        <v>91560</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3408,23 +3398,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3432,10 +3418,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469215</v>
+        <v>469135</v>
       </c>
       <c r="R28" t="n">
-        <v>7065278</v>
+        <v>7065166</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3494,45 +3480,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129060006</v>
+        <v>129060027</v>
       </c>
       <c r="B29" t="n">
-        <v>92257</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469045</v>
+        <v>468896</v>
       </c>
       <c r="R29" t="n">
-        <v>7065011</v>
+        <v>7064986</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3565,6 +3556,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3591,10 +3587,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129060048</v>
+        <v>129060035</v>
       </c>
       <c r="B30" t="n">
-        <v>91558</v>
+        <v>57887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3602,34 +3598,43 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469135</v>
+        <v>469149</v>
       </c>
       <c r="R30" t="n">
-        <v>7065166</v>
+        <v>7065169</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3688,54 +3693,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129060035</v>
+        <v>129060006</v>
       </c>
       <c r="B31" t="n">
-        <v>57887</v>
+        <v>92258</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469149</v>
+        <v>469045</v>
       </c>
       <c r="R31" t="n">
-        <v>7065169</v>
+        <v>7065011</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3794,10 +3790,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129059691</v>
+        <v>129059681</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3805,34 +3801,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468992</v>
+        <v>469043</v>
       </c>
       <c r="R32" t="n">
-        <v>7065224</v>
+        <v>7065365</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3865,6 +3866,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3891,32 +3897,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129059690</v>
+        <v>129059691</v>
       </c>
       <c r="B33" t="n">
-        <v>83005</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3926,10 +3932,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>468887</v>
+        <v>468992</v>
       </c>
       <c r="R33" t="n">
-        <v>7065318</v>
+        <v>7065224</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3988,50 +3994,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129059681</v>
+        <v>129059690</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>83005</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>469043</v>
+        <v>468887</v>
       </c>
       <c r="R34" t="n">
-        <v>7065365</v>
+        <v>7065318</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4064,11 +4065,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4095,10 +4091,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129060009</v>
+        <v>129059694</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>82999</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4106,39 +4102,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>469298</v>
+        <v>469141</v>
       </c>
       <c r="R35" t="n">
-        <v>7065235</v>
+        <v>7065114</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4173,11 +4164,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4186,6 +4172,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälgticka</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Phellinopsis conchata</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4314,10 +4315,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129059694</v>
+        <v>129060009</v>
       </c>
       <c r="B37" t="n">
-        <v>82999</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4325,34 +4326,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>469141</v>
+        <v>469298</v>
       </c>
       <c r="R37" t="n">
-        <v>7065114</v>
+        <v>7065235</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4387,6 +4393,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4395,21 +4406,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälgticka</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Phellinopsis conchata</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5038,10 +5034,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129060049</v>
+        <v>129059703</v>
       </c>
       <c r="B44" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,21 +5045,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5073,10 +5069,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>469012</v>
+        <v>468883</v>
       </c>
       <c r="R44" t="n">
-        <v>7065037</v>
+        <v>7065026</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5135,7 +5131,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129059703</v>
+        <v>129059699</v>
       </c>
       <c r="B45" t="n">
         <v>79041</v>
@@ -5170,10 +5166,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>468883</v>
+        <v>469071</v>
       </c>
       <c r="R45" t="n">
-        <v>7065026</v>
+        <v>7065075</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5232,10 +5228,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129059699</v>
+        <v>129060049</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5243,23 +5239,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5267,10 +5259,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469071</v>
+        <v>469012</v>
       </c>
       <c r="R46" t="n">
-        <v>7065075</v>
+        <v>7065037</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6175,10 +6167,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129060036</v>
+        <v>129060041</v>
       </c>
       <c r="B55" t="n">
-        <v>57887</v>
+        <v>80147</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6186,39 +6178,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>468801</v>
+        <v>469143</v>
       </c>
       <c r="R55" t="n">
-        <v>7065038</v>
+        <v>7065030</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6277,10 +6264,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129060041</v>
+        <v>129060036</v>
       </c>
       <c r="B56" t="n">
-        <v>80147</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6288,34 +6275,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>469143</v>
+        <v>468801</v>
       </c>
       <c r="R56" t="n">
-        <v>7065030</v>
+        <v>7065038</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6374,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129060005</v>
+        <v>129059693</v>
       </c>
       <c r="B57" t="n">
-        <v>91540</v>
+        <v>91560</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6385,23 +6377,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6409,10 +6397,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>468821</v>
+        <v>469137</v>
       </c>
       <c r="R57" t="n">
-        <v>7065043</v>
+        <v>7065120</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6471,10 +6459,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129059693</v>
+        <v>129060032</v>
       </c>
       <c r="B58" t="n">
-        <v>91558</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6482,34 +6470,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>469137</v>
+        <v>469043</v>
       </c>
       <c r="R58" t="n">
-        <v>7065120</v>
+        <v>7064905</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6542,6 +6535,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6568,10 +6566,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129060032</v>
+        <v>129060005</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6579,39 +6577,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>469043</v>
+        <v>468821</v>
       </c>
       <c r="R59" t="n">
-        <v>7064905</v>
+        <v>7065043</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6644,11 +6637,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6675,10 +6663,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129059675</v>
+        <v>129059686</v>
       </c>
       <c r="B60" t="n">
-        <v>91536</v>
+        <v>83002</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6686,21 +6674,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>310</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6710,10 +6698,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>469197</v>
+        <v>468843</v>
       </c>
       <c r="R60" t="n">
-        <v>7065308</v>
+        <v>7065390</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6756,6 +6744,21 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6772,10 +6775,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129059686</v>
+        <v>129059674</v>
       </c>
       <c r="B61" t="n">
-        <v>83002</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6783,21 +6786,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6807,10 +6810,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468843</v>
+        <v>469226</v>
       </c>
       <c r="R61" t="n">
-        <v>7065390</v>
+        <v>7065299</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6853,21 +6856,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6884,32 +6872,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129059674</v>
+        <v>129060043</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>75031</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6919,10 +6907,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>469226</v>
+        <v>469011</v>
       </c>
       <c r="R62" t="n">
-        <v>7065299</v>
+        <v>7065022</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6981,32 +6969,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129060043</v>
+        <v>129060050</v>
       </c>
       <c r="B63" t="n">
-        <v>75031</v>
+        <v>79041</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7016,10 +7004,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>469011</v>
+        <v>469118</v>
       </c>
       <c r="R63" t="n">
-        <v>7065022</v>
+        <v>7065190</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7052,6 +7040,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7078,10 +7071,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129060050</v>
+        <v>129059675</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>91536</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7089,21 +7082,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7113,10 +7106,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>469118</v>
+        <v>469197</v>
       </c>
       <c r="R64" t="n">
-        <v>7065190</v>
+        <v>7065308</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7149,11 +7142,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7613,10 +7601,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129059670</v>
+        <v>129059682</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7624,39 +7612,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>469326</v>
+        <v>468990</v>
       </c>
       <c r="R69" t="n">
-        <v>7065255</v>
+        <v>7065370</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7689,11 +7672,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7720,10 +7698,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129059682</v>
+        <v>129059670</v>
       </c>
       <c r="B70" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7731,34 +7709,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468990</v>
+        <v>469326</v>
       </c>
       <c r="R70" t="n">
-        <v>7065370</v>
+        <v>7065255</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7791,6 +7774,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7817,10 +7805,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129060051</v>
+        <v>129060011</v>
       </c>
       <c r="B71" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7828,34 +7816,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>469121</v>
+        <v>469245</v>
       </c>
       <c r="R71" t="n">
-        <v>7064885</v>
+        <v>7065256</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7892,7 +7885,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Med apotechier</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7919,10 +7912,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129060011</v>
+        <v>129060051</v>
       </c>
       <c r="B72" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7930,39 +7923,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>469245</v>
+        <v>469121</v>
       </c>
       <c r="R72" t="n">
-        <v>7065256</v>
+        <v>7064885</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7999,7 +7987,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8026,10 +8014,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129059714</v>
+        <v>129059677</v>
       </c>
       <c r="B73" t="n">
-        <v>57727</v>
+        <v>78054</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8037,39 +8025,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>468946</v>
+        <v>469160</v>
       </c>
       <c r="R73" t="n">
-        <v>7064969</v>
+        <v>7065329</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8102,11 +8085,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8133,7 +8111,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129059701</v>
+        <v>129059714</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -8173,10 +8151,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>468991</v>
+        <v>468946</v>
       </c>
       <c r="R74" t="n">
-        <v>7065056</v>
+        <v>7064969</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8240,10 +8218,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129059677</v>
+        <v>129059701</v>
       </c>
       <c r="B75" t="n">
-        <v>78054</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8251,34 +8229,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>469160</v>
+        <v>468991</v>
       </c>
       <c r="R75" t="n">
-        <v>7065329</v>
+        <v>7065056</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8311,6 +8294,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8340,7 +8328,7 @@
         <v>129060047</v>
       </c>
       <c r="B76" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8964,10 +8952,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129059676</v>
+        <v>129059706</v>
       </c>
       <c r="B82" t="n">
-        <v>83007</v>
+        <v>80147</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8975,21 +8963,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8999,10 +8987,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>469160</v>
+        <v>468850</v>
       </c>
       <c r="R82" t="n">
-        <v>7065329</v>
+        <v>7065034</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9045,6 +9033,21 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9061,10 +9064,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129059712</v>
+        <v>129059676</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>83007</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9072,21 +9075,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9096,10 +9099,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>468868</v>
+        <v>469160</v>
       </c>
       <c r="R83" t="n">
-        <v>7064989</v>
+        <v>7065329</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9158,10 +9161,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129059706</v>
+        <v>129059712</v>
       </c>
       <c r="B84" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9169,21 +9172,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9193,10 +9196,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>468850</v>
+        <v>468868</v>
       </c>
       <c r="R84" t="n">
-        <v>7065034</v>
+        <v>7064989</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9239,21 +9242,6 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -9273,7 +9261,7 @@
         <v>129059696</v>
       </c>
       <c r="B85" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9290,14 +9278,10 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129059710</v>
+        <v>129060012</v>
       </c>
       <c r="B2" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468844</v>
+        <v>469235</v>
       </c>
       <c r="R2" t="n">
-        <v>7064978</v>
+        <v>7065256</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,6 +753,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -756,21 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129059689</v>
+        <v>129060023</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468887</v>
+        <v>469142</v>
       </c>
       <c r="R3" t="n">
-        <v>7065318</v>
+        <v>7065079</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129059683</v>
+        <v>129060033</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468964</v>
+        <v>469047</v>
       </c>
       <c r="R4" t="n">
-        <v>7065331</v>
+        <v>7064905</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129060044</v>
+        <v>129060008</v>
       </c>
       <c r="B5" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469111</v>
+        <v>469327</v>
       </c>
       <c r="R5" t="n">
-        <v>7065086</v>
+        <v>7065224</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129059711</v>
+        <v>129060020</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468844</v>
+        <v>468803</v>
       </c>
       <c r="R6" t="n">
-        <v>7064978</v>
+        <v>7065369</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,6 +1181,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1159,21 +1194,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1190,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129060012</v>
+        <v>129060024</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1221,7 +1241,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1230,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469235</v>
+        <v>469131</v>
       </c>
       <c r="R7" t="n">
-        <v>7065256</v>
+        <v>7065083</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129060023</v>
+        <v>129059710</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,39 +1328,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469142</v>
+        <v>468844</v>
       </c>
       <c r="R8" t="n">
-        <v>7065079</v>
+        <v>7064978</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1375,11 +1390,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1388,6 +1398,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1404,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129060033</v>
+        <v>129059689</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,39 +1440,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469047</v>
+        <v>468887</v>
       </c>
       <c r="R9" t="n">
-        <v>7064905</v>
+        <v>7065318</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,11 +1500,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129060008</v>
+        <v>129059683</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,39 +1537,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469327</v>
+        <v>468964</v>
       </c>
       <c r="R10" t="n">
-        <v>7065224</v>
+        <v>7065331</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129060020</v>
+        <v>129060044</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,39 +1634,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468803</v>
+        <v>469111</v>
       </c>
       <c r="R11" t="n">
-        <v>7065369</v>
+        <v>7065086</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,11 +1694,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129060024</v>
+        <v>129059711</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,39 +1731,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469131</v>
+        <v>468844</v>
       </c>
       <c r="R12" t="n">
-        <v>7065083</v>
+        <v>7064978</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1803,11 +1793,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1816,6 +1801,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129059678</v>
+        <v>129060015</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,34 +1843,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469160</v>
+        <v>469142</v>
       </c>
       <c r="R13" t="n">
-        <v>7065329</v>
+        <v>7065300</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,6 +1908,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129060015</v>
+        <v>129059678</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1940,39 +1950,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469142</v>
+        <v>469160</v>
       </c>
       <c r="R14" t="n">
-        <v>7065300</v>
+        <v>7065329</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,11 +2010,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129060022</v>
+        <v>129060045</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,39 +2047,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468893</v>
+        <v>469013</v>
       </c>
       <c r="R15" t="n">
-        <v>7065289</v>
+        <v>7065018</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,11 +2107,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2143,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129060045</v>
+        <v>129060022</v>
       </c>
       <c r="B16" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2154,34 +2144,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469013</v>
+        <v>468893</v>
       </c>
       <c r="R16" t="n">
-        <v>7065018</v>
+        <v>7065289</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,6 +2209,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2454,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129060003</v>
+        <v>129060039</v>
       </c>
       <c r="B19" t="n">
-        <v>91540</v>
+        <v>80147</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,21 +2465,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469006</v>
+        <v>469139</v>
       </c>
       <c r="R19" t="n">
-        <v>7065358</v>
+        <v>7065094</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2551,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129060007</v>
+        <v>129060003</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,39 +2562,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469364</v>
+        <v>469006</v>
       </c>
       <c r="R20" t="n">
-        <v>7065232</v>
+        <v>7065358</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2627,11 +2622,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2658,7 +2648,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129059685</v>
+        <v>129060007</v>
       </c>
       <c r="B21" t="n">
         <v>57727</v>
@@ -2698,10 +2688,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468878</v>
+        <v>469364</v>
       </c>
       <c r="R21" t="n">
-        <v>7065401</v>
+        <v>7065232</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,10 +2755,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129060038</v>
+        <v>129059685</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2776,27 +2766,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2805,10 +2795,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469007</v>
+        <v>468878</v>
       </c>
       <c r="R22" t="n">
-        <v>7064930</v>
+        <v>7065401</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2841,6 +2831,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2867,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129060039</v>
+        <v>129059695</v>
       </c>
       <c r="B23" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2878,21 +2873,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2902,10 +2897,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469139</v>
+        <v>469141</v>
       </c>
       <c r="R23" t="n">
-        <v>7065094</v>
+        <v>7065114</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,6 +2943,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -2964,10 +2974,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129059695</v>
+        <v>129060038</v>
       </c>
       <c r="B24" t="n">
-        <v>80146</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2975,34 +2985,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469141</v>
+        <v>469007</v>
       </c>
       <c r="R24" t="n">
-        <v>7065114</v>
+        <v>7064930</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,21 +3060,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3480,50 +3480,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129060027</v>
+        <v>129060006</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>92258</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>468896</v>
+        <v>469045</v>
       </c>
       <c r="R29" t="n">
-        <v>7064986</v>
+        <v>7065011</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,11 +3551,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3587,10 +3577,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129060035</v>
+        <v>129060027</v>
       </c>
       <c r="B30" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3598,31 +3588,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3631,10 +3617,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469149</v>
+        <v>468896</v>
       </c>
       <c r="R30" t="n">
-        <v>7065169</v>
+        <v>7064986</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3667,6 +3653,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3693,45 +3684,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129060006</v>
+        <v>129060035</v>
       </c>
       <c r="B31" t="n">
-        <v>92258</v>
+        <v>57887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469045</v>
+        <v>469149</v>
       </c>
       <c r="R31" t="n">
-        <v>7065011</v>
+        <v>7065169</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4091,10 +4091,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129059694</v>
+        <v>129059700</v>
       </c>
       <c r="B35" t="n">
-        <v>82999</v>
+        <v>80147</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4102,21 +4102,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>469141</v>
+        <v>469036</v>
       </c>
       <c r="R35" t="n">
-        <v>7065114</v>
+        <v>7065082</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4175,17 +4175,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälgticka</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Phellinopsis conchata</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4203,10 +4203,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129059700</v>
+        <v>129060009</v>
       </c>
       <c r="B36" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4214,34 +4214,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>469036</v>
+        <v>469298</v>
       </c>
       <c r="R36" t="n">
-        <v>7065082</v>
+        <v>7065235</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4276,6 +4281,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4284,21 +4294,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4315,10 +4310,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129060009</v>
+        <v>129059694</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>82999</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4326,39 +4321,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>469298</v>
+        <v>469141</v>
       </c>
       <c r="R37" t="n">
-        <v>7065235</v>
+        <v>7065114</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4393,11 +4383,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4406,6 +4391,21 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälgticka</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Phellinopsis conchata</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4519,45 +4519,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129060001</v>
+        <v>129059684</v>
       </c>
       <c r="B39" t="n">
-        <v>91504</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468967</v>
+        <v>468895</v>
       </c>
       <c r="R39" t="n">
-        <v>7065256</v>
+        <v>7065399</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4590,6 +4595,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4616,7 +4626,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129059684</v>
+        <v>129060026</v>
       </c>
       <c r="B40" t="n">
         <v>57727</v>
@@ -4656,10 +4666,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>468895</v>
+        <v>468886</v>
       </c>
       <c r="R40" t="n">
-        <v>7065399</v>
+        <v>7065015</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4723,7 +4733,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129060026</v>
+        <v>129059715</v>
       </c>
       <c r="B41" t="n">
         <v>57727</v>
@@ -4763,10 +4773,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468886</v>
+        <v>469047</v>
       </c>
       <c r="R41" t="n">
-        <v>7065015</v>
+        <v>7064912</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4830,50 +4840,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129059715</v>
+        <v>129060001</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>91504</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469047</v>
+        <v>468967</v>
       </c>
       <c r="R42" t="n">
-        <v>7064912</v>
+        <v>7065256</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4906,11 +4911,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5535,10 +5535,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129059702</v>
+        <v>129059709</v>
       </c>
       <c r="B49" t="n">
-        <v>91540</v>
+        <v>83002</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5546,21 +5546,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>310</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>468889</v>
+        <v>468844</v>
       </c>
       <c r="R49" t="n">
-        <v>7065025</v>
+        <v>7064978</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5616,6 +5616,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5632,10 +5647,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129059709</v>
+        <v>129059702</v>
       </c>
       <c r="B50" t="n">
-        <v>83002</v>
+        <v>91540</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5643,21 +5658,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>310</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5667,10 +5682,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>468844</v>
+        <v>468889</v>
       </c>
       <c r="R50" t="n">
-        <v>7064978</v>
+        <v>7065025</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5713,21 +5728,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5744,50 +5744,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129059704</v>
+        <v>129060042</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>80050</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>468883</v>
+        <v>469356</v>
       </c>
       <c r="R51" t="n">
-        <v>7065026</v>
+        <v>7065233</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5820,11 +5815,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5851,10 +5841,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129060031</v>
+        <v>129059697</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5862,39 +5852,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>469014</v>
+        <v>469114</v>
       </c>
       <c r="R52" t="n">
-        <v>7064913</v>
+        <v>7065083</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5929,11 +5914,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5942,6 +5922,21 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -5958,45 +5953,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129060042</v>
+        <v>129059704</v>
       </c>
       <c r="B53" t="n">
-        <v>80050</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>469356</v>
+        <v>468883</v>
       </c>
       <c r="R53" t="n">
-        <v>7065233</v>
+        <v>7065026</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6029,6 +6029,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6055,10 +6060,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129059697</v>
+        <v>129060031</v>
       </c>
       <c r="B54" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6066,34 +6071,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>469114</v>
+        <v>469014</v>
       </c>
       <c r="R54" t="n">
-        <v>7065083</v>
+        <v>7064913</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6128,6 +6138,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6136,21 +6151,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6366,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129059693</v>
+        <v>129060005</v>
       </c>
       <c r="B57" t="n">
-        <v>91560</v>
+        <v>91540</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6377,19 +6377,23 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6397,10 +6401,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>469137</v>
+        <v>468821</v>
       </c>
       <c r="R57" t="n">
-        <v>7065120</v>
+        <v>7065043</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6459,10 +6463,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129060032</v>
+        <v>129059693</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>91560</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6470,39 +6474,30 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>469043</v>
+        <v>469137</v>
       </c>
       <c r="R58" t="n">
-        <v>7064905</v>
+        <v>7065120</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6535,11 +6530,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6566,10 +6556,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129060005</v>
+        <v>129060032</v>
       </c>
       <c r="B59" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6577,34 +6567,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>468821</v>
+        <v>469043</v>
       </c>
       <c r="R59" t="n">
-        <v>7065043</v>
+        <v>7064905</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6637,6 +6632,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6775,10 +6775,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129059674</v>
+        <v>129059687</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6786,21 +6786,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>469226</v>
+        <v>468843</v>
       </c>
       <c r="R61" t="n">
-        <v>7065299</v>
+        <v>7065390</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6856,6 +6856,21 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6872,32 +6887,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129060043</v>
+        <v>129059675</v>
       </c>
       <c r="B62" t="n">
-        <v>75031</v>
+        <v>91536</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6428</v>
+        <v>1108</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6907,10 +6922,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>469011</v>
+        <v>469197</v>
       </c>
       <c r="R62" t="n">
-        <v>7065022</v>
+        <v>7065308</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6969,10 +6984,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129060050</v>
+        <v>129060029</v>
       </c>
       <c r="B63" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6980,34 +6995,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>469118</v>
+        <v>468970</v>
       </c>
       <c r="R63" t="n">
-        <v>7065190</v>
+        <v>7064946</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7044,7 +7064,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7071,10 +7091,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129059675</v>
+        <v>129060021</v>
       </c>
       <c r="B64" t="n">
-        <v>91536</v>
+        <v>57727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7082,34 +7102,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>469197</v>
+        <v>468788</v>
       </c>
       <c r="R64" t="n">
-        <v>7065308</v>
+        <v>7065344</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7142,6 +7167,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7168,10 +7198,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129059687</v>
+        <v>129060025</v>
       </c>
       <c r="B65" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7179,34 +7209,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>468843</v>
+        <v>469101</v>
       </c>
       <c r="R65" t="n">
-        <v>7065390</v>
+        <v>7065026</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7241,6 +7276,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7249,21 +7289,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7280,10 +7305,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129060029</v>
+        <v>129059674</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7291,39 +7316,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468970</v>
+        <v>469226</v>
       </c>
       <c r="R66" t="n">
-        <v>7064946</v>
+        <v>7065299</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7356,11 +7376,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7387,50 +7402,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129060021</v>
+        <v>129060043</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>75031</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468788</v>
+        <v>469011</v>
       </c>
       <c r="R67" t="n">
-        <v>7065344</v>
+        <v>7065022</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7463,11 +7473,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7494,10 +7499,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129060025</v>
+        <v>129060050</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7505,39 +7510,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>469101</v>
+        <v>469118</v>
       </c>
       <c r="R68" t="n">
-        <v>7065026</v>
+        <v>7065190</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7601,10 +7601,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129059682</v>
+        <v>129059670</v>
       </c>
       <c r="B69" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7612,34 +7612,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>468990</v>
+        <v>469326</v>
       </c>
       <c r="R69" t="n">
-        <v>7065370</v>
+        <v>7065255</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7672,6 +7677,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7698,10 +7708,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129059670</v>
+        <v>129059682</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7709,39 +7719,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>469326</v>
+        <v>468990</v>
       </c>
       <c r="R70" t="n">
-        <v>7065255</v>
+        <v>7065370</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7774,11 +7779,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8014,32 +8014,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129059677</v>
+        <v>129060047</v>
       </c>
       <c r="B73" t="n">
-        <v>78054</v>
+        <v>91913</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228579</v>
+        <v>2063</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8049,10 +8049,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>469160</v>
+        <v>469012</v>
       </c>
       <c r="R73" t="n">
-        <v>7065329</v>
+        <v>7065037</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8111,10 +8111,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129059714</v>
+        <v>129059698</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8122,39 +8122,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>468946</v>
+        <v>469120</v>
       </c>
       <c r="R74" t="n">
-        <v>7064969</v>
+        <v>7065078</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8189,11 +8184,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8202,6 +8192,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8218,10 +8223,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129059701</v>
+        <v>129060040</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8229,36 +8234,31 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>468991</v>
+        <v>469148</v>
       </c>
       <c r="R75" t="n">
         <v>7065056</v>
@@ -8294,11 +8294,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8325,32 +8320,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129060047</v>
+        <v>129059677</v>
       </c>
       <c r="B76" t="n">
-        <v>91913</v>
+        <v>78054</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2063</v>
+        <v>228579</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8360,10 +8355,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>469012</v>
+        <v>469160</v>
       </c>
       <c r="R76" t="n">
-        <v>7065037</v>
+        <v>7065329</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8422,10 +8417,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129059698</v>
+        <v>129059714</v>
       </c>
       <c r="B77" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8433,34 +8428,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>469120</v>
+        <v>468946</v>
       </c>
       <c r="R77" t="n">
-        <v>7065078</v>
+        <v>7064969</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8495,6 +8495,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8503,21 +8508,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -8534,10 +8524,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129060040</v>
+        <v>129059701</v>
       </c>
       <c r="B78" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8545,31 +8535,36 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>469148</v>
+        <v>468991</v>
       </c>
       <c r="R78" t="n">
         <v>7065056</v>
@@ -8605,6 +8600,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8952,10 +8952,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129059706</v>
+        <v>129059696</v>
       </c>
       <c r="B82" t="n">
-        <v>80147</v>
+        <v>91560</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8963,23 +8963,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -8987,10 +8983,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>468850</v>
+        <v>469141</v>
       </c>
       <c r="R82" t="n">
-        <v>7065034</v>
+        <v>7065095</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9033,21 +9029,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9064,10 +9045,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129059676</v>
+        <v>129059679</v>
       </c>
       <c r="B83" t="n">
-        <v>83007</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9075,34 +9056,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>469160</v>
+        <v>469108</v>
       </c>
       <c r="R83" t="n">
-        <v>7065329</v>
+        <v>7065364</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9135,6 +9121,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9161,10 +9152,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129059712</v>
+        <v>129059713</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9172,34 +9163,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>468868</v>
+        <v>468922</v>
       </c>
       <c r="R84" t="n">
-        <v>7064989</v>
+        <v>7064998</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9232,6 +9228,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9258,10 +9259,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129059696</v>
+        <v>129059692</v>
       </c>
       <c r="B85" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9269,30 +9270,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>469141</v>
+        <v>469137</v>
       </c>
       <c r="R85" t="n">
-        <v>7065095</v>
+        <v>7065206</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9325,6 +9335,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9351,10 +9366,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129059679</v>
+        <v>129059706</v>
       </c>
       <c r="B86" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9362,39 +9377,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>469108</v>
+        <v>468850</v>
       </c>
       <c r="R86" t="n">
-        <v>7065364</v>
+        <v>7065034</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9429,11 +9439,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9442,6 +9447,21 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -9458,10 +9478,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129059713</v>
+        <v>129059676</v>
       </c>
       <c r="B87" t="n">
-        <v>57727</v>
+        <v>83007</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9469,39 +9489,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>468922</v>
+        <v>469160</v>
       </c>
       <c r="R87" t="n">
-        <v>7064998</v>
+        <v>7065329</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9534,11 +9549,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9565,10 +9575,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129059692</v>
+        <v>129059712</v>
       </c>
       <c r="B88" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9576,39 +9586,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>469137</v>
+        <v>468868</v>
       </c>
       <c r="R88" t="n">
-        <v>7065206</v>
+        <v>7064989</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9641,11 +9646,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129060012</v>
+        <v>129059710</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469235</v>
+        <v>468844</v>
       </c>
       <c r="R2" t="n">
-        <v>7065256</v>
+        <v>7064978</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,11 +748,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -766,6 +756,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129060023</v>
+        <v>129060012</v>
       </c>
       <c r="B3" t="n">
         <v>57727</v>
@@ -813,7 +818,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469142</v>
+        <v>469235</v>
       </c>
       <c r="R3" t="n">
-        <v>7065079</v>
+        <v>7065256</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129060033</v>
+        <v>129060023</v>
       </c>
       <c r="B4" t="n">
         <v>57727</v>
@@ -929,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469047</v>
+        <v>469142</v>
       </c>
       <c r="R4" t="n">
-        <v>7064905</v>
+        <v>7065079</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129060008</v>
+        <v>129060033</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1036,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469327</v>
+        <v>469047</v>
       </c>
       <c r="R5" t="n">
-        <v>7065224</v>
+        <v>7064905</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129060020</v>
+        <v>129060008</v>
       </c>
       <c r="B6" t="n">
         <v>57727</v>
@@ -1134,7 +1139,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1143,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468803</v>
+        <v>469327</v>
       </c>
       <c r="R6" t="n">
-        <v>7065369</v>
+        <v>7065224</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129060024</v>
+        <v>129060020</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1241,7 +1246,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1250,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469131</v>
+        <v>468803</v>
       </c>
       <c r="R7" t="n">
-        <v>7065083</v>
+        <v>7065369</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129059710</v>
+        <v>129060024</v>
       </c>
       <c r="B8" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,34 +1333,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468844</v>
+        <v>469131</v>
       </c>
       <c r="R8" t="n">
-        <v>7064978</v>
+        <v>7065083</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,6 +1400,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1398,21 +1413,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1432,7 +1432,7 @@
         <v>129059689</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>129059683</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>129060044</v>
       </c>
       <c r="B11" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>129059711</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129060015</v>
+        <v>129059678</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,39 +1843,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469142</v>
+        <v>469160</v>
       </c>
       <c r="R13" t="n">
-        <v>7065300</v>
+        <v>7065329</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,11 +1903,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129059678</v>
+        <v>129060015</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1950,34 +1940,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469160</v>
+        <v>469142</v>
       </c>
       <c r="R14" t="n">
-        <v>7065329</v>
+        <v>7065300</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,6 +2005,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2039,7 +2039,7 @@
         <v>129060045</v>
       </c>
       <c r="B15" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129059708</v>
+        <v>129059695</v>
       </c>
       <c r="B18" t="n">
-        <v>83012</v>
+        <v>80148</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1467</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468783</v>
+        <v>469141</v>
       </c>
       <c r="R18" t="n">
-        <v>7065001</v>
+        <v>7065114</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2426,17 +2426,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129060039</v>
+        <v>129059708</v>
       </c>
       <c r="B19" t="n">
-        <v>80147</v>
+        <v>83016</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,21 +2465,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469139</v>
+        <v>468783</v>
       </c>
       <c r="R19" t="n">
-        <v>7065094</v>
+        <v>7065001</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,6 +2535,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2551,10 +2566,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129060003</v>
+        <v>129060039</v>
       </c>
       <c r="B20" t="n">
-        <v>91540</v>
+        <v>80149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,21 +2577,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2586,10 +2601,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469006</v>
+        <v>469139</v>
       </c>
       <c r="R20" t="n">
-        <v>7065358</v>
+        <v>7065094</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2648,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129060007</v>
+        <v>129060003</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>91543</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2659,39 +2674,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469364</v>
+        <v>469006</v>
       </c>
       <c r="R21" t="n">
-        <v>7065232</v>
+        <v>7065358</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,11 +2734,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2755,7 +2760,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129059685</v>
+        <v>129060007</v>
       </c>
       <c r="B22" t="n">
         <v>57727</v>
@@ -2795,10 +2800,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468878</v>
+        <v>469364</v>
       </c>
       <c r="R22" t="n">
-        <v>7065401</v>
+        <v>7065232</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2862,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129059695</v>
+        <v>129059685</v>
       </c>
       <c r="B23" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2873,34 +2878,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469141</v>
+        <v>468878</v>
       </c>
       <c r="R23" t="n">
-        <v>7065114</v>
+        <v>7065401</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2935,6 +2945,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2943,21 +2958,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3293,7 +3293,7 @@
         <v>129060046</v>
       </c>
       <c r="B27" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3387,30 +3387,34 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129060048</v>
+        <v>129060006</v>
       </c>
       <c r="B28" t="n">
-        <v>91560</v>
+        <v>92261</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3418,10 +3422,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469135</v>
+        <v>469045</v>
       </c>
       <c r="R28" t="n">
-        <v>7065166</v>
+        <v>7065011</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3480,45 +3484,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129060006</v>
+        <v>129060027</v>
       </c>
       <c r="B29" t="n">
-        <v>92258</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469045</v>
+        <v>468896</v>
       </c>
       <c r="R29" t="n">
-        <v>7065011</v>
+        <v>7064986</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,6 +3560,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3577,10 +3591,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129060027</v>
+        <v>129060035</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3588,27 +3602,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3617,10 +3635,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>468896</v>
+        <v>469149</v>
       </c>
       <c r="R30" t="n">
-        <v>7064986</v>
+        <v>7065169</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3653,11 +3671,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3684,10 +3697,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129060035</v>
+        <v>129060048</v>
       </c>
       <c r="B31" t="n">
-        <v>57887</v>
+        <v>91563</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3695,43 +3708,30 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469149</v>
+        <v>469135</v>
       </c>
       <c r="R31" t="n">
-        <v>7065169</v>
+        <v>7065166</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3900,7 +3900,7 @@
         <v>129059691</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>129059690</v>
       </c>
       <c r="B34" t="n">
-        <v>83005</v>
+        <v>83009</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4091,10 +4091,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129059700</v>
+        <v>129059694</v>
       </c>
       <c r="B35" t="n">
-        <v>80147</v>
+        <v>83003</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4102,21 +4102,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>469036</v>
+        <v>469141</v>
       </c>
       <c r="R35" t="n">
-        <v>7065082</v>
+        <v>7065114</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4175,17 +4175,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>sälgticka</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Phellinopsis conchata</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4310,10 +4310,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129059694</v>
+        <v>129059700</v>
       </c>
       <c r="B37" t="n">
-        <v>82999</v>
+        <v>80149</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4321,21 +4321,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>469141</v>
+        <v>469036</v>
       </c>
       <c r="R37" t="n">
-        <v>7065114</v>
+        <v>7065082</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4394,17 +4394,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälgticka</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Phellinopsis conchata</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4425,7 +4425,7 @@
         <v>129060002</v>
       </c>
       <c r="B38" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>129060001</v>
       </c>
       <c r="B42" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>129059671</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>129059703</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5131,10 +5131,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129059699</v>
+        <v>129060049</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>91563</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5142,23 +5142,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5166,10 +5162,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>469071</v>
+        <v>469012</v>
       </c>
       <c r="R45" t="n">
-        <v>7065075</v>
+        <v>7065037</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5228,10 +5224,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129060049</v>
+        <v>129059699</v>
       </c>
       <c r="B46" t="n">
-        <v>91560</v>
+        <v>79043</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5239,19 +5235,23 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469012</v>
+        <v>469071</v>
       </c>
       <c r="R46" t="n">
-        <v>7065037</v>
+        <v>7065075</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5535,10 +5535,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129059709</v>
+        <v>129059702</v>
       </c>
       <c r="B49" t="n">
-        <v>83002</v>
+        <v>91543</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5546,21 +5546,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>310</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>468844</v>
+        <v>468889</v>
       </c>
       <c r="R49" t="n">
-        <v>7064978</v>
+        <v>7065025</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5616,21 +5616,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5647,32 +5632,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129059702</v>
+        <v>129060042</v>
       </c>
       <c r="B50" t="n">
-        <v>91540</v>
+        <v>80052</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5682,10 +5667,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>468889</v>
+        <v>469356</v>
       </c>
       <c r="R50" t="n">
-        <v>7065025</v>
+        <v>7065233</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5744,32 +5729,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129060042</v>
+        <v>129059697</v>
       </c>
       <c r="B51" t="n">
-        <v>80050</v>
+        <v>80148</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5779,10 +5764,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>469356</v>
+        <v>469114</v>
       </c>
       <c r="R51" t="n">
-        <v>7065233</v>
+        <v>7065083</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5825,6 +5810,21 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -5841,10 +5841,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129059697</v>
+        <v>129059709</v>
       </c>
       <c r="B52" t="n">
-        <v>80146</v>
+        <v>83006</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>310</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>469114</v>
+        <v>468844</v>
       </c>
       <c r="R52" t="n">
-        <v>7065083</v>
+        <v>7064978</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6167,10 +6167,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129060041</v>
+        <v>129060036</v>
       </c>
       <c r="B55" t="n">
-        <v>80147</v>
+        <v>57887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6178,34 +6178,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>469143</v>
+        <v>468801</v>
       </c>
       <c r="R55" t="n">
-        <v>7065030</v>
+        <v>7065038</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6264,10 +6269,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129060036</v>
+        <v>129060041</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>80149</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6275,39 +6280,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>468801</v>
+        <v>469143</v>
       </c>
       <c r="R56" t="n">
-        <v>7065038</v>
+        <v>7065030</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6369,7 +6369,7 @@
         <v>129060005</v>
       </c>
       <c r="B57" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6463,10 +6463,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129059693</v>
+        <v>129060032</v>
       </c>
       <c r="B58" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6474,30 +6474,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>469137</v>
+        <v>469043</v>
       </c>
       <c r="R58" t="n">
-        <v>7065120</v>
+        <v>7064905</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6530,6 +6539,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6556,10 +6570,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129060032</v>
+        <v>129059693</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>91563</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6567,39 +6581,30 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>469043</v>
+        <v>469137</v>
       </c>
       <c r="R59" t="n">
-        <v>7064905</v>
+        <v>7065120</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6632,11 +6637,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6663,10 +6663,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129059686</v>
+        <v>129059687</v>
       </c>
       <c r="B60" t="n">
-        <v>83002</v>
+        <v>80149</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6674,21 +6674,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>310</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6775,10 +6775,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129059687</v>
+        <v>129059675</v>
       </c>
       <c r="B61" t="n">
-        <v>80147</v>
+        <v>91539</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6786,21 +6786,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468843</v>
+        <v>469197</v>
       </c>
       <c r="R61" t="n">
-        <v>7065390</v>
+        <v>7065308</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6856,21 +6856,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6887,10 +6872,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129059675</v>
+        <v>129059674</v>
       </c>
       <c r="B62" t="n">
-        <v>91536</v>
+        <v>79043</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6898,21 +6883,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6922,10 +6907,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>469197</v>
+        <v>469226</v>
       </c>
       <c r="R62" t="n">
-        <v>7065308</v>
+        <v>7065299</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6984,50 +6969,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129060029</v>
+        <v>129060043</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>75033</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>468970</v>
+        <v>469011</v>
       </c>
       <c r="R63" t="n">
-        <v>7064946</v>
+        <v>7065022</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7060,11 +7040,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7091,10 +7066,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129060021</v>
+        <v>129060050</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7102,39 +7077,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>468788</v>
+        <v>469118</v>
       </c>
       <c r="R64" t="n">
-        <v>7065344</v>
+        <v>7065190</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7171,7 +7141,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7198,7 +7168,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129060025</v>
+        <v>129060029</v>
       </c>
       <c r="B65" t="n">
         <v>57727</v>
@@ -7238,10 +7208,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>469101</v>
+        <v>468970</v>
       </c>
       <c r="R65" t="n">
-        <v>7065026</v>
+        <v>7064946</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7305,10 +7275,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129059674</v>
+        <v>129060021</v>
       </c>
       <c r="B66" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7316,34 +7286,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>469226</v>
+        <v>468788</v>
       </c>
       <c r="R66" t="n">
-        <v>7065299</v>
+        <v>7065344</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7376,6 +7351,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7402,45 +7382,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129060043</v>
+        <v>129060025</v>
       </c>
       <c r="B67" t="n">
-        <v>75031</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>469011</v>
+        <v>469101</v>
       </c>
       <c r="R67" t="n">
-        <v>7065022</v>
+        <v>7065026</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7473,6 +7458,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7499,10 +7489,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129060050</v>
+        <v>129059686</v>
       </c>
       <c r="B68" t="n">
-        <v>79041</v>
+        <v>83006</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7510,21 +7500,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7534,10 +7524,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>469118</v>
+        <v>468843</v>
       </c>
       <c r="R68" t="n">
-        <v>7065190</v>
+        <v>7065390</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7572,11 +7562,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7585,6 +7570,21 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -7601,10 +7601,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129059670</v>
+        <v>129059682</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>91543</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7612,39 +7612,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>469326</v>
+        <v>468990</v>
       </c>
       <c r="R69" t="n">
-        <v>7065255</v>
+        <v>7065370</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7677,11 +7672,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7708,10 +7698,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129059682</v>
+        <v>129059670</v>
       </c>
       <c r="B70" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7719,34 +7709,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468990</v>
+        <v>469326</v>
       </c>
       <c r="R70" t="n">
-        <v>7065370</v>
+        <v>7065255</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7779,6 +7774,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7805,10 +7805,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129060011</v>
+        <v>129060051</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7816,39 +7816,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>469245</v>
+        <v>469121</v>
       </c>
       <c r="R71" t="n">
-        <v>7065256</v>
+        <v>7064885</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7885,7 +7880,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7912,10 +7907,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129060051</v>
+        <v>129060011</v>
       </c>
       <c r="B72" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7923,34 +7918,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>469121</v>
+        <v>469245</v>
       </c>
       <c r="R72" t="n">
-        <v>7064885</v>
+        <v>7065256</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Med apotechier</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8014,45 +8014,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129060047</v>
+        <v>129059714</v>
       </c>
       <c r="B73" t="n">
-        <v>91913</v>
+        <v>57727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>469012</v>
+        <v>468946</v>
       </c>
       <c r="R73" t="n">
-        <v>7065037</v>
+        <v>7064969</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8085,6 +8090,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8111,10 +8121,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129059698</v>
+        <v>129059701</v>
       </c>
       <c r="B74" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8122,34 +8132,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>469120</v>
+        <v>468991</v>
       </c>
       <c r="R74" t="n">
-        <v>7065078</v>
+        <v>7065056</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8184,6 +8199,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8192,21 +8212,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8223,10 +8228,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129060040</v>
+        <v>129059677</v>
       </c>
       <c r="B75" t="n">
-        <v>80147</v>
+        <v>78056</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8234,21 +8239,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8258,10 +8263,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>469148</v>
+        <v>469160</v>
       </c>
       <c r="R75" t="n">
-        <v>7065056</v>
+        <v>7065329</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8320,32 +8325,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129059677</v>
+        <v>129060047</v>
       </c>
       <c r="B76" t="n">
-        <v>78054</v>
+        <v>91916</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228579</v>
+        <v>2063</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8355,10 +8360,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>469160</v>
+        <v>469012</v>
       </c>
       <c r="R76" t="n">
-        <v>7065329</v>
+        <v>7065037</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8417,10 +8422,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129059714</v>
+        <v>129059698</v>
       </c>
       <c r="B77" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8428,39 +8433,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>468946</v>
+        <v>469120</v>
       </c>
       <c r="R77" t="n">
-        <v>7064969</v>
+        <v>7065078</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8495,11 +8495,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8508,6 +8503,21 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -8524,10 +8534,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129059701</v>
+        <v>129060040</v>
       </c>
       <c r="B78" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8535,36 +8545,31 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>468991</v>
+        <v>469148</v>
       </c>
       <c r="R78" t="n">
         <v>7065056</v>
@@ -8600,11 +8605,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8952,10 +8952,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129059696</v>
+        <v>129059706</v>
       </c>
       <c r="B82" t="n">
-        <v>91560</v>
+        <v>80149</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8963,19 +8963,23 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -8983,10 +8987,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>469141</v>
+        <v>468850</v>
       </c>
       <c r="R82" t="n">
-        <v>7065095</v>
+        <v>7065034</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9029,6 +9033,21 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9045,10 +9064,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129059679</v>
+        <v>129059696</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>91563</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9056,39 +9075,30 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>469108</v>
+        <v>469141</v>
       </c>
       <c r="R83" t="n">
-        <v>7065364</v>
+        <v>7065095</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9121,11 +9131,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9152,10 +9157,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129059713</v>
+        <v>129059676</v>
       </c>
       <c r="B84" t="n">
-        <v>57727</v>
+        <v>83011</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9163,39 +9168,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>468922</v>
+        <v>469160</v>
       </c>
       <c r="R84" t="n">
-        <v>7064998</v>
+        <v>7065329</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9228,11 +9228,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9259,10 +9254,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129059692</v>
+        <v>129059712</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9270,39 +9265,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>469137</v>
+        <v>468868</v>
       </c>
       <c r="R85" t="n">
-        <v>7065206</v>
+        <v>7064989</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9335,11 +9325,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9366,10 +9351,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129059706</v>
+        <v>129059679</v>
       </c>
       <c r="B86" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9377,34 +9362,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>468850</v>
+        <v>469108</v>
       </c>
       <c r="R86" t="n">
-        <v>7065034</v>
+        <v>7065364</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9439,6 +9429,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9447,21 +9442,6 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -9478,10 +9458,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129059676</v>
+        <v>129059713</v>
       </c>
       <c r="B87" t="n">
-        <v>83007</v>
+        <v>57727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9489,34 +9469,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>469160</v>
+        <v>468922</v>
       </c>
       <c r="R87" t="n">
-        <v>7065329</v>
+        <v>7064998</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9549,6 +9534,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9575,10 +9565,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129059712</v>
+        <v>129059692</v>
       </c>
       <c r="B88" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9586,34 +9576,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>468868</v>
+        <v>469137</v>
       </c>
       <c r="R88" t="n">
-        <v>7064989</v>
+        <v>7065206</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9646,6 +9641,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129059695</v>
+        <v>129059708</v>
       </c>
       <c r="B18" t="n">
-        <v>80148</v>
+        <v>83016</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1467</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469141</v>
+        <v>468783</v>
       </c>
       <c r="R18" t="n">
-        <v>7065114</v>
+        <v>7065001</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2426,17 +2426,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129059708</v>
+        <v>129060039</v>
       </c>
       <c r="B19" t="n">
-        <v>83016</v>
+        <v>80149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,21 +2465,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468783</v>
+        <v>469139</v>
       </c>
       <c r="R19" t="n">
-        <v>7065001</v>
+        <v>7065094</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,21 +2535,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2566,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129060039</v>
+        <v>129060003</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>91543</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,21 +2562,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2601,10 +2586,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469139</v>
+        <v>469006</v>
       </c>
       <c r="R20" t="n">
-        <v>7065094</v>
+        <v>7065358</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,10 +2648,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129060003</v>
+        <v>129060007</v>
       </c>
       <c r="B21" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,34 +2659,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469006</v>
+        <v>469364</v>
       </c>
       <c r="R21" t="n">
-        <v>7065358</v>
+        <v>7065232</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,6 +2724,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2760,7 +2755,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129060007</v>
+        <v>129059685</v>
       </c>
       <c r="B22" t="n">
         <v>57727</v>
@@ -2800,10 +2795,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469364</v>
+        <v>468878</v>
       </c>
       <c r="R22" t="n">
-        <v>7065232</v>
+        <v>7065401</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2867,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129059685</v>
+        <v>129060038</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2878,27 +2873,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2907,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468878</v>
+        <v>469007</v>
       </c>
       <c r="R23" t="n">
-        <v>7065401</v>
+        <v>7064930</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2943,11 +2938,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2974,10 +2964,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129060038</v>
+        <v>129059695</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>80148</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2985,39 +2975,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469007</v>
+        <v>469141</v>
       </c>
       <c r="R24" t="n">
-        <v>7064930</v>
+        <v>7065114</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3060,6 +3045,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3790,10 +3790,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129059681</v>
+        <v>129059691</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3801,39 +3801,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>469043</v>
+        <v>468992</v>
       </c>
       <c r="R32" t="n">
-        <v>7065365</v>
+        <v>7065224</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3866,11 +3861,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3897,32 +3887,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129059691</v>
+        <v>129059690</v>
       </c>
       <c r="B33" t="n">
-        <v>79043</v>
+        <v>83009</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3932,10 +3922,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>468992</v>
+        <v>468887</v>
       </c>
       <c r="R33" t="n">
-        <v>7065224</v>
+        <v>7065318</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3994,45 +3984,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129059690</v>
+        <v>129059681</v>
       </c>
       <c r="B34" t="n">
-        <v>83009</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>468887</v>
+        <v>469043</v>
       </c>
       <c r="R34" t="n">
-        <v>7065318</v>
+        <v>7065365</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4065,6 +4060,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5034,10 +5034,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129059703</v>
+        <v>129060049</v>
       </c>
       <c r="B44" t="n">
-        <v>79043</v>
+        <v>91563</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5045,23 +5045,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5069,10 +5065,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>468883</v>
+        <v>469012</v>
       </c>
       <c r="R44" t="n">
-        <v>7065026</v>
+        <v>7065037</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5131,10 +5127,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129060049</v>
+        <v>129059703</v>
       </c>
       <c r="B45" t="n">
-        <v>91563</v>
+        <v>79043</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5142,19 +5138,23 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5162,10 +5162,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>469012</v>
+        <v>468883</v>
       </c>
       <c r="R45" t="n">
-        <v>7065037</v>
+        <v>7065026</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5632,32 +5632,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129060042</v>
+        <v>129059709</v>
       </c>
       <c r="B50" t="n">
-        <v>80052</v>
+        <v>83006</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6456</v>
+        <v>310</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5667,10 +5667,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>469356</v>
+        <v>468844</v>
       </c>
       <c r="R50" t="n">
-        <v>7065233</v>
+        <v>7064978</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5713,6 +5713,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5729,32 +5744,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129059697</v>
+        <v>129060042</v>
       </c>
       <c r="B51" t="n">
-        <v>80148</v>
+        <v>80052</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5764,10 +5779,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>469114</v>
+        <v>469356</v>
       </c>
       <c r="R51" t="n">
-        <v>7065083</v>
+        <v>7065233</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5810,21 +5825,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -5841,10 +5841,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129059709</v>
+        <v>129059697</v>
       </c>
       <c r="B52" t="n">
-        <v>83006</v>
+        <v>80148</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>310</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>468844</v>
+        <v>469114</v>
       </c>
       <c r="R52" t="n">
-        <v>7064978</v>
+        <v>7065083</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6167,10 +6167,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129060036</v>
+        <v>129060041</v>
       </c>
       <c r="B55" t="n">
-        <v>57887</v>
+        <v>80149</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6178,39 +6178,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>468801</v>
+        <v>469143</v>
       </c>
       <c r="R55" t="n">
-        <v>7065038</v>
+        <v>7065030</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6269,10 +6264,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129060041</v>
+        <v>129060036</v>
       </c>
       <c r="B56" t="n">
-        <v>80149</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6280,34 +6275,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>469143</v>
+        <v>468801</v>
       </c>
       <c r="R56" t="n">
-        <v>7065030</v>
+        <v>7065038</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129059710</v>
       </c>
       <c r="B2" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>129059689</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>129059683</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>129060044</v>
       </c>
       <c r="B11" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>129059711</v>
       </c>
       <c r="B12" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129059678</v>
+        <v>129060015</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,34 +1843,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469160</v>
+        <v>469142</v>
       </c>
       <c r="R13" t="n">
-        <v>7065329</v>
+        <v>7065300</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,6 +1908,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129060015</v>
+        <v>129059678</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1940,39 +1950,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469142</v>
+        <v>469160</v>
       </c>
       <c r="R14" t="n">
-        <v>7065300</v>
+        <v>7065329</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,11 +2010,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129060045</v>
+        <v>129060037</v>
       </c>
       <c r="B15" t="n">
-        <v>80148</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,34 +2047,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469013</v>
+        <v>468874</v>
       </c>
       <c r="R15" t="n">
-        <v>7065018</v>
+        <v>7064975</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2240,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129060037</v>
+        <v>129060045</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>80149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,39 +2256,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468874</v>
+        <v>469013</v>
       </c>
       <c r="R17" t="n">
-        <v>7064975</v>
+        <v>7065018</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
         <v>129059708</v>
       </c>
       <c r="B18" t="n">
-        <v>83016</v>
+        <v>83017</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>129060039</v>
       </c>
       <c r="B19" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2551,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129060003</v>
+        <v>129060038</v>
       </c>
       <c r="B20" t="n">
-        <v>91543</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,34 +2562,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469006</v>
+        <v>469007</v>
       </c>
       <c r="R20" t="n">
-        <v>7065358</v>
+        <v>7064930</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2648,10 +2653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129060007</v>
+        <v>129060003</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>91545</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2659,39 +2664,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469364</v>
+        <v>469006</v>
       </c>
       <c r="R21" t="n">
-        <v>7065232</v>
+        <v>7065358</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,11 +2724,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2755,7 +2750,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129059685</v>
+        <v>129060007</v>
       </c>
       <c r="B22" t="n">
         <v>57727</v>
@@ -2795,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468878</v>
+        <v>469364</v>
       </c>
       <c r="R22" t="n">
-        <v>7065401</v>
+        <v>7065232</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2862,10 +2857,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129060038</v>
+        <v>129059685</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2873,27 +2868,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2902,10 +2897,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469007</v>
+        <v>468878</v>
       </c>
       <c r="R23" t="n">
-        <v>7064930</v>
+        <v>7065401</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2938,6 +2933,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2967,7 +2967,7 @@
         <v>129059695</v>
       </c>
       <c r="B24" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129060046</v>
+        <v>129060048</v>
       </c>
       <c r="B27" t="n">
-        <v>91539</v>
+        <v>91565</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3301,23 +3301,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3325,10 +3321,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469215</v>
+        <v>469135</v>
       </c>
       <c r="R27" t="n">
-        <v>7065278</v>
+        <v>7065166</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3387,32 +3383,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129060006</v>
+        <v>129060046</v>
       </c>
       <c r="B28" t="n">
-        <v>92261</v>
+        <v>91541</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3422,10 +3418,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469045</v>
+        <v>469215</v>
       </c>
       <c r="R28" t="n">
-        <v>7065011</v>
+        <v>7065278</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3591,54 +3587,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129060035</v>
+        <v>129060006</v>
       </c>
       <c r="B30" t="n">
-        <v>57887</v>
+        <v>92263</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469149</v>
+        <v>469045</v>
       </c>
       <c r="R30" t="n">
-        <v>7065169</v>
+        <v>7065011</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3697,10 +3684,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129060048</v>
+        <v>129060035</v>
       </c>
       <c r="B31" t="n">
-        <v>91563</v>
+        <v>57887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3708,30 +3695,43 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469135</v>
+        <v>469149</v>
       </c>
       <c r="R31" t="n">
-        <v>7065166</v>
+        <v>7065169</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3790,10 +3790,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129059691</v>
+        <v>129059681</v>
       </c>
       <c r="B32" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3801,34 +3801,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468992</v>
+        <v>469043</v>
       </c>
       <c r="R32" t="n">
-        <v>7065224</v>
+        <v>7065365</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3861,6 +3866,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3887,32 +3897,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129059690</v>
+        <v>129059691</v>
       </c>
       <c r="B33" t="n">
-        <v>83009</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3922,10 +3932,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>468887</v>
+        <v>468992</v>
       </c>
       <c r="R33" t="n">
-        <v>7065318</v>
+        <v>7065224</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3984,50 +3994,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129059681</v>
+        <v>129059690</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>83010</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>469043</v>
+        <v>468887</v>
       </c>
       <c r="R34" t="n">
-        <v>7065365</v>
+        <v>7065318</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4060,11 +4065,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4091,10 +4091,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129059694</v>
+        <v>129060009</v>
       </c>
       <c r="B35" t="n">
-        <v>83003</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4102,34 +4102,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>469141</v>
+        <v>469298</v>
       </c>
       <c r="R35" t="n">
-        <v>7065114</v>
+        <v>7065235</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4164,6 +4169,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4172,21 +4182,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>sälgticka</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Phellinopsis conchata</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4203,10 +4198,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129060009</v>
+        <v>129059700</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4214,39 +4209,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>469298</v>
+        <v>469036</v>
       </c>
       <c r="R36" t="n">
-        <v>7065235</v>
+        <v>7065082</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4281,11 +4271,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4294,6 +4279,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4310,10 +4310,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129059700</v>
+        <v>129059694</v>
       </c>
       <c r="B37" t="n">
-        <v>80149</v>
+        <v>83004</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4321,21 +4321,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>469036</v>
+        <v>469141</v>
       </c>
       <c r="R37" t="n">
-        <v>7065082</v>
+        <v>7065114</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4394,17 +4394,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>sälgticka</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Phellinopsis conchata</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4422,10 +4422,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129060002</v>
+        <v>129059684</v>
       </c>
       <c r="B38" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4433,34 +4433,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>469031</v>
+        <v>468895</v>
       </c>
       <c r="R38" t="n">
-        <v>7065017</v>
+        <v>7065399</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4493,6 +4498,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4519,7 +4529,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129059684</v>
+        <v>129060026</v>
       </c>
       <c r="B39" t="n">
         <v>57727</v>
@@ -4559,10 +4569,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468895</v>
+        <v>468886</v>
       </c>
       <c r="R39" t="n">
-        <v>7065399</v>
+        <v>7065015</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4626,7 +4636,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129060026</v>
+        <v>129059715</v>
       </c>
       <c r="B40" t="n">
         <v>57727</v>
@@ -4666,10 +4676,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>468886</v>
+        <v>469047</v>
       </c>
       <c r="R40" t="n">
-        <v>7065015</v>
+        <v>7064912</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4733,50 +4743,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129059715</v>
+        <v>129060001</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>91509</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>469047</v>
+        <v>468967</v>
       </c>
       <c r="R41" t="n">
-        <v>7064912</v>
+        <v>7065256</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4809,11 +4814,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4840,32 +4840,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129060001</v>
+        <v>129060002</v>
       </c>
       <c r="B42" t="n">
-        <v>91507</v>
+        <v>91545</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>468967</v>
+        <v>469031</v>
       </c>
       <c r="R42" t="n">
-        <v>7065256</v>
+        <v>7065017</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4940,7 +4940,7 @@
         <v>129059671</v>
       </c>
       <c r="B43" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5034,10 +5034,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129060049</v>
+        <v>129059703</v>
       </c>
       <c r="B44" t="n">
-        <v>91563</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5045,19 +5045,23 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5065,10 +5069,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>469012</v>
+        <v>468883</v>
       </c>
       <c r="R44" t="n">
-        <v>7065037</v>
+        <v>7065026</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5127,10 +5131,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129059703</v>
+        <v>129059699</v>
       </c>
       <c r="B45" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5162,10 +5166,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>468883</v>
+        <v>469071</v>
       </c>
       <c r="R45" t="n">
-        <v>7065026</v>
+        <v>7065075</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5224,10 +5228,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129059699</v>
+        <v>129060018</v>
       </c>
       <c r="B46" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5235,34 +5239,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469071</v>
+        <v>469093</v>
       </c>
       <c r="R46" t="n">
-        <v>7065075</v>
+        <v>7065345</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5295,6 +5304,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5321,7 +5335,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129060018</v>
+        <v>129060017</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5361,10 +5375,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>469093</v>
+        <v>469122</v>
       </c>
       <c r="R47" t="n">
-        <v>7065345</v>
+        <v>7065303</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5428,10 +5442,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129060017</v>
+        <v>129060049</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>91565</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5439,39 +5453,30 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>469122</v>
+        <v>469012</v>
       </c>
       <c r="R48" t="n">
-        <v>7065303</v>
+        <v>7065037</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5504,11 +5509,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5535,10 +5535,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129059702</v>
+        <v>129059697</v>
       </c>
       <c r="B49" t="n">
-        <v>91543</v>
+        <v>80149</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5546,21 +5546,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>468889</v>
+        <v>469114</v>
       </c>
       <c r="R49" t="n">
-        <v>7065025</v>
+        <v>7065083</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5616,6 +5616,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5632,32 +5647,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129059709</v>
+        <v>129060042</v>
       </c>
       <c r="B50" t="n">
-        <v>83006</v>
+        <v>80053</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>310</v>
+        <v>6456</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5667,10 +5682,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>468844</v>
+        <v>469356</v>
       </c>
       <c r="R50" t="n">
-        <v>7064978</v>
+        <v>7065233</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5713,21 +5728,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5744,32 +5744,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129060042</v>
+        <v>129059702</v>
       </c>
       <c r="B51" t="n">
-        <v>80052</v>
+        <v>91545</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>469356</v>
+        <v>468889</v>
       </c>
       <c r="R51" t="n">
-        <v>7065233</v>
+        <v>7065025</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129059697</v>
+        <v>129059709</v>
       </c>
       <c r="B52" t="n">
-        <v>80148</v>
+        <v>83007</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>310</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>469114</v>
+        <v>468844</v>
       </c>
       <c r="R52" t="n">
-        <v>7065083</v>
+        <v>7064978</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6167,10 +6167,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129060041</v>
+        <v>129060036</v>
       </c>
       <c r="B55" t="n">
-        <v>80149</v>
+        <v>57887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6178,34 +6178,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>469143</v>
+        <v>468801</v>
       </c>
       <c r="R55" t="n">
-        <v>7065030</v>
+        <v>7065038</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6264,10 +6269,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129060036</v>
+        <v>129060041</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>80150</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6275,39 +6280,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>468801</v>
+        <v>469143</v>
       </c>
       <c r="R56" t="n">
-        <v>7065038</v>
+        <v>7065030</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6366,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129060005</v>
+        <v>129059693</v>
       </c>
       <c r="B57" t="n">
-        <v>91543</v>
+        <v>91565</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6377,23 +6377,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6401,10 +6397,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>468821</v>
+        <v>469137</v>
       </c>
       <c r="R57" t="n">
-        <v>7065043</v>
+        <v>7065120</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6463,10 +6459,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129060032</v>
+        <v>129060005</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>91545</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6474,39 +6470,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>469043</v>
+        <v>468821</v>
       </c>
       <c r="R58" t="n">
-        <v>7064905</v>
+        <v>7065043</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6539,11 +6530,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6570,10 +6556,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129059693</v>
+        <v>129060032</v>
       </c>
       <c r="B59" t="n">
-        <v>91563</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6581,30 +6567,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>469137</v>
+        <v>469043</v>
       </c>
       <c r="R59" t="n">
-        <v>7065120</v>
+        <v>7064905</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6637,6 +6632,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6666,7 +6666,7 @@
         <v>129059687</v>
       </c>
       <c r="B60" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6775,10 +6775,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129059675</v>
+        <v>129059674</v>
       </c>
       <c r="B61" t="n">
-        <v>91539</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6786,21 +6786,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>469197</v>
+        <v>469226</v>
       </c>
       <c r="R61" t="n">
-        <v>7065308</v>
+        <v>7065299</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6872,32 +6872,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129059674</v>
+        <v>129060043</v>
       </c>
       <c r="B62" t="n">
-        <v>79043</v>
+        <v>75033</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>469226</v>
+        <v>469011</v>
       </c>
       <c r="R62" t="n">
-        <v>7065299</v>
+        <v>7065022</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6969,32 +6969,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129060043</v>
+        <v>129060050</v>
       </c>
       <c r="B63" t="n">
-        <v>75033</v>
+        <v>79044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7004,10 +7004,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>469011</v>
+        <v>469118</v>
       </c>
       <c r="R63" t="n">
-        <v>7065022</v>
+        <v>7065190</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7040,6 +7040,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7066,10 +7071,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129060050</v>
+        <v>129059675</v>
       </c>
       <c r="B64" t="n">
-        <v>79043</v>
+        <v>91541</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7077,21 +7082,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7101,10 +7106,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>469118</v>
+        <v>469197</v>
       </c>
       <c r="R64" t="n">
-        <v>7065190</v>
+        <v>7065308</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7137,11 +7142,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7168,10 +7168,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129060029</v>
+        <v>129059686</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>83007</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7179,39 +7179,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>310</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>468970</v>
+        <v>468843</v>
       </c>
       <c r="R65" t="n">
-        <v>7064946</v>
+        <v>7065390</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7246,11 +7241,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7259,6 +7249,21 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7275,7 +7280,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129060021</v>
+        <v>129060029</v>
       </c>
       <c r="B66" t="n">
         <v>57727</v>
@@ -7306,7 +7311,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7315,10 +7320,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468788</v>
+        <v>468970</v>
       </c>
       <c r="R66" t="n">
-        <v>7065344</v>
+        <v>7064946</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7382,7 +7387,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129060025</v>
+        <v>129060021</v>
       </c>
       <c r="B67" t="n">
         <v>57727</v>
@@ -7413,7 +7418,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7422,10 +7427,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>469101</v>
+        <v>468788</v>
       </c>
       <c r="R67" t="n">
-        <v>7065026</v>
+        <v>7065344</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7489,10 +7494,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129059686</v>
+        <v>129060025</v>
       </c>
       <c r="B68" t="n">
-        <v>83006</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7500,34 +7505,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>468843</v>
+        <v>469101</v>
       </c>
       <c r="R68" t="n">
-        <v>7065390</v>
+        <v>7065026</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7562,6 +7572,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7570,21 +7585,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -7601,10 +7601,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129059682</v>
+        <v>129059670</v>
       </c>
       <c r="B69" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7612,34 +7612,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>468990</v>
+        <v>469326</v>
       </c>
       <c r="R69" t="n">
-        <v>7065370</v>
+        <v>7065255</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7672,6 +7677,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7698,10 +7708,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129059670</v>
+        <v>129059682</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>91545</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7709,39 +7719,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>469326</v>
+        <v>468990</v>
       </c>
       <c r="R70" t="n">
-        <v>7065255</v>
+        <v>7065370</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7774,11 +7779,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7805,10 +7805,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129060051</v>
+        <v>129060011</v>
       </c>
       <c r="B71" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7816,34 +7816,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>469121</v>
+        <v>469245</v>
       </c>
       <c r="R71" t="n">
-        <v>7064885</v>
+        <v>7065256</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7880,7 +7885,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Med apotechier</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7907,10 +7912,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129060011</v>
+        <v>129060051</v>
       </c>
       <c r="B72" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7918,39 +7923,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>469245</v>
+        <v>469121</v>
       </c>
       <c r="R72" t="n">
-        <v>7065256</v>
+        <v>7064885</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8014,10 +8014,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129059714</v>
+        <v>129059677</v>
       </c>
       <c r="B73" t="n">
-        <v>57727</v>
+        <v>78057</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8025,39 +8025,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>468946</v>
+        <v>469160</v>
       </c>
       <c r="R73" t="n">
-        <v>7064969</v>
+        <v>7065329</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8090,11 +8085,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8121,50 +8111,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129059701</v>
+        <v>129060047</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>91918</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>468991</v>
+        <v>469012</v>
       </c>
       <c r="R74" t="n">
-        <v>7065056</v>
+        <v>7065037</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8197,11 +8182,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8228,10 +8208,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129059677</v>
+        <v>129059698</v>
       </c>
       <c r="B75" t="n">
-        <v>78056</v>
+        <v>80150</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8239,21 +8219,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8263,10 +8243,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>469160</v>
+        <v>469120</v>
       </c>
       <c r="R75" t="n">
-        <v>7065329</v>
+        <v>7065078</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8309,6 +8289,21 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8325,32 +8320,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129060047</v>
+        <v>129060040</v>
       </c>
       <c r="B76" t="n">
-        <v>91916</v>
+        <v>80150</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2063</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8360,10 +8355,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>469012</v>
+        <v>469148</v>
       </c>
       <c r="R76" t="n">
-        <v>7065037</v>
+        <v>7065056</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8422,10 +8417,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129059698</v>
+        <v>129059714</v>
       </c>
       <c r="B77" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8433,34 +8428,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>469120</v>
+        <v>468946</v>
       </c>
       <c r="R77" t="n">
-        <v>7065078</v>
+        <v>7064969</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8495,6 +8495,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8503,21 +8508,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -8534,10 +8524,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129060040</v>
+        <v>129059701</v>
       </c>
       <c r="B78" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8545,31 +8535,36 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>469148</v>
+        <v>468991</v>
       </c>
       <c r="R78" t="n">
         <v>7065056</v>
@@ -8605,6 +8600,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8952,10 +8952,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129059706</v>
+        <v>129059679</v>
       </c>
       <c r="B82" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8963,34 +8963,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>468850</v>
+        <v>469108</v>
       </c>
       <c r="R82" t="n">
-        <v>7065034</v>
+        <v>7065364</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9025,6 +9030,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9033,21 +9043,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9064,10 +9059,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129059696</v>
+        <v>129059713</v>
       </c>
       <c r="B83" t="n">
-        <v>91563</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9075,30 +9070,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>469141</v>
+        <v>468922</v>
       </c>
       <c r="R83" t="n">
-        <v>7065095</v>
+        <v>7064998</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9131,6 +9135,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9157,10 +9166,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129059676</v>
+        <v>129059692</v>
       </c>
       <c r="B84" t="n">
-        <v>83011</v>
+        <v>57727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9168,34 +9177,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>469160</v>
+        <v>469137</v>
       </c>
       <c r="R84" t="n">
-        <v>7065329</v>
+        <v>7065206</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9228,6 +9242,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9254,10 +9273,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129059712</v>
+        <v>129059706</v>
       </c>
       <c r="B85" t="n">
-        <v>79043</v>
+        <v>80150</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9265,21 +9284,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9289,10 +9308,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>468868</v>
+        <v>468850</v>
       </c>
       <c r="R85" t="n">
-        <v>7064989</v>
+        <v>7065034</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9335,6 +9354,21 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -9351,10 +9385,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129059679</v>
+        <v>129059696</v>
       </c>
       <c r="B86" t="n">
-        <v>57727</v>
+        <v>91565</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9362,39 +9396,30 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>469108</v>
+        <v>469141</v>
       </c>
       <c r="R86" t="n">
-        <v>7065364</v>
+        <v>7065095</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9427,11 +9452,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9458,10 +9478,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129059713</v>
+        <v>129059676</v>
       </c>
       <c r="B87" t="n">
-        <v>57727</v>
+        <v>83012</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9469,39 +9489,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>468922</v>
+        <v>469160</v>
       </c>
       <c r="R87" t="n">
-        <v>7064998</v>
+        <v>7065329</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9534,11 +9549,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9565,10 +9575,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129059692</v>
+        <v>129059712</v>
       </c>
       <c r="B88" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9576,39 +9586,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>469137</v>
+        <v>468868</v>
       </c>
       <c r="R88" t="n">
-        <v>7065206</v>
+        <v>7064989</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9641,11 +9646,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129059710</v>
+        <v>129059689</v>
       </c>
       <c r="B2" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468844</v>
+        <v>468887</v>
       </c>
       <c r="R2" t="n">
-        <v>7064978</v>
+        <v>7065318</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,21 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129060012</v>
+        <v>129060044</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469235</v>
+        <v>469111</v>
       </c>
       <c r="R3" t="n">
-        <v>7065256</v>
+        <v>7065086</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129060023</v>
+        <v>129059711</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,39 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469142</v>
+        <v>468844</v>
       </c>
       <c r="R4" t="n">
-        <v>7065079</v>
+        <v>7064978</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,11 +942,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -985,6 +950,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1001,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129060033</v>
+        <v>129060012</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1032,7 +1012,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1041,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469047</v>
+        <v>469235</v>
       </c>
       <c r="R5" t="n">
-        <v>7064905</v>
+        <v>7065256</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129060008</v>
+        <v>129060023</v>
       </c>
       <c r="B6" t="n">
         <v>57727</v>
@@ -1148,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469327</v>
+        <v>469142</v>
       </c>
       <c r="R6" t="n">
-        <v>7065224</v>
+        <v>7065079</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129060020</v>
+        <v>129060033</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1246,7 +1226,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1255,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468803</v>
+        <v>469047</v>
       </c>
       <c r="R7" t="n">
-        <v>7065369</v>
+        <v>7064905</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129060024</v>
+        <v>129060008</v>
       </c>
       <c r="B8" t="n">
         <v>57727</v>
@@ -1362,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469131</v>
+        <v>469327</v>
       </c>
       <c r="R8" t="n">
-        <v>7065083</v>
+        <v>7065224</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129059689</v>
+        <v>129060020</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,34 +1420,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468887</v>
+        <v>468803</v>
       </c>
       <c r="R9" t="n">
-        <v>7065318</v>
+        <v>7065369</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129059683</v>
+        <v>129060024</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1537,34 +1527,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468964</v>
+        <v>469131</v>
       </c>
       <c r="R10" t="n">
-        <v>7065331</v>
+        <v>7065083</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1592,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129060044</v>
+        <v>129059683</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1634,21 +1634,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469111</v>
+        <v>468964</v>
       </c>
       <c r="R11" t="n">
-        <v>7065086</v>
+        <v>7065331</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129059711</v>
+        <v>129059710</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129060015</v>
+        <v>129059678</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,39 +1843,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469142</v>
+        <v>469160</v>
       </c>
       <c r="R13" t="n">
-        <v>7065300</v>
+        <v>7065329</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,11 +1903,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129059678</v>
+        <v>129060015</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1950,34 +1940,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469160</v>
+        <v>469142</v>
       </c>
       <c r="R14" t="n">
-        <v>7065329</v>
+        <v>7065300</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,6 +2005,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129060037</v>
+        <v>129060045</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>80149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,39 +2047,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468874</v>
+        <v>469013</v>
       </c>
       <c r="R15" t="n">
-        <v>7064975</v>
+        <v>7065018</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129060045</v>
+        <v>129060037</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,34 +2251,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>469013</v>
+        <v>468874</v>
       </c>
       <c r="R17" t="n">
-        <v>7065018</v>
+        <v>7064975</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129059708</v>
+        <v>129060039</v>
       </c>
       <c r="B18" t="n">
-        <v>83017</v>
+        <v>80150</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468783</v>
+        <v>469139</v>
       </c>
       <c r="R18" t="n">
-        <v>7065001</v>
+        <v>7065094</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2423,21 +2423,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2454,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129060039</v>
+        <v>129059695</v>
       </c>
       <c r="B19" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,21 +2450,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469139</v>
+        <v>469141</v>
       </c>
       <c r="R19" t="n">
-        <v>7065094</v>
+        <v>7065114</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,6 +2520,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2551,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129060038</v>
+        <v>129059708</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>83017</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,39 +2562,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469007</v>
+        <v>468783</v>
       </c>
       <c r="R20" t="n">
-        <v>7064930</v>
+        <v>7065001</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,6 +2632,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2656,7 +2666,7 @@
         <v>129060003</v>
       </c>
       <c r="B21" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,10 +2974,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129059695</v>
+        <v>129060038</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2975,34 +2985,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469141</v>
+        <v>469007</v>
       </c>
       <c r="R24" t="n">
-        <v>7065114</v>
+        <v>7064930</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,21 +3060,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3290,30 +3290,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129060048</v>
+        <v>129060006</v>
       </c>
       <c r="B27" t="n">
-        <v>91565</v>
+        <v>92267</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3321,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469135</v>
+        <v>469045</v>
       </c>
       <c r="R27" t="n">
-        <v>7065166</v>
+        <v>7065011</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3383,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129060046</v>
+        <v>129060048</v>
       </c>
       <c r="B28" t="n">
-        <v>91541</v>
+        <v>91569</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3394,23 +3398,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3418,10 +3418,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469215</v>
+        <v>469135</v>
       </c>
       <c r="R28" t="n">
-        <v>7065278</v>
+        <v>7065166</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3480,10 +3480,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129060027</v>
+        <v>129060046</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>91545</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3491,39 +3491,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>468896</v>
+        <v>469215</v>
       </c>
       <c r="R29" t="n">
-        <v>7064986</v>
+        <v>7065278</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,11 +3551,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3587,45 +3577,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129060006</v>
+        <v>129060027</v>
       </c>
       <c r="B30" t="n">
-        <v>92263</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469045</v>
+        <v>468896</v>
       </c>
       <c r="R30" t="n">
-        <v>7065011</v>
+        <v>7064986</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3658,6 +3653,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3790,50 +3790,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129059681</v>
+        <v>129059690</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>83010</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>469043</v>
+        <v>468887</v>
       </c>
       <c r="R32" t="n">
-        <v>7065365</v>
+        <v>7065318</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3866,11 +3861,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3994,45 +3984,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129059690</v>
+        <v>129059681</v>
       </c>
       <c r="B34" t="n">
-        <v>83010</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>468887</v>
+        <v>469043</v>
       </c>
       <c r="R34" t="n">
-        <v>7065318</v>
+        <v>7065365</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4065,6 +4060,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4091,10 +4091,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129060009</v>
+        <v>129059700</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4102,39 +4102,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>469298</v>
+        <v>469036</v>
       </c>
       <c r="R35" t="n">
-        <v>7065235</v>
+        <v>7065082</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4169,11 +4164,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4182,6 +4172,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4198,10 +4203,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129059700</v>
+        <v>129059694</v>
       </c>
       <c r="B36" t="n">
-        <v>80150</v>
+        <v>83004</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4209,21 +4214,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4233,10 +4238,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>469036</v>
+        <v>469141</v>
       </c>
       <c r="R36" t="n">
-        <v>7065082</v>
+        <v>7065114</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4282,17 +4287,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>sälgticka</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Phellinopsis conchata</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4310,10 +4315,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129059694</v>
+        <v>129060009</v>
       </c>
       <c r="B37" t="n">
-        <v>83004</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4321,34 +4326,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>469141</v>
+        <v>469298</v>
       </c>
       <c r="R37" t="n">
-        <v>7065114</v>
+        <v>7065235</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4383,6 +4393,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4391,21 +4406,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälgticka</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Phellinopsis conchata</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4422,10 +4422,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129059684</v>
+        <v>129060002</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4433,39 +4433,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>468895</v>
+        <v>469031</v>
       </c>
       <c r="R38" t="n">
-        <v>7065399</v>
+        <v>7065017</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4498,11 +4493,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4529,50 +4519,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129060026</v>
+        <v>129060001</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91513</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468886</v>
+        <v>468967</v>
       </c>
       <c r="R39" t="n">
-        <v>7065015</v>
+        <v>7065256</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4605,11 +4590,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4636,7 +4616,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129059715</v>
+        <v>129059684</v>
       </c>
       <c r="B40" t="n">
         <v>57727</v>
@@ -4676,10 +4656,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>469047</v>
+        <v>468895</v>
       </c>
       <c r="R40" t="n">
-        <v>7064912</v>
+        <v>7065399</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4743,45 +4723,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129060001</v>
+        <v>129060026</v>
       </c>
       <c r="B41" t="n">
-        <v>91509</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468967</v>
+        <v>468886</v>
       </c>
       <c r="R41" t="n">
-        <v>7065256</v>
+        <v>7065015</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4814,6 +4799,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4840,10 +4830,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129060002</v>
+        <v>129059715</v>
       </c>
       <c r="B42" t="n">
-        <v>91545</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4851,34 +4841,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469031</v>
+        <v>469047</v>
       </c>
       <c r="R42" t="n">
-        <v>7065017</v>
+        <v>7064912</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4911,6 +4906,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5034,10 +5034,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129059703</v>
+        <v>129060018</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5045,34 +5045,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>468883</v>
+        <v>469093</v>
       </c>
       <c r="R44" t="n">
-        <v>7065026</v>
+        <v>7065345</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5105,6 +5110,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5131,10 +5141,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129059699</v>
+        <v>129060017</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5142,34 +5152,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>469071</v>
+        <v>469122</v>
       </c>
       <c r="R45" t="n">
-        <v>7065075</v>
+        <v>7065303</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5202,6 +5217,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5228,10 +5248,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129060018</v>
+        <v>129060049</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>91569</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5239,39 +5259,30 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469093</v>
+        <v>469012</v>
       </c>
       <c r="R46" t="n">
-        <v>7065345</v>
+        <v>7065037</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5304,11 +5315,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5335,10 +5341,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129060017</v>
+        <v>129059699</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5346,39 +5352,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>469122</v>
+        <v>469071</v>
       </c>
       <c r="R47" t="n">
-        <v>7065303</v>
+        <v>7065075</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5411,11 +5412,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5442,10 +5438,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129060049</v>
+        <v>129059703</v>
       </c>
       <c r="B48" t="n">
-        <v>91565</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5453,19 +5449,23 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>469012</v>
+        <v>468883</v>
       </c>
       <c r="R48" t="n">
-        <v>7065037</v>
+        <v>7065026</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5535,10 +5535,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129059697</v>
+        <v>129059709</v>
       </c>
       <c r="B49" t="n">
-        <v>80149</v>
+        <v>83007</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5546,21 +5546,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>310</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>469114</v>
+        <v>468844</v>
       </c>
       <c r="R49" t="n">
-        <v>7065083</v>
+        <v>7064978</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5747,7 +5747,7 @@
         <v>129059702</v>
       </c>
       <c r="B51" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129059709</v>
+        <v>129059697</v>
       </c>
       <c r="B52" t="n">
-        <v>83007</v>
+        <v>80149</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>310</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>468844</v>
+        <v>469114</v>
       </c>
       <c r="R52" t="n">
-        <v>7064978</v>
+        <v>7065083</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6366,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129059693</v>
+        <v>129060005</v>
       </c>
       <c r="B57" t="n">
-        <v>91565</v>
+        <v>91549</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6377,19 +6377,23 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6397,10 +6401,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>469137</v>
+        <v>468821</v>
       </c>
       <c r="R57" t="n">
-        <v>7065120</v>
+        <v>7065043</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6459,10 +6463,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129060005</v>
+        <v>129059693</v>
       </c>
       <c r="B58" t="n">
-        <v>91545</v>
+        <v>91569</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6470,23 +6474,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6494,10 +6494,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468821</v>
+        <v>469137</v>
       </c>
       <c r="R58" t="n">
-        <v>7065043</v>
+        <v>7065120</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6663,10 +6663,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129059687</v>
+        <v>129059675</v>
       </c>
       <c r="B60" t="n">
-        <v>80150</v>
+        <v>91545</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6674,21 +6674,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6698,10 +6698,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>468843</v>
+        <v>469197</v>
       </c>
       <c r="R60" t="n">
-        <v>7065390</v>
+        <v>7065308</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6744,21 +6744,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6775,10 +6760,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129059674</v>
+        <v>129059687</v>
       </c>
       <c r="B61" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6786,21 +6771,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6810,10 +6795,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>469226</v>
+        <v>468843</v>
       </c>
       <c r="R61" t="n">
-        <v>7065299</v>
+        <v>7065390</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6856,6 +6841,21 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6872,32 +6872,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129060043</v>
+        <v>129059686</v>
       </c>
       <c r="B62" t="n">
-        <v>75033</v>
+        <v>83007</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6428</v>
+        <v>310</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>469011</v>
+        <v>468843</v>
       </c>
       <c r="R62" t="n">
-        <v>7065022</v>
+        <v>7065390</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6953,6 +6953,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -6969,32 +6984,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129060050</v>
+        <v>129060043</v>
       </c>
       <c r="B63" t="n">
-        <v>79044</v>
+        <v>75033</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7004,10 +7019,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>469118</v>
+        <v>469011</v>
       </c>
       <c r="R63" t="n">
-        <v>7065190</v>
+        <v>7065022</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7040,11 +7055,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7071,10 +7081,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129059675</v>
+        <v>129059674</v>
       </c>
       <c r="B64" t="n">
-        <v>91541</v>
+        <v>79044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7082,21 +7092,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7106,10 +7116,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>469197</v>
+        <v>469226</v>
       </c>
       <c r="R64" t="n">
-        <v>7065308</v>
+        <v>7065299</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7168,10 +7178,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129059686</v>
+        <v>129060050</v>
       </c>
       <c r="B65" t="n">
-        <v>83007</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7179,21 +7189,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>310</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7203,10 +7213,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>468843</v>
+        <v>469118</v>
       </c>
       <c r="R65" t="n">
-        <v>7065390</v>
+        <v>7065190</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7241,6 +7251,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7249,21 +7264,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7601,10 +7601,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129059670</v>
+        <v>129059682</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7612,39 +7612,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>469326</v>
+        <v>468990</v>
       </c>
       <c r="R69" t="n">
-        <v>7065255</v>
+        <v>7065370</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7677,11 +7672,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7708,10 +7698,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129059682</v>
+        <v>129059670</v>
       </c>
       <c r="B70" t="n">
-        <v>91545</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7719,34 +7709,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468990</v>
+        <v>469326</v>
       </c>
       <c r="R70" t="n">
-        <v>7065370</v>
+        <v>7065255</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7779,6 +7774,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8014,10 +8014,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129059677</v>
+        <v>129059714</v>
       </c>
       <c r="B73" t="n">
-        <v>78057</v>
+        <v>57727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8025,34 +8025,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>469160</v>
+        <v>468946</v>
       </c>
       <c r="R73" t="n">
-        <v>7065329</v>
+        <v>7064969</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8085,6 +8090,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8111,45 +8121,50 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129060047</v>
+        <v>129059701</v>
       </c>
       <c r="B74" t="n">
-        <v>91918</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>469012</v>
+        <v>468991</v>
       </c>
       <c r="R74" t="n">
-        <v>7065037</v>
+        <v>7065056</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8182,6 +8197,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8208,10 +8228,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129059698</v>
+        <v>129059677</v>
       </c>
       <c r="B75" t="n">
-        <v>80150</v>
+        <v>78057</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8219,21 +8239,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8243,10 +8263,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>469120</v>
+        <v>469160</v>
       </c>
       <c r="R75" t="n">
-        <v>7065078</v>
+        <v>7065329</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8289,21 +8309,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8320,32 +8325,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129060040</v>
+        <v>129060047</v>
       </c>
       <c r="B76" t="n">
-        <v>80150</v>
+        <v>91922</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8355,10 +8360,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>469148</v>
+        <v>469012</v>
       </c>
       <c r="R76" t="n">
-        <v>7065056</v>
+        <v>7065037</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8417,10 +8422,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129059714</v>
+        <v>129059698</v>
       </c>
       <c r="B77" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8428,39 +8433,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>468946</v>
+        <v>469120</v>
       </c>
       <c r="R77" t="n">
-        <v>7064969</v>
+        <v>7065078</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8495,11 +8495,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8508,6 +8503,21 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -8524,10 +8534,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129059701</v>
+        <v>129060040</v>
       </c>
       <c r="B78" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8535,36 +8545,31 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>468991</v>
+        <v>469148</v>
       </c>
       <c r="R78" t="n">
         <v>7065056</v>
@@ -8600,11 +8605,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8952,10 +8952,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129059679</v>
+        <v>129059706</v>
       </c>
       <c r="B82" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8963,39 +8963,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>469108</v>
+        <v>468850</v>
       </c>
       <c r="R82" t="n">
-        <v>7065364</v>
+        <v>7065034</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9030,11 +9025,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9043,6 +9033,21 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9059,10 +9064,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129059713</v>
+        <v>129059676</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>83012</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9070,39 +9075,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>468922</v>
+        <v>469160</v>
       </c>
       <c r="R83" t="n">
-        <v>7064998</v>
+        <v>7065329</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9135,11 +9135,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9166,10 +9161,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129059692</v>
+        <v>129059696</v>
       </c>
       <c r="B84" t="n">
-        <v>57727</v>
+        <v>91569</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9177,39 +9172,30 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>469137</v>
+        <v>469141</v>
       </c>
       <c r="R84" t="n">
-        <v>7065206</v>
+        <v>7065095</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9242,11 +9228,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9273,10 +9254,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129059706</v>
+        <v>129059712</v>
       </c>
       <c r="B85" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9284,21 +9265,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9308,10 +9289,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>468850</v>
+        <v>468868</v>
       </c>
       <c r="R85" t="n">
-        <v>7065034</v>
+        <v>7064989</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9354,21 +9335,6 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -9385,10 +9351,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129059696</v>
+        <v>129059679</v>
       </c>
       <c r="B86" t="n">
-        <v>91565</v>
+        <v>57727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9396,30 +9362,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>469141</v>
+        <v>469108</v>
       </c>
       <c r="R86" t="n">
-        <v>7065095</v>
+        <v>7065364</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9452,6 +9427,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9478,10 +9458,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129059676</v>
+        <v>129059713</v>
       </c>
       <c r="B87" t="n">
-        <v>83012</v>
+        <v>57727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9489,34 +9469,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>469160</v>
+        <v>468922</v>
       </c>
       <c r="R87" t="n">
-        <v>7065329</v>
+        <v>7064998</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9549,6 +9534,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9575,10 +9565,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129059712</v>
+        <v>129059692</v>
       </c>
       <c r="B88" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9586,34 +9576,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>468868</v>
+        <v>469137</v>
       </c>
       <c r="R88" t="n">
-        <v>7064989</v>
+        <v>7065206</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9646,6 +9641,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129059689</v>
+        <v>129060044</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468887</v>
+        <v>469111</v>
       </c>
       <c r="R2" t="n">
-        <v>7065318</v>
+        <v>7065086</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129060044</v>
+        <v>129059711</v>
       </c>
       <c r="B3" t="n">
         <v>80149</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469111</v>
+        <v>468844</v>
       </c>
       <c r="R3" t="n">
-        <v>7065086</v>
+        <v>7064978</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -869,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129059711</v>
+        <v>129059689</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468844</v>
+        <v>468887</v>
       </c>
       <c r="R4" t="n">
-        <v>7064978</v>
+        <v>7065318</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,21 +965,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129060012</v>
+        <v>129059683</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,39 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469235</v>
+        <v>468964</v>
       </c>
       <c r="R5" t="n">
-        <v>7065256</v>
+        <v>7065331</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1052,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1078,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129060023</v>
+        <v>129060012</v>
       </c>
       <c r="B6" t="n">
         <v>57727</v>
@@ -1119,7 +1109,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1128,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469142</v>
+        <v>469235</v>
       </c>
       <c r="R6" t="n">
-        <v>7065079</v>
+        <v>7065256</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129060033</v>
+        <v>129060023</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1235,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469047</v>
+        <v>469142</v>
       </c>
       <c r="R7" t="n">
-        <v>7064905</v>
+        <v>7065079</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1623,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129059683</v>
+        <v>129060033</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1634,34 +1624,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468964</v>
+        <v>469047</v>
       </c>
       <c r="R11" t="n">
-        <v>7065331</v>
+        <v>7064905</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,6 +1689,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129059678</v>
+        <v>129060015</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,34 +1843,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469160</v>
+        <v>469142</v>
       </c>
       <c r="R13" t="n">
-        <v>7065329</v>
+        <v>7065300</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,6 +1908,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129060015</v>
+        <v>129059678</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1940,39 +1950,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469142</v>
+        <v>469160</v>
       </c>
       <c r="R14" t="n">
-        <v>7065300</v>
+        <v>7065329</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,11 +2010,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129060039</v>
+        <v>129059708</v>
       </c>
       <c r="B18" t="n">
-        <v>80150</v>
+        <v>83017</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469139</v>
+        <v>468783</v>
       </c>
       <c r="R18" t="n">
-        <v>7065094</v>
+        <v>7065001</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2423,6 +2423,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2439,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129059695</v>
+        <v>129060039</v>
       </c>
       <c r="B19" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2450,21 +2465,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469141</v>
+        <v>469139</v>
       </c>
       <c r="R19" t="n">
-        <v>7065114</v>
+        <v>7065094</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2520,21 +2535,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2551,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129059708</v>
+        <v>129060003</v>
       </c>
       <c r="B20" t="n">
-        <v>83017</v>
+        <v>91550</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,21 +2562,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468783</v>
+        <v>469006</v>
       </c>
       <c r="R20" t="n">
-        <v>7065001</v>
+        <v>7065358</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2632,21 +2632,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2663,10 +2648,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129060003</v>
+        <v>129059695</v>
       </c>
       <c r="B21" t="n">
-        <v>91549</v>
+        <v>80149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,21 +2659,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2698,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469006</v>
+        <v>469141</v>
       </c>
       <c r="R21" t="n">
-        <v>7065358</v>
+        <v>7065114</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,6 +2729,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3290,45 +3290,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129060006</v>
+        <v>129060035</v>
       </c>
       <c r="B27" t="n">
-        <v>92267</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469045</v>
+        <v>469149</v>
       </c>
       <c r="R27" t="n">
-        <v>7065011</v>
+        <v>7065169</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3387,10 +3396,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129060048</v>
+        <v>129060046</v>
       </c>
       <c r="B28" t="n">
-        <v>91569</v>
+        <v>91546</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3398,19 +3407,23 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3418,10 +3431,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469135</v>
+        <v>469215</v>
       </c>
       <c r="R28" t="n">
-        <v>7065166</v>
+        <v>7065278</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3480,32 +3493,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129060046</v>
+        <v>129060006</v>
       </c>
       <c r="B29" t="n">
-        <v>91545</v>
+        <v>92268</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3515,10 +3528,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469215</v>
+        <v>469045</v>
       </c>
       <c r="R29" t="n">
-        <v>7065278</v>
+        <v>7065011</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3577,10 +3590,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129060027</v>
+        <v>129060048</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>91570</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3588,39 +3601,30 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>468896</v>
+        <v>469135</v>
       </c>
       <c r="R30" t="n">
-        <v>7064986</v>
+        <v>7065166</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3653,11 +3657,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3684,10 +3683,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129060035</v>
+        <v>129060027</v>
       </c>
       <c r="B31" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3695,31 +3694,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3728,10 +3723,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469149</v>
+        <v>468896</v>
       </c>
       <c r="R31" t="n">
-        <v>7065169</v>
+        <v>7064986</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3764,6 +3759,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4422,10 +4422,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129060002</v>
+        <v>129059684</v>
       </c>
       <c r="B38" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4433,34 +4433,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>469031</v>
+        <v>468895</v>
       </c>
       <c r="R38" t="n">
-        <v>7065017</v>
+        <v>7065399</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4493,6 +4498,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4519,45 +4529,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129060001</v>
+        <v>129060026</v>
       </c>
       <c r="B39" t="n">
-        <v>91513</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468967</v>
+        <v>468886</v>
       </c>
       <c r="R39" t="n">
-        <v>7065256</v>
+        <v>7065015</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4590,6 +4605,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4616,7 +4636,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129059684</v>
+        <v>129059715</v>
       </c>
       <c r="B40" t="n">
         <v>57727</v>
@@ -4656,10 +4676,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>468895</v>
+        <v>469047</v>
       </c>
       <c r="R40" t="n">
-        <v>7065399</v>
+        <v>7064912</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4723,50 +4743,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129060026</v>
+        <v>129060001</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>91514</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468886</v>
+        <v>468967</v>
       </c>
       <c r="R41" t="n">
-        <v>7065015</v>
+        <v>7065256</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4799,11 +4814,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4830,10 +4840,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129059715</v>
+        <v>129060002</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4841,39 +4851,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469047</v>
+        <v>469031</v>
       </c>
       <c r="R42" t="n">
-        <v>7064912</v>
+        <v>7065017</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4906,11 +4911,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5034,10 +5034,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129060018</v>
+        <v>129060049</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>91570</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5045,39 +5045,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>469093</v>
+        <v>469012</v>
       </c>
       <c r="R44" t="n">
-        <v>7065345</v>
+        <v>7065037</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5110,11 +5101,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5141,10 +5127,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129060017</v>
+        <v>129059703</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5152,39 +5138,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>469122</v>
+        <v>468883</v>
       </c>
       <c r="R45" t="n">
-        <v>7065303</v>
+        <v>7065026</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5217,11 +5198,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5248,10 +5224,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129060049</v>
+        <v>129059699</v>
       </c>
       <c r="B46" t="n">
-        <v>91569</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5259,19 +5235,23 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5279,10 +5259,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469012</v>
+        <v>469071</v>
       </c>
       <c r="R46" t="n">
-        <v>7065037</v>
+        <v>7065075</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5341,10 +5321,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129059699</v>
+        <v>129060018</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5352,34 +5332,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>469071</v>
+        <v>469093</v>
       </c>
       <c r="R47" t="n">
-        <v>7065075</v>
+        <v>7065345</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5412,6 +5397,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5438,10 +5428,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129059703</v>
+        <v>129060017</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5449,34 +5439,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>468883</v>
+        <v>469122</v>
       </c>
       <c r="R48" t="n">
-        <v>7065026</v>
+        <v>7065303</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5509,6 +5504,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5535,10 +5535,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129059709</v>
+        <v>129059702</v>
       </c>
       <c r="B49" t="n">
-        <v>83007</v>
+        <v>91550</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5546,21 +5546,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>310</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>468844</v>
+        <v>468889</v>
       </c>
       <c r="R49" t="n">
-        <v>7064978</v>
+        <v>7065025</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5616,21 +5616,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5647,32 +5632,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129060042</v>
+        <v>129059709</v>
       </c>
       <c r="B50" t="n">
-        <v>80053</v>
+        <v>83007</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6456</v>
+        <v>310</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5682,10 +5667,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>469356</v>
+        <v>468844</v>
       </c>
       <c r="R50" t="n">
-        <v>7065233</v>
+        <v>7064978</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5728,6 +5713,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5744,32 +5744,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129059702</v>
+        <v>129060042</v>
       </c>
       <c r="B51" t="n">
-        <v>91549</v>
+        <v>80053</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>468889</v>
+        <v>469356</v>
       </c>
       <c r="R51" t="n">
-        <v>7065025</v>
+        <v>7065233</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6167,10 +6167,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129060036</v>
+        <v>129060041</v>
       </c>
       <c r="B55" t="n">
-        <v>57887</v>
+        <v>80150</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6178,39 +6178,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>468801</v>
+        <v>469143</v>
       </c>
       <c r="R55" t="n">
-        <v>7065038</v>
+        <v>7065030</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6269,10 +6264,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129060041</v>
+        <v>129060036</v>
       </c>
       <c r="B56" t="n">
-        <v>80150</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6280,34 +6275,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>469143</v>
+        <v>468801</v>
       </c>
       <c r="R56" t="n">
-        <v>7065030</v>
+        <v>7065038</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6366,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129060005</v>
+        <v>129059693</v>
       </c>
       <c r="B57" t="n">
-        <v>91549</v>
+        <v>91570</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6377,23 +6377,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6401,10 +6397,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>468821</v>
+        <v>469137</v>
       </c>
       <c r="R57" t="n">
-        <v>7065043</v>
+        <v>7065120</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6463,10 +6459,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129059693</v>
+        <v>129060005</v>
       </c>
       <c r="B58" t="n">
-        <v>91569</v>
+        <v>91550</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6474,19 +6470,23 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6494,10 +6494,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>469137</v>
+        <v>468821</v>
       </c>
       <c r="R58" t="n">
-        <v>7065120</v>
+        <v>7065043</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6663,10 +6663,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129059675</v>
+        <v>129059687</v>
       </c>
       <c r="B60" t="n">
-        <v>91545</v>
+        <v>80150</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6674,21 +6674,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6698,10 +6698,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>469197</v>
+        <v>468843</v>
       </c>
       <c r="R60" t="n">
-        <v>7065308</v>
+        <v>7065390</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6744,6 +6744,21 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6760,10 +6775,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129059687</v>
+        <v>129059675</v>
       </c>
       <c r="B61" t="n">
-        <v>80150</v>
+        <v>91546</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6771,21 +6786,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6795,10 +6810,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468843</v>
+        <v>469197</v>
       </c>
       <c r="R61" t="n">
-        <v>7065390</v>
+        <v>7065308</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6841,21 +6856,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7280,7 +7280,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129060029</v>
+        <v>129060025</v>
       </c>
       <c r="B66" t="n">
         <v>57727</v>
@@ -7320,10 +7320,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468970</v>
+        <v>469101</v>
       </c>
       <c r="R66" t="n">
-        <v>7064946</v>
+        <v>7065026</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7387,7 +7387,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129060021</v>
+        <v>129060029</v>
       </c>
       <c r="B67" t="n">
         <v>57727</v>
@@ -7418,7 +7418,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7427,10 +7427,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468788</v>
+        <v>468970</v>
       </c>
       <c r="R67" t="n">
-        <v>7065344</v>
+        <v>7064946</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7494,7 +7494,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129060025</v>
+        <v>129060021</v>
       </c>
       <c r="B68" t="n">
         <v>57727</v>
@@ -7525,7 +7525,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>469101</v>
+        <v>468788</v>
       </c>
       <c r="R68" t="n">
-        <v>7065026</v>
+        <v>7065344</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7604,7 +7604,7 @@
         <v>129059682</v>
       </c>
       <c r="B69" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7805,10 +7805,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129060011</v>
+        <v>129060051</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7816,39 +7816,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>469245</v>
+        <v>469121</v>
       </c>
       <c r="R71" t="n">
-        <v>7065256</v>
+        <v>7064885</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7885,7 +7880,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7912,10 +7907,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129060051</v>
+        <v>129060011</v>
       </c>
       <c r="B72" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7923,34 +7918,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>469121</v>
+        <v>469245</v>
       </c>
       <c r="R72" t="n">
-        <v>7064885</v>
+        <v>7065256</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Med apotechier</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8228,32 +8228,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129059677</v>
+        <v>129060047</v>
       </c>
       <c r="B75" t="n">
-        <v>78057</v>
+        <v>91923</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228579</v>
+        <v>2063</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8263,10 +8263,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>469160</v>
+        <v>469012</v>
       </c>
       <c r="R75" t="n">
-        <v>7065329</v>
+        <v>7065037</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8325,32 +8325,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129060047</v>
+        <v>129059698</v>
       </c>
       <c r="B76" t="n">
-        <v>91922</v>
+        <v>80150</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2063</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8360,10 +8360,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>469012</v>
+        <v>469120</v>
       </c>
       <c r="R76" t="n">
-        <v>7065037</v>
+        <v>7065078</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8406,6 +8406,21 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8422,7 +8437,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129059698</v>
+        <v>129060040</v>
       </c>
       <c r="B77" t="n">
         <v>80150</v>
@@ -8457,10 +8472,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>469120</v>
+        <v>469148</v>
       </c>
       <c r="R77" t="n">
-        <v>7065078</v>
+        <v>7065056</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8503,21 +8518,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -8534,10 +8534,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129060040</v>
+        <v>129059677</v>
       </c>
       <c r="B78" t="n">
-        <v>80150</v>
+        <v>78057</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8545,21 +8545,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>469148</v>
+        <v>469160</v>
       </c>
       <c r="R78" t="n">
-        <v>7065056</v>
+        <v>7065329</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9064,10 +9064,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129059676</v>
+        <v>129059696</v>
       </c>
       <c r="B83" t="n">
-        <v>83012</v>
+        <v>91570</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9075,23 +9075,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9099,10 +9095,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>469160</v>
+        <v>469141</v>
       </c>
       <c r="R83" t="n">
-        <v>7065329</v>
+        <v>7065095</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9161,10 +9157,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129059696</v>
+        <v>129059676</v>
       </c>
       <c r="B84" t="n">
-        <v>91569</v>
+        <v>83012</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9172,19 +9168,23 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9192,10 +9192,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>469141</v>
+        <v>469160</v>
       </c>
       <c r="R84" t="n">
-        <v>7065095</v>
+        <v>7065329</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129059711</v>
+        <v>129059683</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468844</v>
+        <v>468964</v>
       </c>
       <c r="R3" t="n">
-        <v>7064978</v>
+        <v>7065331</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,21 +853,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -884,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129059689</v>
+        <v>129059711</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468887</v>
+        <v>468844</v>
       </c>
       <c r="R4" t="n">
-        <v>7065318</v>
+        <v>7064978</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +950,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129059683</v>
+        <v>129059689</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468964</v>
+        <v>468887</v>
       </c>
       <c r="R5" t="n">
-        <v>7065331</v>
+        <v>7065318</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129060012</v>
+        <v>129059710</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,39 +1089,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469235</v>
+        <v>468844</v>
       </c>
       <c r="R6" t="n">
-        <v>7065256</v>
+        <v>7064978</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,11 +1151,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1169,6 +1159,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1185,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129060023</v>
+        <v>129060012</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1216,7 +1221,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469142</v>
+        <v>469235</v>
       </c>
       <c r="R7" t="n">
-        <v>7065079</v>
+        <v>7065256</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129060008</v>
+        <v>129060023</v>
       </c>
       <c r="B8" t="n">
         <v>57727</v>
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469327</v>
+        <v>469142</v>
       </c>
       <c r="R8" t="n">
-        <v>7065224</v>
+        <v>7065079</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129060020</v>
+        <v>129060033</v>
       </c>
       <c r="B9" t="n">
         <v>57727</v>
@@ -1430,7 +1435,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468803</v>
+        <v>469047</v>
       </c>
       <c r="R9" t="n">
-        <v>7065369</v>
+        <v>7064905</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,7 +1511,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129060024</v>
+        <v>129060008</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1546,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469131</v>
+        <v>469327</v>
       </c>
       <c r="R10" t="n">
-        <v>7065083</v>
+        <v>7065224</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129060033</v>
+        <v>129060020</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1644,7 +1649,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1653,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469047</v>
+        <v>468803</v>
       </c>
       <c r="R11" t="n">
-        <v>7064905</v>
+        <v>7065369</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129059710</v>
+        <v>129060024</v>
       </c>
       <c r="B12" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,34 +1736,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468844</v>
+        <v>469131</v>
       </c>
       <c r="R12" t="n">
-        <v>7064978</v>
+        <v>7065083</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1793,6 +1803,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1801,21 +1816,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129060045</v>
+        <v>129060037</v>
       </c>
       <c r="B15" t="n">
-        <v>80149</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,34 +2047,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469013</v>
+        <v>468874</v>
       </c>
       <c r="R15" t="n">
-        <v>7065018</v>
+        <v>7064975</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129060022</v>
+        <v>129060045</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2144,39 +2149,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468893</v>
+        <v>469013</v>
       </c>
       <c r="R16" t="n">
-        <v>7065289</v>
+        <v>7065018</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,11 +2209,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2240,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129060037</v>
+        <v>129060022</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,27 +2246,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2280,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468874</v>
+        <v>468893</v>
       </c>
       <c r="R17" t="n">
-        <v>7064975</v>
+        <v>7065289</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,6 +2311,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129059708</v>
+        <v>129060003</v>
       </c>
       <c r="B18" t="n">
-        <v>83017</v>
+        <v>91550</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468783</v>
+        <v>469006</v>
       </c>
       <c r="R18" t="n">
-        <v>7065001</v>
+        <v>7065358</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2423,21 +2423,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2454,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129060039</v>
+        <v>129059695</v>
       </c>
       <c r="B19" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,21 +2450,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469139</v>
+        <v>469141</v>
       </c>
       <c r="R19" t="n">
-        <v>7065094</v>
+        <v>7065114</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,6 +2520,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2551,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129060003</v>
+        <v>129059708</v>
       </c>
       <c r="B20" t="n">
-        <v>91550</v>
+        <v>83017</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,21 +2562,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469006</v>
+        <v>468783</v>
       </c>
       <c r="R20" t="n">
-        <v>7065358</v>
+        <v>7065001</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2632,6 +2632,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2648,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129059695</v>
+        <v>129060039</v>
       </c>
       <c r="B21" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2659,21 +2674,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469141</v>
+        <v>469139</v>
       </c>
       <c r="R21" t="n">
-        <v>7065114</v>
+        <v>7065094</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2729,21 +2744,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3290,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129060035</v>
+        <v>129060048</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>91570</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3301,43 +3301,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469149</v>
+        <v>469135</v>
       </c>
       <c r="R27" t="n">
-        <v>7065169</v>
+        <v>7065166</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3396,32 +3383,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129060046</v>
+        <v>129060006</v>
       </c>
       <c r="B28" t="n">
-        <v>91546</v>
+        <v>92268</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3431,10 +3418,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469215</v>
+        <v>469045</v>
       </c>
       <c r="R28" t="n">
-        <v>7065278</v>
+        <v>7065011</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3493,45 +3480,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129060006</v>
+        <v>129060027</v>
       </c>
       <c r="B29" t="n">
-        <v>92268</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469045</v>
+        <v>468896</v>
       </c>
       <c r="R29" t="n">
-        <v>7065011</v>
+        <v>7064986</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3564,6 +3556,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3590,10 +3587,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129060048</v>
+        <v>129060035</v>
       </c>
       <c r="B30" t="n">
-        <v>91570</v>
+        <v>57887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3601,30 +3598,43 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469135</v>
+        <v>469149</v>
       </c>
       <c r="R30" t="n">
-        <v>7065166</v>
+        <v>7065169</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3683,10 +3693,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129060027</v>
+        <v>129060046</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>91546</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3694,39 +3704,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>468896</v>
+        <v>469215</v>
       </c>
       <c r="R31" t="n">
-        <v>7064986</v>
+        <v>7065278</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3759,11 +3764,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3790,32 +3790,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129059690</v>
+        <v>129059691</v>
       </c>
       <c r="B32" t="n">
-        <v>83010</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468887</v>
+        <v>468992</v>
       </c>
       <c r="R32" t="n">
-        <v>7065318</v>
+        <v>7065224</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3887,32 +3887,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129059691</v>
+        <v>129059690</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>83010</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>468992</v>
+        <v>468887</v>
       </c>
       <c r="R33" t="n">
-        <v>7065224</v>
+        <v>7065318</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4091,10 +4091,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129059700</v>
+        <v>129059694</v>
       </c>
       <c r="B35" t="n">
-        <v>80150</v>
+        <v>83004</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4102,21 +4102,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>469036</v>
+        <v>469141</v>
       </c>
       <c r="R35" t="n">
-        <v>7065082</v>
+        <v>7065114</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4175,17 +4175,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>sälgticka</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Phellinopsis conchata</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4203,10 +4203,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129059694</v>
+        <v>129059700</v>
       </c>
       <c r="B36" t="n">
-        <v>83004</v>
+        <v>80150</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4214,21 +4214,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>469141</v>
+        <v>469036</v>
       </c>
       <c r="R36" t="n">
-        <v>7065114</v>
+        <v>7065082</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4287,17 +4287,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälgticka</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Phellinopsis conchata</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4422,10 +4422,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129059684</v>
+        <v>129060002</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4433,39 +4433,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>468895</v>
+        <v>469031</v>
       </c>
       <c r="R38" t="n">
-        <v>7065399</v>
+        <v>7065017</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4498,11 +4493,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4529,50 +4519,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129060026</v>
+        <v>129060001</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91514</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468886</v>
+        <v>468967</v>
       </c>
       <c r="R39" t="n">
-        <v>7065015</v>
+        <v>7065256</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4605,11 +4590,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4636,7 +4616,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129059715</v>
+        <v>129060026</v>
       </c>
       <c r="B40" t="n">
         <v>57727</v>
@@ -4676,10 +4656,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>469047</v>
+        <v>468886</v>
       </c>
       <c r="R40" t="n">
-        <v>7064912</v>
+        <v>7065015</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4743,45 +4723,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129060001</v>
+        <v>129059715</v>
       </c>
       <c r="B41" t="n">
-        <v>91514</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468967</v>
+        <v>469047</v>
       </c>
       <c r="R41" t="n">
-        <v>7065256</v>
+        <v>7064912</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4814,6 +4799,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4840,10 +4830,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129060002</v>
+        <v>129059684</v>
       </c>
       <c r="B42" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4851,34 +4841,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469031</v>
+        <v>468895</v>
       </c>
       <c r="R42" t="n">
-        <v>7065017</v>
+        <v>7065399</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4911,6 +4906,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5034,10 +5034,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129060049</v>
+        <v>129059699</v>
       </c>
       <c r="B44" t="n">
-        <v>91570</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5045,19 +5045,23 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5065,10 +5069,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>469012</v>
+        <v>469071</v>
       </c>
       <c r="R44" t="n">
-        <v>7065037</v>
+        <v>7065075</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5224,10 +5228,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129059699</v>
+        <v>129060018</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5235,34 +5239,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469071</v>
+        <v>469093</v>
       </c>
       <c r="R46" t="n">
-        <v>7065075</v>
+        <v>7065345</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5295,6 +5304,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5321,7 +5335,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129060018</v>
+        <v>129060017</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5361,10 +5375,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>469093</v>
+        <v>469122</v>
       </c>
       <c r="R47" t="n">
-        <v>7065345</v>
+        <v>7065303</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5428,10 +5442,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129060017</v>
+        <v>129060049</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>91570</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5439,39 +5453,30 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>469122</v>
+        <v>469012</v>
       </c>
       <c r="R48" t="n">
-        <v>7065303</v>
+        <v>7065037</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5504,11 +5509,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5535,10 +5535,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129059702</v>
+        <v>129059709</v>
       </c>
       <c r="B49" t="n">
-        <v>91550</v>
+        <v>83007</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5546,21 +5546,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>310</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>468889</v>
+        <v>468844</v>
       </c>
       <c r="R49" t="n">
-        <v>7065025</v>
+        <v>7064978</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5616,6 +5616,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5632,10 +5647,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129059709</v>
+        <v>129059702</v>
       </c>
       <c r="B50" t="n">
-        <v>83007</v>
+        <v>91550</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5643,21 +5658,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>310</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5667,10 +5682,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>468844</v>
+        <v>468889</v>
       </c>
       <c r="R50" t="n">
-        <v>7064978</v>
+        <v>7065025</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5713,21 +5728,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5744,32 +5744,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129060042</v>
+        <v>129059697</v>
       </c>
       <c r="B51" t="n">
-        <v>80053</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>469356</v>
+        <v>469114</v>
       </c>
       <c r="R51" t="n">
-        <v>7065233</v>
+        <v>7065083</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5825,6 +5825,21 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -5841,32 +5856,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129059697</v>
+        <v>129060042</v>
       </c>
       <c r="B52" t="n">
-        <v>80149</v>
+        <v>80053</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5876,10 +5891,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>469114</v>
+        <v>469356</v>
       </c>
       <c r="R52" t="n">
-        <v>7065083</v>
+        <v>7065233</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5922,21 +5937,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6167,10 +6167,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129060041</v>
+        <v>129060036</v>
       </c>
       <c r="B55" t="n">
-        <v>80150</v>
+        <v>57887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6178,34 +6178,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>469143</v>
+        <v>468801</v>
       </c>
       <c r="R55" t="n">
-        <v>7065030</v>
+        <v>7065038</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6264,10 +6269,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129060036</v>
+        <v>129060041</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>80150</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6275,39 +6280,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>468801</v>
+        <v>469143</v>
       </c>
       <c r="R56" t="n">
-        <v>7065038</v>
+        <v>7065030</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6366,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129059693</v>
+        <v>129060005</v>
       </c>
       <c r="B57" t="n">
-        <v>91570</v>
+        <v>91550</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6377,19 +6377,23 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6397,10 +6401,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>469137</v>
+        <v>468821</v>
       </c>
       <c r="R57" t="n">
-        <v>7065120</v>
+        <v>7065043</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6459,10 +6463,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129060005</v>
+        <v>129059693</v>
       </c>
       <c r="B58" t="n">
-        <v>91550</v>
+        <v>91570</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6470,23 +6474,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6494,10 +6494,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468821</v>
+        <v>469137</v>
       </c>
       <c r="R58" t="n">
-        <v>7065043</v>
+        <v>7065120</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6775,10 +6775,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129059675</v>
+        <v>129060029</v>
       </c>
       <c r="B61" t="n">
-        <v>91546</v>
+        <v>57727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6786,34 +6786,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>469197</v>
+        <v>468970</v>
       </c>
       <c r="R61" t="n">
-        <v>7065308</v>
+        <v>7064946</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6846,6 +6851,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6872,10 +6882,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129059686</v>
+        <v>129060021</v>
       </c>
       <c r="B62" t="n">
-        <v>83007</v>
+        <v>57727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6883,34 +6893,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468843</v>
+        <v>468788</v>
       </c>
       <c r="R62" t="n">
-        <v>7065390</v>
+        <v>7065344</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6945,6 +6960,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -6953,21 +6973,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -6984,45 +6989,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129060043</v>
+        <v>129060025</v>
       </c>
       <c r="B63" t="n">
-        <v>75033</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>469011</v>
+        <v>469101</v>
       </c>
       <c r="R63" t="n">
-        <v>7065022</v>
+        <v>7065026</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7055,6 +7065,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7081,10 +7096,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129059674</v>
+        <v>129059675</v>
       </c>
       <c r="B64" t="n">
-        <v>79044</v>
+        <v>91546</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7092,21 +7107,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7116,10 +7131,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>469226</v>
+        <v>469197</v>
       </c>
       <c r="R64" t="n">
-        <v>7065299</v>
+        <v>7065308</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7178,10 +7193,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129060050</v>
+        <v>129059686</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>83007</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7189,21 +7204,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>310</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7213,10 +7228,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>469118</v>
+        <v>468843</v>
       </c>
       <c r="R65" t="n">
-        <v>7065190</v>
+        <v>7065390</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7251,11 +7266,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7264,6 +7274,21 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7280,10 +7305,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129060025</v>
+        <v>129059674</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7291,39 +7316,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>469101</v>
+        <v>469226</v>
       </c>
       <c r="R66" t="n">
-        <v>7065026</v>
+        <v>7065299</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7356,11 +7376,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7387,10 +7402,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129060029</v>
+        <v>129060050</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7398,39 +7413,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468970</v>
+        <v>469118</v>
       </c>
       <c r="R67" t="n">
-        <v>7064946</v>
+        <v>7065190</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7467,7 +7477,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7494,50 +7504,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129060021</v>
+        <v>129060043</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>75033</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>468788</v>
+        <v>469011</v>
       </c>
       <c r="R68" t="n">
-        <v>7065344</v>
+        <v>7065022</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7570,11 +7575,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8228,32 +8228,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129060047</v>
+        <v>129059698</v>
       </c>
       <c r="B75" t="n">
-        <v>91923</v>
+        <v>80150</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2063</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8263,10 +8263,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>469012</v>
+        <v>469120</v>
       </c>
       <c r="R75" t="n">
-        <v>7065037</v>
+        <v>7065078</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8309,6 +8309,21 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8325,7 +8340,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129059698</v>
+        <v>129060040</v>
       </c>
       <c r="B76" t="n">
         <v>80150</v>
@@ -8360,10 +8375,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>469120</v>
+        <v>469148</v>
       </c>
       <c r="R76" t="n">
-        <v>7065078</v>
+        <v>7065056</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8406,21 +8421,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8437,32 +8437,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129060040</v>
+        <v>129060047</v>
       </c>
       <c r="B77" t="n">
-        <v>80150</v>
+        <v>91923</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8472,10 +8472,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>469148</v>
+        <v>469012</v>
       </c>
       <c r="R77" t="n">
-        <v>7065056</v>
+        <v>7065037</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8952,10 +8952,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129059706</v>
+        <v>129059679</v>
       </c>
       <c r="B82" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8963,34 +8963,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>468850</v>
+        <v>469108</v>
       </c>
       <c r="R82" t="n">
-        <v>7065034</v>
+        <v>7065364</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9025,6 +9030,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9033,21 +9043,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9064,10 +9059,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129059696</v>
+        <v>129059713</v>
       </c>
       <c r="B83" t="n">
-        <v>91570</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9075,30 +9070,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>469141</v>
+        <v>468922</v>
       </c>
       <c r="R83" t="n">
-        <v>7065095</v>
+        <v>7064998</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9131,6 +9135,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9157,10 +9166,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129059676</v>
+        <v>129059692</v>
       </c>
       <c r="B84" t="n">
-        <v>83012</v>
+        <v>57727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9168,34 +9177,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>469160</v>
+        <v>469137</v>
       </c>
       <c r="R84" t="n">
-        <v>7065329</v>
+        <v>7065206</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9228,6 +9242,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9254,10 +9273,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129059712</v>
+        <v>129059696</v>
       </c>
       <c r="B85" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9265,23 +9284,19 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -9289,10 +9304,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>468868</v>
+        <v>469141</v>
       </c>
       <c r="R85" t="n">
-        <v>7064989</v>
+        <v>7065095</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9351,10 +9366,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129059679</v>
+        <v>129059712</v>
       </c>
       <c r="B86" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9362,39 +9377,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>469108</v>
+        <v>468868</v>
       </c>
       <c r="R86" t="n">
-        <v>7065364</v>
+        <v>7064989</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9427,11 +9437,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9458,10 +9463,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129059713</v>
+        <v>129059676</v>
       </c>
       <c r="B87" t="n">
-        <v>57727</v>
+        <v>83012</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9469,39 +9474,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>468922</v>
+        <v>469160</v>
       </c>
       <c r="R87" t="n">
-        <v>7064998</v>
+        <v>7065329</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9534,11 +9534,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9565,10 +9560,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129059692</v>
+        <v>129059706</v>
       </c>
       <c r="B88" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9576,39 +9571,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>469137</v>
+        <v>468850</v>
       </c>
       <c r="R88" t="n">
-        <v>7065206</v>
+        <v>7065034</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9643,11 +9633,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -9656,6 +9641,21 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129060015</v>
+        <v>129059678</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,39 +1843,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469142</v>
+        <v>469160</v>
       </c>
       <c r="R13" t="n">
-        <v>7065300</v>
+        <v>7065329</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,11 +1903,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129059678</v>
+        <v>129060015</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1950,34 +1940,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469160</v>
+        <v>469142</v>
       </c>
       <c r="R14" t="n">
-        <v>7065329</v>
+        <v>7065300</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,6 +2005,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2551,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129059708</v>
+        <v>129060007</v>
       </c>
       <c r="B20" t="n">
-        <v>83017</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,34 +2562,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468783</v>
+        <v>469364</v>
       </c>
       <c r="R20" t="n">
-        <v>7065001</v>
+        <v>7065232</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2624,6 +2629,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2632,21 +2642,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2663,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129060039</v>
+        <v>129059685</v>
       </c>
       <c r="B21" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,34 +2669,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469139</v>
+        <v>468878</v>
       </c>
       <c r="R21" t="n">
-        <v>7065094</v>
+        <v>7065401</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,6 +2734,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2760,10 +2765,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129060007</v>
+        <v>129059708</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>83017</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2771,39 +2776,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469364</v>
+        <v>468783</v>
       </c>
       <c r="R22" t="n">
-        <v>7065232</v>
+        <v>7065001</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2838,11 +2838,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2851,6 +2846,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2867,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129059685</v>
+        <v>129060039</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2878,39 +2888,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468878</v>
+        <v>469139</v>
       </c>
       <c r="R23" t="n">
-        <v>7065401</v>
+        <v>7065094</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2943,11 +2948,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3290,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129060048</v>
+        <v>129060035</v>
       </c>
       <c r="B27" t="n">
-        <v>91570</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3301,30 +3301,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469135</v>
+        <v>469149</v>
       </c>
       <c r="R27" t="n">
-        <v>7065166</v>
+        <v>7065169</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3383,34 +3396,30 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129060006</v>
+        <v>129060048</v>
       </c>
       <c r="B28" t="n">
-        <v>92268</v>
+        <v>91570</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3418,10 +3427,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469045</v>
+        <v>469135</v>
       </c>
       <c r="R28" t="n">
-        <v>7065011</v>
+        <v>7065166</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3480,10 +3489,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129060027</v>
+        <v>129060046</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>91546</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3491,39 +3500,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>468896</v>
+        <v>469215</v>
       </c>
       <c r="R29" t="n">
-        <v>7064986</v>
+        <v>7065278</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,11 +3560,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3587,54 +3586,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129060035</v>
+        <v>129060006</v>
       </c>
       <c r="B30" t="n">
-        <v>57887</v>
+        <v>92268</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469149</v>
+        <v>469045</v>
       </c>
       <c r="R30" t="n">
-        <v>7065169</v>
+        <v>7065011</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3693,10 +3683,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129060046</v>
+        <v>129060027</v>
       </c>
       <c r="B31" t="n">
-        <v>91546</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3704,34 +3694,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469215</v>
+        <v>468896</v>
       </c>
       <c r="R31" t="n">
-        <v>7065278</v>
+        <v>7064986</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3764,6 +3759,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4091,10 +4091,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129059694</v>
+        <v>129059700</v>
       </c>
       <c r="B35" t="n">
-        <v>83004</v>
+        <v>80150</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4102,21 +4102,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>469141</v>
+        <v>469036</v>
       </c>
       <c r="R35" t="n">
-        <v>7065114</v>
+        <v>7065082</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4175,17 +4175,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälgticka</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Phellinopsis conchata</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4203,10 +4203,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129059700</v>
+        <v>129059694</v>
       </c>
       <c r="B36" t="n">
-        <v>80150</v>
+        <v>83004</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4214,21 +4214,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>469036</v>
+        <v>469141</v>
       </c>
       <c r="R36" t="n">
-        <v>7065082</v>
+        <v>7065114</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4287,17 +4287,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>sälgticka</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Phellinopsis conchata</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4422,32 +4422,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129060002</v>
+        <v>129060001</v>
       </c>
       <c r="B38" t="n">
-        <v>91550</v>
+        <v>91514</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>469031</v>
+        <v>468967</v>
       </c>
       <c r="R38" t="n">
-        <v>7065017</v>
+        <v>7065256</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4519,45 +4519,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129060001</v>
+        <v>129059684</v>
       </c>
       <c r="B39" t="n">
-        <v>91514</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468967</v>
+        <v>468895</v>
       </c>
       <c r="R39" t="n">
-        <v>7065256</v>
+        <v>7065399</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4590,6 +4595,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4830,10 +4840,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129059684</v>
+        <v>129060002</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4841,39 +4851,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>468895</v>
+        <v>469031</v>
       </c>
       <c r="R42" t="n">
-        <v>7065399</v>
+        <v>7065017</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4906,11 +4911,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5034,10 +5034,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129059699</v>
+        <v>129060018</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5045,34 +5045,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>469071</v>
+        <v>469093</v>
       </c>
       <c r="R44" t="n">
-        <v>7065075</v>
+        <v>7065345</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5105,6 +5110,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5131,10 +5141,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129059703</v>
+        <v>129060017</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5142,34 +5152,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>468883</v>
+        <v>469122</v>
       </c>
       <c r="R45" t="n">
-        <v>7065026</v>
+        <v>7065303</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5202,6 +5217,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5228,10 +5248,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129060018</v>
+        <v>129060049</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>91570</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5239,39 +5259,30 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469093</v>
+        <v>469012</v>
       </c>
       <c r="R46" t="n">
-        <v>7065345</v>
+        <v>7065037</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5304,11 +5315,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5335,10 +5341,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129060017</v>
+        <v>129059699</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5346,39 +5352,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>469122</v>
+        <v>469071</v>
       </c>
       <c r="R47" t="n">
-        <v>7065303</v>
+        <v>7065075</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5411,11 +5412,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5442,10 +5438,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129060049</v>
+        <v>129059703</v>
       </c>
       <c r="B48" t="n">
-        <v>91570</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5453,19 +5449,23 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>469012</v>
+        <v>468883</v>
       </c>
       <c r="R48" t="n">
-        <v>7065037</v>
+        <v>7065026</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6167,10 +6167,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129060036</v>
+        <v>129060041</v>
       </c>
       <c r="B55" t="n">
-        <v>57887</v>
+        <v>80150</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6178,39 +6178,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>468801</v>
+        <v>469143</v>
       </c>
       <c r="R55" t="n">
-        <v>7065038</v>
+        <v>7065030</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6269,10 +6264,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129060041</v>
+        <v>129060036</v>
       </c>
       <c r="B56" t="n">
-        <v>80150</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6280,34 +6275,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>469143</v>
+        <v>468801</v>
       </c>
       <c r="R56" t="n">
-        <v>7065030</v>
+        <v>7065038</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6663,10 +6663,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129059687</v>
+        <v>129059686</v>
       </c>
       <c r="B60" t="n">
-        <v>80150</v>
+        <v>83007</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6674,21 +6674,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>310</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6775,10 +6775,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129060029</v>
+        <v>129059674</v>
       </c>
       <c r="B61" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6786,39 +6786,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468970</v>
+        <v>469226</v>
       </c>
       <c r="R61" t="n">
-        <v>7064946</v>
+        <v>7065299</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6851,11 +6846,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6882,10 +6872,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129060021</v>
+        <v>129060050</v>
       </c>
       <c r="B62" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6893,39 +6883,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468788</v>
+        <v>469118</v>
       </c>
       <c r="R62" t="n">
-        <v>7065344</v>
+        <v>7065190</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6962,7 +6947,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6989,50 +6974,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129060025</v>
+        <v>129060043</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>75033</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>469101</v>
+        <v>469011</v>
       </c>
       <c r="R63" t="n">
-        <v>7065026</v>
+        <v>7065022</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7065,11 +7045,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7193,10 +7168,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129059686</v>
+        <v>129059687</v>
       </c>
       <c r="B65" t="n">
-        <v>83007</v>
+        <v>80150</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7204,21 +7179,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>310</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7305,10 +7280,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129059674</v>
+        <v>129060029</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7316,34 +7291,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>469226</v>
+        <v>468970</v>
       </c>
       <c r="R66" t="n">
-        <v>7065299</v>
+        <v>7064946</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7376,6 +7356,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7402,10 +7387,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129060050</v>
+        <v>129060021</v>
       </c>
       <c r="B67" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7413,34 +7398,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>469118</v>
+        <v>468788</v>
       </c>
       <c r="R67" t="n">
-        <v>7065190</v>
+        <v>7065344</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7477,7 +7467,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7504,45 +7494,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129060043</v>
+        <v>129060025</v>
       </c>
       <c r="B68" t="n">
-        <v>75033</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>469011</v>
+        <v>469101</v>
       </c>
       <c r="R68" t="n">
-        <v>7065022</v>
+        <v>7065026</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7575,6 +7570,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129060044</v>
+        <v>129059689</v>
       </c>
       <c r="B2" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469111</v>
+        <v>468887</v>
       </c>
       <c r="R2" t="n">
-        <v>7065086</v>
+        <v>7065318</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129059683</v>
+        <v>129060044</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468964</v>
+        <v>469111</v>
       </c>
       <c r="R3" t="n">
-        <v>7065331</v>
+        <v>7065086</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129059711</v>
+        <v>129060012</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468844</v>
+        <v>469235</v>
       </c>
       <c r="R4" t="n">
-        <v>7064978</v>
+        <v>7065256</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -942,6 +947,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -950,21 +960,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -981,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129059689</v>
+        <v>129060023</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +987,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468887</v>
+        <v>469142</v>
       </c>
       <c r="R5" t="n">
-        <v>7065318</v>
+        <v>7065079</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,6 +1052,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129059710</v>
+        <v>129060033</v>
       </c>
       <c r="B6" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,34 +1094,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468844</v>
+        <v>469047</v>
       </c>
       <c r="R6" t="n">
-        <v>7064978</v>
+        <v>7064905</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,6 +1161,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1159,21 +1174,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129060012</v>
+        <v>129060008</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1221,7 +1221,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469235</v>
+        <v>469327</v>
       </c>
       <c r="R7" t="n">
-        <v>7065256</v>
+        <v>7065224</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129060023</v>
+        <v>129060020</v>
       </c>
       <c r="B8" t="n">
         <v>57727</v>
@@ -1328,7 +1328,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469142</v>
+        <v>468803</v>
       </c>
       <c r="R8" t="n">
-        <v>7065079</v>
+        <v>7065369</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129060033</v>
+        <v>129060024</v>
       </c>
       <c r="B9" t="n">
         <v>57727</v>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469047</v>
+        <v>469131</v>
       </c>
       <c r="R9" t="n">
-        <v>7064905</v>
+        <v>7065083</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129060008</v>
+        <v>129059710</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,39 +1522,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469327</v>
+        <v>468844</v>
       </c>
       <c r="R10" t="n">
-        <v>7065224</v>
+        <v>7064978</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,11 +1584,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1602,6 +1592,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1618,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129060020</v>
+        <v>129059683</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,39 +1634,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468803</v>
+        <v>468964</v>
       </c>
       <c r="R11" t="n">
-        <v>7065369</v>
+        <v>7065331</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,11 +1694,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129060024</v>
+        <v>129059711</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,39 +1731,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469131</v>
+        <v>468844</v>
       </c>
       <c r="R12" t="n">
-        <v>7065083</v>
+        <v>7064978</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1803,11 +1793,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1816,6 +1801,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129059678</v>
+        <v>129060015</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,34 +1843,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469160</v>
+        <v>469142</v>
       </c>
       <c r="R13" t="n">
-        <v>7065329</v>
+        <v>7065300</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,6 +1908,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129060015</v>
+        <v>129059678</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1940,39 +1950,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469142</v>
+        <v>469160</v>
       </c>
       <c r="R14" t="n">
-        <v>7065300</v>
+        <v>7065329</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,11 +2010,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129060037</v>
+        <v>129060045</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>80149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,39 +2047,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468874</v>
+        <v>469013</v>
       </c>
       <c r="R15" t="n">
-        <v>7064975</v>
+        <v>7065018</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129060045</v>
+        <v>129060022</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,34 +2144,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469013</v>
+        <v>468893</v>
       </c>
       <c r="R16" t="n">
-        <v>7065018</v>
+        <v>7065289</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,6 +2209,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129060022</v>
+        <v>129060037</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,27 +2251,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2275,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468893</v>
+        <v>468874</v>
       </c>
       <c r="R17" t="n">
-        <v>7065289</v>
+        <v>7064975</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2311,11 +2316,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129060003</v>
+        <v>129059695</v>
       </c>
       <c r="B18" t="n">
-        <v>91550</v>
+        <v>80149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469006</v>
+        <v>469141</v>
       </c>
       <c r="R18" t="n">
-        <v>7065358</v>
+        <v>7065114</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2423,6 +2423,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2439,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129059695</v>
+        <v>129059708</v>
       </c>
       <c r="B19" t="n">
-        <v>80149</v>
+        <v>83017</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2450,21 +2465,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469141</v>
+        <v>468783</v>
       </c>
       <c r="R19" t="n">
-        <v>7065114</v>
+        <v>7065001</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2523,17 +2538,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2551,10 +2566,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129060007</v>
+        <v>129060003</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,39 +2577,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469364</v>
+        <v>469006</v>
       </c>
       <c r="R20" t="n">
-        <v>7065232</v>
+        <v>7065358</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2627,11 +2637,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2658,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129059685</v>
+        <v>129060039</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,39 +2674,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468878</v>
+        <v>469139</v>
       </c>
       <c r="R21" t="n">
-        <v>7065401</v>
+        <v>7065094</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,11 +2734,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2765,10 +2760,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129059708</v>
+        <v>129060007</v>
       </c>
       <c r="B22" t="n">
-        <v>83017</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2776,34 +2771,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468783</v>
+        <v>469364</v>
       </c>
       <c r="R22" t="n">
-        <v>7065001</v>
+        <v>7065232</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2838,6 +2838,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2846,21 +2851,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2877,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129060039</v>
+        <v>129059685</v>
       </c>
       <c r="B23" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2888,34 +2878,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469139</v>
+        <v>468878</v>
       </c>
       <c r="R23" t="n">
-        <v>7065094</v>
+        <v>7065401</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,6 +2943,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3290,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129060035</v>
+        <v>129060046</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>91549</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3301,43 +3301,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469149</v>
+        <v>469215</v>
       </c>
       <c r="R27" t="n">
-        <v>7065169</v>
+        <v>7065278</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3396,30 +3387,34 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129060048</v>
+        <v>129060006</v>
       </c>
       <c r="B28" t="n">
-        <v>91570</v>
+        <v>92271</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3427,10 +3422,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469135</v>
+        <v>469045</v>
       </c>
       <c r="R28" t="n">
-        <v>7065166</v>
+        <v>7065011</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3489,10 +3484,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129060046</v>
+        <v>129060048</v>
       </c>
       <c r="B29" t="n">
-        <v>91546</v>
+        <v>91573</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3500,23 +3495,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3524,10 +3515,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469215</v>
+        <v>469135</v>
       </c>
       <c r="R29" t="n">
-        <v>7065278</v>
+        <v>7065166</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3586,45 +3577,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129060006</v>
+        <v>129060027</v>
       </c>
       <c r="B30" t="n">
-        <v>92268</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469045</v>
+        <v>468896</v>
       </c>
       <c r="R30" t="n">
-        <v>7065011</v>
+        <v>7064986</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3657,6 +3653,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3683,10 +3684,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129060027</v>
+        <v>129060035</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3694,27 +3695,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3723,10 +3728,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>468896</v>
+        <v>469149</v>
       </c>
       <c r="R31" t="n">
-        <v>7064986</v>
+        <v>7065169</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3759,11 +3764,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3887,45 +3887,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129059690</v>
+        <v>129059681</v>
       </c>
       <c r="B33" t="n">
-        <v>83010</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>468887</v>
+        <v>469043</v>
       </c>
       <c r="R33" t="n">
-        <v>7065318</v>
+        <v>7065365</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3958,6 +3963,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3984,50 +3994,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129059681</v>
+        <v>129059690</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>83010</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>469043</v>
+        <v>468887</v>
       </c>
       <c r="R34" t="n">
-        <v>7065365</v>
+        <v>7065318</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4060,11 +4065,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4091,10 +4091,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129059700</v>
+        <v>129059694</v>
       </c>
       <c r="B35" t="n">
-        <v>80150</v>
+        <v>83004</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4102,21 +4102,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>469036</v>
+        <v>469141</v>
       </c>
       <c r="R35" t="n">
-        <v>7065082</v>
+        <v>7065114</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4175,17 +4175,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>sälgticka</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Phellinopsis conchata</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4203,10 +4203,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129059694</v>
+        <v>129059700</v>
       </c>
       <c r="B36" t="n">
-        <v>83004</v>
+        <v>80150</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4214,21 +4214,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>469141</v>
+        <v>469036</v>
       </c>
       <c r="R36" t="n">
-        <v>7065114</v>
+        <v>7065082</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4287,17 +4287,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälgticka</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Phellinopsis conchata</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4425,7 +4425,7 @@
         <v>129060001</v>
       </c>
       <c r="B38" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4519,10 +4519,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129059684</v>
+        <v>129060002</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4530,39 +4530,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468895</v>
+        <v>469031</v>
       </c>
       <c r="R39" t="n">
-        <v>7065399</v>
+        <v>7065017</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4595,11 +4590,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4626,7 +4616,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129060026</v>
+        <v>129059684</v>
       </c>
       <c r="B40" t="n">
         <v>57727</v>
@@ -4666,10 +4656,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>468886</v>
+        <v>468895</v>
       </c>
       <c r="R40" t="n">
-        <v>7065015</v>
+        <v>7065399</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4733,7 +4723,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129059715</v>
+        <v>129060026</v>
       </c>
       <c r="B41" t="n">
         <v>57727</v>
@@ -4773,10 +4763,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>469047</v>
+        <v>468886</v>
       </c>
       <c r="R41" t="n">
-        <v>7064912</v>
+        <v>7065015</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4840,10 +4830,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129060002</v>
+        <v>129059715</v>
       </c>
       <c r="B42" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4851,34 +4841,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469031</v>
+        <v>469047</v>
       </c>
       <c r="R42" t="n">
-        <v>7065017</v>
+        <v>7064912</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4911,6 +4906,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5034,10 +5034,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129060018</v>
+        <v>129060049</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5045,39 +5045,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>469093</v>
+        <v>469012</v>
       </c>
       <c r="R44" t="n">
-        <v>7065345</v>
+        <v>7065037</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5110,11 +5101,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5141,10 +5127,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129060017</v>
+        <v>129059699</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5152,39 +5138,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>469122</v>
+        <v>469071</v>
       </c>
       <c r="R45" t="n">
-        <v>7065303</v>
+        <v>7065075</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5217,11 +5198,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5248,10 +5224,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129060049</v>
+        <v>129060018</v>
       </c>
       <c r="B46" t="n">
-        <v>91570</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5259,30 +5235,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469012</v>
+        <v>469093</v>
       </c>
       <c r="R46" t="n">
-        <v>7065037</v>
+        <v>7065345</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5315,6 +5300,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5341,10 +5331,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129059699</v>
+        <v>129060017</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5352,34 +5342,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>469071</v>
+        <v>469122</v>
       </c>
       <c r="R47" t="n">
-        <v>7065075</v>
+        <v>7065303</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5412,6 +5407,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5535,10 +5535,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129059709</v>
+        <v>129059697</v>
       </c>
       <c r="B49" t="n">
-        <v>83007</v>
+        <v>80149</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5546,21 +5546,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>310</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>468844</v>
+        <v>469114</v>
       </c>
       <c r="R49" t="n">
-        <v>7064978</v>
+        <v>7065083</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5650,7 +5650,7 @@
         <v>129059702</v>
       </c>
       <c r="B50" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5744,10 +5744,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129059697</v>
+        <v>129059709</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>83007</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5755,21 +5755,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>310</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>469114</v>
+        <v>468844</v>
       </c>
       <c r="R51" t="n">
-        <v>7065083</v>
+        <v>7064978</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6369,7 +6369,7 @@
         <v>129060005</v>
       </c>
       <c r="B57" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>129059693</v>
       </c>
       <c r="B58" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6663,10 +6663,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129059686</v>
+        <v>129059687</v>
       </c>
       <c r="B60" t="n">
-        <v>83007</v>
+        <v>80150</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6674,21 +6674,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>310</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6775,32 +6775,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129059674</v>
+        <v>129060043</v>
       </c>
       <c r="B61" t="n">
-        <v>79044</v>
+        <v>75033</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>469226</v>
+        <v>469011</v>
       </c>
       <c r="R61" t="n">
-        <v>7065299</v>
+        <v>7065022</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6872,10 +6872,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129060050</v>
+        <v>129060029</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6883,34 +6883,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>469118</v>
+        <v>468970</v>
       </c>
       <c r="R62" t="n">
-        <v>7065190</v>
+        <v>7064946</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6947,7 +6952,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6974,45 +6979,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129060043</v>
+        <v>129060021</v>
       </c>
       <c r="B63" t="n">
-        <v>75033</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>469011</v>
+        <v>468788</v>
       </c>
       <c r="R63" t="n">
-        <v>7065022</v>
+        <v>7065344</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7045,6 +7055,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7071,10 +7086,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129059675</v>
+        <v>129060025</v>
       </c>
       <c r="B64" t="n">
-        <v>91546</v>
+        <v>57727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7082,34 +7097,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>469197</v>
+        <v>469101</v>
       </c>
       <c r="R64" t="n">
-        <v>7065308</v>
+        <v>7065026</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7142,6 +7162,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7168,10 +7193,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129059687</v>
+        <v>129059686</v>
       </c>
       <c r="B65" t="n">
-        <v>80150</v>
+        <v>83007</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7179,21 +7204,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>310</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7280,10 +7305,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129060029</v>
+        <v>129059675</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7291,39 +7316,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468970</v>
+        <v>469197</v>
       </c>
       <c r="R66" t="n">
-        <v>7064946</v>
+        <v>7065308</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7356,11 +7376,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7387,10 +7402,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129060021</v>
+        <v>129059674</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7398,39 +7413,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468788</v>
+        <v>469226</v>
       </c>
       <c r="R67" t="n">
-        <v>7065344</v>
+        <v>7065299</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7463,11 +7473,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7494,10 +7499,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129060025</v>
+        <v>129060050</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7505,39 +7510,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>469101</v>
+        <v>469118</v>
       </c>
       <c r="R68" t="n">
-        <v>7065026</v>
+        <v>7065190</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7601,10 +7601,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129059682</v>
+        <v>129059670</v>
       </c>
       <c r="B69" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7612,34 +7612,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>468990</v>
+        <v>469326</v>
       </c>
       <c r="R69" t="n">
-        <v>7065370</v>
+        <v>7065255</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7672,6 +7677,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7698,10 +7708,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129059670</v>
+        <v>129059682</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7709,39 +7719,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>469326</v>
+        <v>468990</v>
       </c>
       <c r="R70" t="n">
-        <v>7065255</v>
+        <v>7065370</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7774,11 +7779,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8014,50 +8014,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129059714</v>
+        <v>129060047</v>
       </c>
       <c r="B73" t="n">
-        <v>57727</v>
+        <v>91926</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>468946</v>
+        <v>469012</v>
       </c>
       <c r="R73" t="n">
-        <v>7064969</v>
+        <v>7065037</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8090,11 +8085,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8121,10 +8111,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129059701</v>
+        <v>129059698</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8132,39 +8122,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>468991</v>
+        <v>469120</v>
       </c>
       <c r="R74" t="n">
-        <v>7065056</v>
+        <v>7065078</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8199,11 +8184,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8212,6 +8192,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8228,7 +8223,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129059698</v>
+        <v>129060040</v>
       </c>
       <c r="B75" t="n">
         <v>80150</v>
@@ -8263,10 +8258,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>469120</v>
+        <v>469148</v>
       </c>
       <c r="R75" t="n">
-        <v>7065078</v>
+        <v>7065056</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8309,21 +8304,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8340,10 +8320,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129060040</v>
+        <v>129059714</v>
       </c>
       <c r="B76" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8351,34 +8331,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>469148</v>
+        <v>468946</v>
       </c>
       <c r="R76" t="n">
-        <v>7065056</v>
+        <v>7064969</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8411,6 +8396,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8437,45 +8427,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129060047</v>
+        <v>129059701</v>
       </c>
       <c r="B77" t="n">
-        <v>91923</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>469012</v>
+        <v>468991</v>
       </c>
       <c r="R77" t="n">
-        <v>7065037</v>
+        <v>7065056</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8508,6 +8503,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8952,10 +8952,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129059679</v>
+        <v>129059676</v>
       </c>
       <c r="B82" t="n">
-        <v>57727</v>
+        <v>83012</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8963,39 +8963,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>469108</v>
+        <v>469160</v>
       </c>
       <c r="R82" t="n">
-        <v>7065364</v>
+        <v>7065329</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9028,11 +9023,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9059,10 +9049,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129059713</v>
+        <v>129059712</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9070,39 +9060,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>468922</v>
+        <v>468868</v>
       </c>
       <c r="R83" t="n">
-        <v>7064998</v>
+        <v>7064989</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9135,11 +9120,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9166,10 +9146,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129059692</v>
+        <v>129059706</v>
       </c>
       <c r="B84" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9177,39 +9157,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>469137</v>
+        <v>468850</v>
       </c>
       <c r="R84" t="n">
-        <v>7065206</v>
+        <v>7065034</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9244,11 +9219,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9257,6 +9227,21 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -9276,7 +9261,7 @@
         <v>129059696</v>
       </c>
       <c r="B85" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9366,10 +9351,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129059712</v>
+        <v>129059679</v>
       </c>
       <c r="B86" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9377,34 +9362,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>468868</v>
+        <v>469108</v>
       </c>
       <c r="R86" t="n">
-        <v>7064989</v>
+        <v>7065364</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9437,6 +9427,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9463,10 +9458,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129059676</v>
+        <v>129059713</v>
       </c>
       <c r="B87" t="n">
-        <v>83012</v>
+        <v>57727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9474,34 +9469,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>469160</v>
+        <v>468922</v>
       </c>
       <c r="R87" t="n">
-        <v>7065329</v>
+        <v>7064998</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9534,6 +9534,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9560,10 +9565,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129059706</v>
+        <v>129059692</v>
       </c>
       <c r="B88" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9571,34 +9576,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>468850</v>
+        <v>469137</v>
       </c>
       <c r="R88" t="n">
-        <v>7065034</v>
+        <v>7065206</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9633,6 +9643,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -9641,21 +9656,6 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129059689</v>
+        <v>129059710</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468887</v>
+        <v>468844</v>
       </c>
       <c r="R2" t="n">
-        <v>7065318</v>
+        <v>7064978</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,6 +756,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -772,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129060044</v>
+        <v>129060023</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +798,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469111</v>
+        <v>469142</v>
       </c>
       <c r="R3" t="n">
-        <v>7065086</v>
+        <v>7065079</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +863,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129060012</v>
+        <v>129060033</v>
       </c>
       <c r="B4" t="n">
         <v>57727</v>
@@ -900,7 +925,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -909,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469235</v>
+        <v>469047</v>
       </c>
       <c r="R4" t="n">
-        <v>7065256</v>
+        <v>7064905</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129060023</v>
+        <v>129060008</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1016,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469142</v>
+        <v>469327</v>
       </c>
       <c r="R5" t="n">
-        <v>7065079</v>
+        <v>7065224</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129060033</v>
+        <v>129060024</v>
       </c>
       <c r="B6" t="n">
         <v>57727</v>
@@ -1123,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469047</v>
+        <v>469131</v>
       </c>
       <c r="R6" t="n">
-        <v>7064905</v>
+        <v>7065083</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129060008</v>
+        <v>129060012</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1221,7 +1246,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1230,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469327</v>
+        <v>469235</v>
       </c>
       <c r="R7" t="n">
-        <v>7065224</v>
+        <v>7065256</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129060024</v>
+        <v>129059689</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,39 +1440,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469131</v>
+        <v>468887</v>
       </c>
       <c r="R9" t="n">
-        <v>7065083</v>
+        <v>7065318</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,11 +1500,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129059710</v>
+        <v>129059683</v>
       </c>
       <c r="B10" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468844</v>
+        <v>468964</v>
       </c>
       <c r="R10" t="n">
-        <v>7064978</v>
+        <v>7065331</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,21 +1607,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129059683</v>
+        <v>129060044</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1634,21 +1634,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468964</v>
+        <v>469111</v>
       </c>
       <c r="R11" t="n">
-        <v>7065331</v>
+        <v>7065086</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129060015</v>
+        <v>129059678</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,39 +1843,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469142</v>
+        <v>469160</v>
       </c>
       <c r="R13" t="n">
-        <v>7065300</v>
+        <v>7065329</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,11 +1903,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129059678</v>
+        <v>129060015</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1950,34 +1940,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469160</v>
+        <v>469142</v>
       </c>
       <c r="R14" t="n">
-        <v>7065329</v>
+        <v>7065300</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,6 +2005,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129060045</v>
+        <v>129060037</v>
       </c>
       <c r="B15" t="n">
-        <v>80149</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,34 +2047,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469013</v>
+        <v>468874</v>
       </c>
       <c r="R15" t="n">
-        <v>7065018</v>
+        <v>7064975</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129060022</v>
+        <v>129060045</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2144,39 +2149,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468893</v>
+        <v>469013</v>
       </c>
       <c r="R16" t="n">
-        <v>7065289</v>
+        <v>7065018</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,11 +2209,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2240,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129060037</v>
+        <v>129060022</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,27 +2246,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2280,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468874</v>
+        <v>468893</v>
       </c>
       <c r="R17" t="n">
-        <v>7064975</v>
+        <v>7065289</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,6 +2311,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2454,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129059708</v>
+        <v>129060007</v>
       </c>
       <c r="B19" t="n">
-        <v>83017</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,34 +2465,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468783</v>
+        <v>469364</v>
       </c>
       <c r="R19" t="n">
-        <v>7065001</v>
+        <v>7065232</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2527,6 +2532,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2535,21 +2545,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2566,10 +2561,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129060003</v>
+        <v>129059685</v>
       </c>
       <c r="B20" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,34 +2572,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469006</v>
+        <v>468878</v>
       </c>
       <c r="R20" t="n">
-        <v>7065358</v>
+        <v>7065401</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,6 +2637,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2663,10 +2668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129060039</v>
+        <v>129060038</v>
       </c>
       <c r="B21" t="n">
-        <v>80150</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,34 +2679,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469139</v>
+        <v>469007</v>
       </c>
       <c r="R21" t="n">
-        <v>7065094</v>
+        <v>7064930</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2760,10 +2770,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129060007</v>
+        <v>129060003</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2771,39 +2781,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469364</v>
+        <v>469006</v>
       </c>
       <c r="R22" t="n">
-        <v>7065232</v>
+        <v>7065358</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2836,11 +2841,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2867,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129059685</v>
+        <v>129059708</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>83017</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2878,39 +2878,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468878</v>
+        <v>468783</v>
       </c>
       <c r="R23" t="n">
-        <v>7065401</v>
+        <v>7065001</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2945,11 +2940,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2958,6 +2948,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -2974,10 +2979,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129060038</v>
+        <v>129060039</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>80150</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2985,39 +2990,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469007</v>
+        <v>469139</v>
       </c>
       <c r="R24" t="n">
-        <v>7064930</v>
+        <v>7065094</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129060013</v>
+        <v>129060010</v>
       </c>
       <c r="B25" t="n">
         <v>57727</v>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>469205</v>
+        <v>469310</v>
       </c>
       <c r="R25" t="n">
-        <v>7065283</v>
+        <v>7065244</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3183,7 +3183,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129060010</v>
+        <v>129060013</v>
       </c>
       <c r="B26" t="n">
         <v>57727</v>
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>469310</v>
+        <v>469205</v>
       </c>
       <c r="R26" t="n">
-        <v>7065244</v>
+        <v>7065283</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3290,32 +3290,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129060046</v>
+        <v>129060006</v>
       </c>
       <c r="B27" t="n">
-        <v>91549</v>
+        <v>92271</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469215</v>
+        <v>469045</v>
       </c>
       <c r="R27" t="n">
-        <v>7065278</v>
+        <v>7065011</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3387,45 +3387,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129060006</v>
+        <v>129060027</v>
       </c>
       <c r="B28" t="n">
-        <v>92271</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469045</v>
+        <v>468896</v>
       </c>
       <c r="R28" t="n">
-        <v>7065011</v>
+        <v>7064986</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3458,6 +3463,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3484,10 +3494,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129060048</v>
+        <v>129060035</v>
       </c>
       <c r="B29" t="n">
-        <v>91573</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3495,30 +3505,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469135</v>
+        <v>469149</v>
       </c>
       <c r="R29" t="n">
-        <v>7065166</v>
+        <v>7065169</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3577,10 +3600,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129060027</v>
+        <v>129060046</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3588,39 +3611,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>468896</v>
+        <v>469215</v>
       </c>
       <c r="R30" t="n">
-        <v>7064986</v>
+        <v>7065278</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3653,11 +3671,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3684,10 +3697,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129060035</v>
+        <v>129060048</v>
       </c>
       <c r="B31" t="n">
-        <v>57887</v>
+        <v>91573</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3695,43 +3708,30 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469149</v>
+        <v>469135</v>
       </c>
       <c r="R31" t="n">
-        <v>7065169</v>
+        <v>7065166</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3790,32 +3790,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129059691</v>
+        <v>129059690</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>83010</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468992</v>
+        <v>468887</v>
       </c>
       <c r="R32" t="n">
-        <v>7065224</v>
+        <v>7065318</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3887,10 +3887,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129059681</v>
+        <v>129059691</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3898,39 +3898,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>469043</v>
+        <v>468992</v>
       </c>
       <c r="R33" t="n">
-        <v>7065365</v>
+        <v>7065224</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3963,11 +3958,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3994,45 +3984,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129059690</v>
+        <v>129059681</v>
       </c>
       <c r="B34" t="n">
-        <v>83010</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>468887</v>
+        <v>469043</v>
       </c>
       <c r="R34" t="n">
-        <v>7065318</v>
+        <v>7065365</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4065,6 +4060,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4091,10 +4091,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129059694</v>
+        <v>129060009</v>
       </c>
       <c r="B35" t="n">
-        <v>83004</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4102,34 +4102,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>469141</v>
+        <v>469298</v>
       </c>
       <c r="R35" t="n">
-        <v>7065114</v>
+        <v>7065235</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4164,6 +4169,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4172,21 +4182,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>sälgticka</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Phellinopsis conchata</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4203,10 +4198,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129059700</v>
+        <v>129059694</v>
       </c>
       <c r="B36" t="n">
-        <v>80150</v>
+        <v>83004</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4214,21 +4209,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4238,10 +4233,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>469036</v>
+        <v>469141</v>
       </c>
       <c r="R36" t="n">
-        <v>7065082</v>
+        <v>7065114</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4287,17 +4282,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>sälgticka</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Phellinopsis conchata</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4315,10 +4310,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129060009</v>
+        <v>129059700</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4326,39 +4321,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>469298</v>
+        <v>469036</v>
       </c>
       <c r="R37" t="n">
-        <v>7065235</v>
+        <v>7065082</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4393,11 +4383,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4406,6 +4391,21 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4422,32 +4422,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129060001</v>
+        <v>129060002</v>
       </c>
       <c r="B38" t="n">
-        <v>91517</v>
+        <v>91553</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>468967</v>
+        <v>469031</v>
       </c>
       <c r="R38" t="n">
-        <v>7065256</v>
+        <v>7065017</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4519,32 +4519,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129060002</v>
+        <v>129060001</v>
       </c>
       <c r="B39" t="n">
-        <v>91553</v>
+        <v>91517</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4554,10 +4554,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>469031</v>
+        <v>468967</v>
       </c>
       <c r="R39" t="n">
-        <v>7065017</v>
+        <v>7065256</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4723,7 +4723,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129060026</v>
+        <v>129059715</v>
       </c>
       <c r="B41" t="n">
         <v>57727</v>
@@ -4763,10 +4763,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468886</v>
+        <v>469047</v>
       </c>
       <c r="R41" t="n">
-        <v>7065015</v>
+        <v>7064912</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4830,7 +4830,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129059715</v>
+        <v>129060026</v>
       </c>
       <c r="B42" t="n">
         <v>57727</v>
@@ -4870,10 +4870,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469047</v>
+        <v>468886</v>
       </c>
       <c r="R42" t="n">
-        <v>7064912</v>
+        <v>7065015</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5127,7 +5127,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129059699</v>
+        <v>129059703</v>
       </c>
       <c r="B45" t="n">
         <v>79044</v>
@@ -5162,10 +5162,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>469071</v>
+        <v>468883</v>
       </c>
       <c r="R45" t="n">
-        <v>7065075</v>
+        <v>7065026</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5224,10 +5224,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129060018</v>
+        <v>129059699</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5235,39 +5235,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469093</v>
+        <v>469071</v>
       </c>
       <c r="R46" t="n">
-        <v>7065345</v>
+        <v>7065075</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5300,11 +5295,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5331,7 +5321,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129060017</v>
+        <v>129060018</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5371,10 +5361,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>469122</v>
+        <v>469093</v>
       </c>
       <c r="R47" t="n">
-        <v>7065303</v>
+        <v>7065345</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5438,10 +5428,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129059703</v>
+        <v>129060017</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5449,34 +5439,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>468883</v>
+        <v>469122</v>
       </c>
       <c r="R48" t="n">
-        <v>7065026</v>
+        <v>7065303</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5509,6 +5504,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5647,32 +5647,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129059702</v>
+        <v>129060042</v>
       </c>
       <c r="B50" t="n">
-        <v>91553</v>
+        <v>80053</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>468889</v>
+        <v>469356</v>
       </c>
       <c r="R50" t="n">
-        <v>7065025</v>
+        <v>7065233</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5856,32 +5856,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129060042</v>
+        <v>129059702</v>
       </c>
       <c r="B52" t="n">
-        <v>80053</v>
+        <v>91553</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>469356</v>
+        <v>468889</v>
       </c>
       <c r="R52" t="n">
-        <v>7065233</v>
+        <v>7065025</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6167,10 +6167,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129060041</v>
+        <v>129060036</v>
       </c>
       <c r="B55" t="n">
-        <v>80150</v>
+        <v>57887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6178,34 +6178,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>469143</v>
+        <v>468801</v>
       </c>
       <c r="R55" t="n">
-        <v>7065030</v>
+        <v>7065038</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6264,10 +6269,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129060036</v>
+        <v>129060041</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>80150</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6275,39 +6280,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>468801</v>
+        <v>469143</v>
       </c>
       <c r="R56" t="n">
-        <v>7065038</v>
+        <v>7065030</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7193,10 +7193,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129059686</v>
+        <v>129059675</v>
       </c>
       <c r="B65" t="n">
-        <v>83007</v>
+        <v>91549</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7204,21 +7204,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>310</v>
+        <v>1108</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7228,10 +7228,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>468843</v>
+        <v>469197</v>
       </c>
       <c r="R65" t="n">
-        <v>7065390</v>
+        <v>7065308</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7274,21 +7274,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7305,10 +7290,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129059675</v>
+        <v>129059686</v>
       </c>
       <c r="B66" t="n">
-        <v>91549</v>
+        <v>83007</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7316,21 +7301,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1108</v>
+        <v>310</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7340,10 +7325,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>469197</v>
+        <v>468843</v>
       </c>
       <c r="R66" t="n">
-        <v>7065308</v>
+        <v>7065390</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7386,6 +7371,21 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -7601,10 +7601,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129059670</v>
+        <v>129059682</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7612,39 +7612,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>469326</v>
+        <v>468990</v>
       </c>
       <c r="R69" t="n">
-        <v>7065255</v>
+        <v>7065370</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7677,11 +7672,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7708,10 +7698,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129059682</v>
+        <v>129059670</v>
       </c>
       <c r="B70" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7719,34 +7709,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468990</v>
+        <v>469326</v>
       </c>
       <c r="R70" t="n">
-        <v>7065370</v>
+        <v>7065255</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7779,6 +7774,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8014,45 +8014,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129060047</v>
+        <v>129059714</v>
       </c>
       <c r="B73" t="n">
-        <v>91926</v>
+        <v>57727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>469012</v>
+        <v>468946</v>
       </c>
       <c r="R73" t="n">
-        <v>7065037</v>
+        <v>7064969</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8085,6 +8090,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8111,10 +8121,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129059698</v>
+        <v>129059701</v>
       </c>
       <c r="B74" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8122,34 +8132,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>469120</v>
+        <v>468991</v>
       </c>
       <c r="R74" t="n">
-        <v>7065078</v>
+        <v>7065056</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8184,6 +8199,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8192,21 +8212,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8223,32 +8228,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129060040</v>
+        <v>129060047</v>
       </c>
       <c r="B75" t="n">
-        <v>80150</v>
+        <v>91926</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8258,10 +8263,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>469148</v>
+        <v>469012</v>
       </c>
       <c r="R75" t="n">
-        <v>7065056</v>
+        <v>7065037</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8320,10 +8325,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129059714</v>
+        <v>129059698</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8331,39 +8336,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>468946</v>
+        <v>469120</v>
       </c>
       <c r="R76" t="n">
-        <v>7064969</v>
+        <v>7065078</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8398,11 +8398,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8411,6 +8406,21 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8427,10 +8437,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129059701</v>
+        <v>129060040</v>
       </c>
       <c r="B77" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8438,36 +8448,31 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>468991</v>
+        <v>469148</v>
       </c>
       <c r="R77" t="n">
         <v>7065056</v>
@@ -8503,11 +8508,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8631,7 +8631,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129059680</v>
+        <v>129060016</v>
       </c>
       <c r="B79" t="n">
         <v>57727</v>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>469094</v>
+        <v>469152</v>
       </c>
       <c r="R79" t="n">
-        <v>7065363</v>
+        <v>7065299</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8738,7 +8738,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129060016</v>
+        <v>129060014</v>
       </c>
       <c r="B80" t="n">
         <v>57727</v>
@@ -8769,7 +8769,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -8778,10 +8778,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>469152</v>
+        <v>469198</v>
       </c>
       <c r="R80" t="n">
-        <v>7065299</v>
+        <v>7065284</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8845,7 +8845,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129060014</v>
+        <v>129059680</v>
       </c>
       <c r="B81" t="n">
         <v>57727</v>
@@ -8876,7 +8876,7 @@
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -8885,10 +8885,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>469198</v>
+        <v>469094</v>
       </c>
       <c r="R81" t="n">
-        <v>7065284</v>
+        <v>7065363</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8952,10 +8952,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129059676</v>
+        <v>129059696</v>
       </c>
       <c r="B82" t="n">
-        <v>83012</v>
+        <v>91573</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8963,23 +8963,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -8987,10 +8983,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>469160</v>
+        <v>469141</v>
       </c>
       <c r="R82" t="n">
-        <v>7065329</v>
+        <v>7065095</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9049,10 +9045,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129059712</v>
+        <v>129059692</v>
       </c>
       <c r="B83" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9060,34 +9056,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>468868</v>
+        <v>469137</v>
       </c>
       <c r="R83" t="n">
-        <v>7064989</v>
+        <v>7065206</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9120,6 +9121,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9146,10 +9152,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129059706</v>
+        <v>129059679</v>
       </c>
       <c r="B84" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9157,34 +9163,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>468850</v>
+        <v>469108</v>
       </c>
       <c r="R84" t="n">
-        <v>7065034</v>
+        <v>7065364</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9219,6 +9230,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9227,21 +9243,6 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -9258,10 +9259,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129059696</v>
+        <v>129059713</v>
       </c>
       <c r="B85" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9269,30 +9270,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>469141</v>
+        <v>468922</v>
       </c>
       <c r="R85" t="n">
-        <v>7065095</v>
+        <v>7064998</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9325,6 +9335,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9351,10 +9366,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129059679</v>
+        <v>129059706</v>
       </c>
       <c r="B86" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9362,39 +9377,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>469108</v>
+        <v>468850</v>
       </c>
       <c r="R86" t="n">
-        <v>7065364</v>
+        <v>7065034</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9429,11 +9439,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9442,6 +9447,21 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -9458,10 +9478,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129059713</v>
+        <v>129059676</v>
       </c>
       <c r="B87" t="n">
-        <v>57727</v>
+        <v>83012</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9469,39 +9489,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>468922</v>
+        <v>469160</v>
       </c>
       <c r="R87" t="n">
-        <v>7064998</v>
+        <v>7065329</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9534,11 +9549,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9565,10 +9575,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129059692</v>
+        <v>129059712</v>
       </c>
       <c r="B88" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9576,39 +9586,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>469137</v>
+        <v>468868</v>
       </c>
       <c r="R88" t="n">
-        <v>7065206</v>
+        <v>7064989</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9641,11 +9646,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129059710</v>
+        <v>129060044</v>
       </c>
       <c r="B2" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468844</v>
+        <v>469111</v>
       </c>
       <c r="R2" t="n">
-        <v>7064978</v>
+        <v>7065086</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,21 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129060023</v>
+        <v>129059711</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469142</v>
+        <v>468844</v>
       </c>
       <c r="R3" t="n">
-        <v>7065079</v>
+        <v>7064978</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,11 +845,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -878,6 +853,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -894,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129060033</v>
+        <v>129059710</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,39 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469047</v>
+        <v>468844</v>
       </c>
       <c r="R4" t="n">
-        <v>7064905</v>
+        <v>7064978</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,11 +957,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -985,6 +965,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1001,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129060008</v>
+        <v>129059689</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469327</v>
+        <v>468887</v>
       </c>
       <c r="R5" t="n">
-        <v>7065224</v>
+        <v>7065318</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129060024</v>
+        <v>129059683</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,39 +1104,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469131</v>
+        <v>468964</v>
       </c>
       <c r="R6" t="n">
-        <v>7065083</v>
+        <v>7065331</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129060012</v>
+        <v>129060024</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1246,7 +1221,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1255,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469235</v>
+        <v>469131</v>
       </c>
       <c r="R7" t="n">
-        <v>7065256</v>
+        <v>7065083</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129060020</v>
+        <v>129060012</v>
       </c>
       <c r="B8" t="n">
         <v>57727</v>
@@ -1362,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468803</v>
+        <v>469235</v>
       </c>
       <c r="R8" t="n">
-        <v>7065369</v>
+        <v>7065256</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129059689</v>
+        <v>129060023</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,34 +1415,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468887</v>
+        <v>469142</v>
       </c>
       <c r="R9" t="n">
-        <v>7065318</v>
+        <v>7065079</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,6 +1480,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129059683</v>
+        <v>129060033</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1537,34 +1522,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468964</v>
+        <v>469047</v>
       </c>
       <c r="R10" t="n">
-        <v>7065331</v>
+        <v>7064905</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1587,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129060044</v>
+        <v>129060008</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1634,34 +1629,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469111</v>
+        <v>469327</v>
       </c>
       <c r="R11" t="n">
-        <v>7065086</v>
+        <v>7065224</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,6 +1694,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129059711</v>
+        <v>129060020</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,34 +1736,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468844</v>
+        <v>468803</v>
       </c>
       <c r="R12" t="n">
-        <v>7064978</v>
+        <v>7065369</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1793,6 +1803,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1801,21 +1816,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129059695</v>
+        <v>129060007</v>
       </c>
       <c r="B18" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,34 +2353,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469141</v>
+        <v>469364</v>
       </c>
       <c r="R18" t="n">
-        <v>7065114</v>
+        <v>7065232</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2415,6 +2420,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2423,21 +2433,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2454,7 +2449,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129060007</v>
+        <v>129059685</v>
       </c>
       <c r="B19" t="n">
         <v>57727</v>
@@ -2494,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>469364</v>
+        <v>468878</v>
       </c>
       <c r="R19" t="n">
-        <v>7065232</v>
+        <v>7065401</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2561,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129059685</v>
+        <v>129060039</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2572,39 +2567,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468878</v>
+        <v>469139</v>
       </c>
       <c r="R20" t="n">
-        <v>7065401</v>
+        <v>7065094</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,11 +2627,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2668,10 +2653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129060038</v>
+        <v>129059695</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>80149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2679,39 +2664,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469007</v>
+        <v>469141</v>
       </c>
       <c r="R21" t="n">
-        <v>7064930</v>
+        <v>7065114</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2754,6 +2734,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2770,10 +2765,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129060003</v>
+        <v>129059708</v>
       </c>
       <c r="B22" t="n">
-        <v>91553</v>
+        <v>83017</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2781,21 +2776,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2805,10 +2800,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>469006</v>
+        <v>468783</v>
       </c>
       <c r="R22" t="n">
-        <v>7065358</v>
+        <v>7065001</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2851,6 +2846,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2867,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129059708</v>
+        <v>129060003</v>
       </c>
       <c r="B23" t="n">
-        <v>83017</v>
+        <v>91553</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2878,21 +2888,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2902,10 +2912,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468783</v>
+        <v>469006</v>
       </c>
       <c r="R23" t="n">
-        <v>7065001</v>
+        <v>7065358</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,21 +2958,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -2979,10 +2974,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129060039</v>
+        <v>129060038</v>
       </c>
       <c r="B24" t="n">
-        <v>80150</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2990,34 +2985,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469139</v>
+        <v>469007</v>
       </c>
       <c r="R24" t="n">
-        <v>7065094</v>
+        <v>7064930</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129060010</v>
+        <v>129060013</v>
       </c>
       <c r="B25" t="n">
         <v>57727</v>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>469310</v>
+        <v>469205</v>
       </c>
       <c r="R25" t="n">
-        <v>7065244</v>
+        <v>7065283</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3183,7 +3183,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129060013</v>
+        <v>129060010</v>
       </c>
       <c r="B26" t="n">
         <v>57727</v>
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>469205</v>
+        <v>469310</v>
       </c>
       <c r="R26" t="n">
-        <v>7065283</v>
+        <v>7065244</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3290,34 +3290,30 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129060006</v>
+        <v>129060048</v>
       </c>
       <c r="B27" t="n">
-        <v>92271</v>
+        <v>91573</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3325,10 +3321,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469045</v>
+        <v>469135</v>
       </c>
       <c r="R27" t="n">
-        <v>7065011</v>
+        <v>7065166</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3387,50 +3383,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129060027</v>
+        <v>129060006</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>92271</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>468896</v>
+        <v>469045</v>
       </c>
       <c r="R28" t="n">
-        <v>7064986</v>
+        <v>7065011</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3463,11 +3454,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3494,10 +3480,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129060035</v>
+        <v>129060027</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3505,31 +3491,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3538,10 +3520,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469149</v>
+        <v>468896</v>
       </c>
       <c r="R29" t="n">
-        <v>7065169</v>
+        <v>7064986</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3574,6 +3556,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3697,10 +3684,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129060048</v>
+        <v>129060035</v>
       </c>
       <c r="B31" t="n">
-        <v>91573</v>
+        <v>57887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3708,30 +3695,43 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469135</v>
+        <v>469149</v>
       </c>
       <c r="R31" t="n">
-        <v>7065166</v>
+        <v>7065169</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4091,10 +4091,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129060009</v>
+        <v>129059700</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4102,39 +4102,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>469298</v>
+        <v>469036</v>
       </c>
       <c r="R35" t="n">
-        <v>7065235</v>
+        <v>7065082</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4169,11 +4164,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4182,6 +4172,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4310,10 +4315,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129059700</v>
+        <v>129060009</v>
       </c>
       <c r="B37" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4321,34 +4326,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>469036</v>
+        <v>469298</v>
       </c>
       <c r="R37" t="n">
-        <v>7065082</v>
+        <v>7065235</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4383,6 +4393,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4391,21 +4406,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4422,10 +4422,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129060002</v>
+        <v>129059684</v>
       </c>
       <c r="B38" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4433,34 +4433,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>469031</v>
+        <v>468895</v>
       </c>
       <c r="R38" t="n">
-        <v>7065017</v>
+        <v>7065399</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4493,6 +4498,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4519,45 +4529,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129060001</v>
+        <v>129060026</v>
       </c>
       <c r="B39" t="n">
-        <v>91517</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468967</v>
+        <v>468886</v>
       </c>
       <c r="R39" t="n">
-        <v>7065256</v>
+        <v>7065015</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4590,6 +4605,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4616,7 +4636,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129059684</v>
+        <v>129059715</v>
       </c>
       <c r="B40" t="n">
         <v>57727</v>
@@ -4656,10 +4676,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>468895</v>
+        <v>469047</v>
       </c>
       <c r="R40" t="n">
-        <v>7065399</v>
+        <v>7064912</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4723,50 +4743,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129059715</v>
+        <v>129060001</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>469047</v>
+        <v>468967</v>
       </c>
       <c r="R41" t="n">
-        <v>7064912</v>
+        <v>7065256</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4799,11 +4814,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4830,10 +4840,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129060026</v>
+        <v>129060002</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4841,39 +4851,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>468886</v>
+        <v>469031</v>
       </c>
       <c r="R42" t="n">
-        <v>7065015</v>
+        <v>7065017</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4906,11 +4911,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5034,10 +5034,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129060049</v>
+        <v>129059703</v>
       </c>
       <c r="B44" t="n">
-        <v>91573</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5045,19 +5045,23 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5065,10 +5069,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>469012</v>
+        <v>468883</v>
       </c>
       <c r="R44" t="n">
-        <v>7065037</v>
+        <v>7065026</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5127,7 +5131,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129059703</v>
+        <v>129059699</v>
       </c>
       <c r="B45" t="n">
         <v>79044</v>
@@ -5162,10 +5166,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>468883</v>
+        <v>469071</v>
       </c>
       <c r="R45" t="n">
-        <v>7065026</v>
+        <v>7065075</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5224,10 +5228,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129059699</v>
+        <v>129060049</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>91573</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5235,23 +5239,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469071</v>
+        <v>469012</v>
       </c>
       <c r="R46" t="n">
-        <v>7065075</v>
+        <v>7065037</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5647,32 +5647,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129060042</v>
+        <v>129059709</v>
       </c>
       <c r="B50" t="n">
-        <v>80053</v>
+        <v>83007</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6456</v>
+        <v>310</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>469356</v>
+        <v>468844</v>
       </c>
       <c r="R50" t="n">
-        <v>7065233</v>
+        <v>7064978</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5728,6 +5728,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5744,32 +5759,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129059709</v>
+        <v>129060042</v>
       </c>
       <c r="B51" t="n">
-        <v>83007</v>
+        <v>80053</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>310</v>
+        <v>6456</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5779,10 +5794,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>468844</v>
+        <v>469356</v>
       </c>
       <c r="R51" t="n">
-        <v>7064978</v>
+        <v>7065233</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5825,21 +5840,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6167,10 +6167,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129060036</v>
+        <v>129060041</v>
       </c>
       <c r="B55" t="n">
-        <v>57887</v>
+        <v>80150</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6178,39 +6178,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>468801</v>
+        <v>469143</v>
       </c>
       <c r="R55" t="n">
-        <v>7065038</v>
+        <v>7065030</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6269,10 +6264,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129060041</v>
+        <v>129060036</v>
       </c>
       <c r="B56" t="n">
-        <v>80150</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6280,34 +6275,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>469143</v>
+        <v>468801</v>
       </c>
       <c r="R56" t="n">
-        <v>7065030</v>
+        <v>7065038</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6366,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129060005</v>
+        <v>129060032</v>
       </c>
       <c r="B57" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6377,34 +6377,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>468821</v>
+        <v>469043</v>
       </c>
       <c r="R57" t="n">
-        <v>7065043</v>
+        <v>7064905</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6437,6 +6442,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6556,10 +6566,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129060032</v>
+        <v>129060005</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6567,39 +6577,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>469043</v>
+        <v>468821</v>
       </c>
       <c r="R59" t="n">
-        <v>7064905</v>
+        <v>7065043</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6632,11 +6637,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6663,10 +6663,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129059687</v>
+        <v>129059674</v>
       </c>
       <c r="B60" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6674,21 +6674,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6698,10 +6698,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>468843</v>
+        <v>469226</v>
       </c>
       <c r="R60" t="n">
-        <v>7065390</v>
+        <v>7065299</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6744,21 +6744,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6872,10 +6857,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129060029</v>
+        <v>129059675</v>
       </c>
       <c r="B62" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6883,39 +6868,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468970</v>
+        <v>469197</v>
       </c>
       <c r="R62" t="n">
-        <v>7064946</v>
+        <v>7065308</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6948,11 +6928,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6979,10 +6954,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129060021</v>
+        <v>129059687</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6990,39 +6965,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>468788</v>
+        <v>468843</v>
       </c>
       <c r="R63" t="n">
-        <v>7065344</v>
+        <v>7065390</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7057,11 +7027,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7070,6 +7035,21 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7086,10 +7066,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129060025</v>
+        <v>129059686</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>83007</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7097,39 +7077,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>310</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>469101</v>
+        <v>468843</v>
       </c>
       <c r="R64" t="n">
-        <v>7065026</v>
+        <v>7065390</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7164,11 +7139,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7177,6 +7147,21 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7193,10 +7178,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129059675</v>
+        <v>129060050</v>
       </c>
       <c r="B65" t="n">
-        <v>91549</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7204,21 +7189,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7228,10 +7213,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>469197</v>
+        <v>469118</v>
       </c>
       <c r="R65" t="n">
-        <v>7065308</v>
+        <v>7065190</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7264,6 +7249,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7290,10 +7280,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129059686</v>
+        <v>129060029</v>
       </c>
       <c r="B66" t="n">
-        <v>83007</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7301,34 +7291,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468843</v>
+        <v>468970</v>
       </c>
       <c r="R66" t="n">
-        <v>7065390</v>
+        <v>7064946</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7363,6 +7358,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7371,21 +7371,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -7402,10 +7387,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129059674</v>
+        <v>129060021</v>
       </c>
       <c r="B67" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7413,34 +7398,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>469226</v>
+        <v>468788</v>
       </c>
       <c r="R67" t="n">
-        <v>7065299</v>
+        <v>7065344</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7473,6 +7463,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7499,10 +7494,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129060050</v>
+        <v>129060025</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7510,34 +7505,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>469118</v>
+        <v>469101</v>
       </c>
       <c r="R68" t="n">
-        <v>7065190</v>
+        <v>7065026</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7805,10 +7805,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129060051</v>
+        <v>129060011</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7816,34 +7816,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>469121</v>
+        <v>469245</v>
       </c>
       <c r="R71" t="n">
-        <v>7064885</v>
+        <v>7065256</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7880,7 +7885,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Med apotechier</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7907,10 +7912,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129060011</v>
+        <v>129060051</v>
       </c>
       <c r="B72" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7918,39 +7923,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>469245</v>
+        <v>469121</v>
       </c>
       <c r="R72" t="n">
-        <v>7065256</v>
+        <v>7064885</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7987,7 +7987,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8014,10 +8014,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129059714</v>
+        <v>129059677</v>
       </c>
       <c r="B73" t="n">
-        <v>57727</v>
+        <v>78057</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8025,39 +8025,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>468946</v>
+        <v>469160</v>
       </c>
       <c r="R73" t="n">
-        <v>7064969</v>
+        <v>7065329</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8090,11 +8085,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8121,10 +8111,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129059701</v>
+        <v>129059698</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8132,39 +8122,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>468991</v>
+        <v>469120</v>
       </c>
       <c r="R74" t="n">
-        <v>7065056</v>
+        <v>7065078</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8199,11 +8184,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8212,6 +8192,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8228,45 +8223,50 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129060047</v>
+        <v>129059714</v>
       </c>
       <c r="B75" t="n">
-        <v>91926</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>469012</v>
+        <v>468946</v>
       </c>
       <c r="R75" t="n">
-        <v>7065037</v>
+        <v>7064969</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8299,6 +8299,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8325,10 +8330,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129059698</v>
+        <v>129059701</v>
       </c>
       <c r="B76" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8336,34 +8341,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>469120</v>
+        <v>468991</v>
       </c>
       <c r="R76" t="n">
-        <v>7065078</v>
+        <v>7065056</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8398,6 +8408,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8406,21 +8421,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8437,32 +8437,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129060040</v>
+        <v>129060047</v>
       </c>
       <c r="B77" t="n">
-        <v>80150</v>
+        <v>91926</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8472,10 +8472,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>469148</v>
+        <v>469012</v>
       </c>
       <c r="R77" t="n">
-        <v>7065056</v>
+        <v>7065037</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8534,10 +8534,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129059677</v>
+        <v>129060040</v>
       </c>
       <c r="B78" t="n">
-        <v>78057</v>
+        <v>80150</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8545,21 +8545,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>469160</v>
+        <v>469148</v>
       </c>
       <c r="R78" t="n">
-        <v>7065329</v>
+        <v>7065056</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8631,7 +8631,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129060016</v>
+        <v>129059680</v>
       </c>
       <c r="B79" t="n">
         <v>57727</v>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>469152</v>
+        <v>469094</v>
       </c>
       <c r="R79" t="n">
-        <v>7065299</v>
+        <v>7065363</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8738,7 +8738,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129060014</v>
+        <v>129060016</v>
       </c>
       <c r="B80" t="n">
         <v>57727</v>
@@ -8769,7 +8769,7 @@
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -8778,10 +8778,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>469198</v>
+        <v>469152</v>
       </c>
       <c r="R80" t="n">
-        <v>7065284</v>
+        <v>7065299</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8845,7 +8845,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129059680</v>
+        <v>129060014</v>
       </c>
       <c r="B81" t="n">
         <v>57727</v>
@@ -8876,7 +8876,7 @@
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -8885,10 +8885,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>469094</v>
+        <v>469198</v>
       </c>
       <c r="R81" t="n">
-        <v>7065363</v>
+        <v>7065284</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8952,10 +8952,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129059696</v>
+        <v>129059676</v>
       </c>
       <c r="B82" t="n">
-        <v>91573</v>
+        <v>83012</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8963,19 +8963,23 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -8983,10 +8987,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>469141</v>
+        <v>469160</v>
       </c>
       <c r="R82" t="n">
-        <v>7065095</v>
+        <v>7065329</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9045,10 +9049,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129059692</v>
+        <v>129059712</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9056,39 +9060,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>469137</v>
+        <v>468868</v>
       </c>
       <c r="R83" t="n">
-        <v>7065206</v>
+        <v>7064989</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9121,11 +9120,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9152,10 +9146,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129059679</v>
+        <v>129059706</v>
       </c>
       <c r="B84" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9163,39 +9157,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>469108</v>
+        <v>468850</v>
       </c>
       <c r="R84" t="n">
-        <v>7065364</v>
+        <v>7065034</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9230,11 +9219,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9243,6 +9227,21 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -9259,10 +9258,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129059713</v>
+        <v>129059696</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9270,39 +9269,30 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>468922</v>
+        <v>469141</v>
       </c>
       <c r="R85" t="n">
-        <v>7064998</v>
+        <v>7065095</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9335,11 +9325,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9366,10 +9351,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129059706</v>
+        <v>129059679</v>
       </c>
       <c r="B86" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9377,34 +9362,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>468850</v>
+        <v>469108</v>
       </c>
       <c r="R86" t="n">
-        <v>7065034</v>
+        <v>7065364</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9439,6 +9429,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9447,21 +9442,6 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -9478,10 +9458,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129059676</v>
+        <v>129059713</v>
       </c>
       <c r="B87" t="n">
-        <v>83012</v>
+        <v>57727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9489,34 +9469,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>469160</v>
+        <v>468922</v>
       </c>
       <c r="R87" t="n">
-        <v>7065329</v>
+        <v>7064998</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9549,6 +9534,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9575,10 +9565,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129059712</v>
+        <v>129059692</v>
       </c>
       <c r="B88" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9586,34 +9576,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>468868</v>
+        <v>469137</v>
       </c>
       <c r="R88" t="n">
-        <v>7064989</v>
+        <v>7065206</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9646,6 +9641,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -1193,7 +1193,7 @@
         <v>129060024</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>129060012</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>129060023</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>129060033</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>129060008</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>129060020</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>129060015</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>129060022</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>129060007</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>129059685</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>129060013</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>129060010</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>129060027</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>129059681</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>129060009</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>129059684</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>129060026</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>129059715</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>129060018</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>129060017</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>129059704</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>129060031</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>129060032</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>129060029</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         <v>129060021</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>129060025</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>129059670</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>129060011</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>129059714</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>129059701</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>129059680</v>
       </c>
       <c r="B79" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>129060016</v>
       </c>
       <c r="B80" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>129060014</v>
       </c>
       <c r="B81" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>129059679</v>
       </c>
       <c r="B86" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>129059713</v>
       </c>
       <c r="B87" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>129059692</v>
       </c>
       <c r="B88" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -1193,7 +1193,7 @@
         <v>129060024</v>
       </c>
       <c r="B7" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>129060012</v>
       </c>
       <c r="B8" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>129060023</v>
       </c>
       <c r="B9" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>129060033</v>
       </c>
       <c r="B10" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>129060008</v>
       </c>
       <c r="B11" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>129060020</v>
       </c>
       <c r="B12" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>129060015</v>
       </c>
       <c r="B14" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>129060022</v>
       </c>
       <c r="B17" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>129060007</v>
       </c>
       <c r="B18" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>129059685</v>
       </c>
       <c r="B19" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>129060013</v>
       </c>
       <c r="B25" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>129060010</v>
       </c>
       <c r="B26" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>129060027</v>
       </c>
       <c r="B29" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>129059681</v>
       </c>
       <c r="B34" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>129060009</v>
       </c>
       <c r="B37" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>129059684</v>
       </c>
       <c r="B38" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>129060026</v>
       </c>
       <c r="B39" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>129059715</v>
       </c>
       <c r="B40" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>129060018</v>
       </c>
       <c r="B47" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>129060017</v>
       </c>
       <c r="B48" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>129059704</v>
       </c>
       <c r="B53" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>129060031</v>
       </c>
       <c r="B54" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>129060032</v>
       </c>
       <c r="B57" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>129060029</v>
       </c>
       <c r="B66" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         <v>129060021</v>
       </c>
       <c r="B67" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>129060025</v>
       </c>
       <c r="B68" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>129059670</v>
       </c>
       <c r="B70" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>129060011</v>
       </c>
       <c r="B71" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>129059714</v>
       </c>
       <c r="B75" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>129059701</v>
       </c>
       <c r="B76" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>129059680</v>
       </c>
       <c r="B79" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>129060016</v>
       </c>
       <c r="B80" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>129060014</v>
       </c>
       <c r="B81" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>129059679</v>
       </c>
       <c r="B86" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>129059713</v>
       </c>
       <c r="B87" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>129059692</v>
       </c>
       <c r="B88" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -1193,7 +1193,7 @@
         <v>129060024</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>129060012</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>129060023</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>129060033</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>129060008</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>129060020</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>129060015</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>129060022</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>129060007</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>129059685</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>129060013</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>129060010</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>129060027</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>129059681</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>129060009</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>129059684</v>
       </c>
       <c r="B38" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>129060026</v>
       </c>
       <c r="B39" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>129059715</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>129060018</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>129060017</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>129059704</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>129060031</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>129060032</v>
       </c>
       <c r="B57" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>129060029</v>
       </c>
       <c r="B66" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         <v>129060021</v>
       </c>
       <c r="B67" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>129060025</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>129059670</v>
       </c>
       <c r="B70" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>129060011</v>
       </c>
       <c r="B71" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>129059714</v>
       </c>
       <c r="B75" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>129059701</v>
       </c>
       <c r="B76" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>129059680</v>
       </c>
       <c r="B79" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>129060016</v>
       </c>
       <c r="B80" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>129060014</v>
       </c>
       <c r="B81" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>129059679</v>
       </c>
       <c r="B86" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>129059713</v>
       </c>
       <c r="B87" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>129059692</v>
       </c>
       <c r="B88" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -1193,7 +1193,7 @@
         <v>129060024</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>129060012</v>
       </c>
       <c r="B8" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>129060023</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>129060033</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>129060008</v>
       </c>
       <c r="B11" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>129060020</v>
       </c>
       <c r="B12" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>129060015</v>
       </c>
       <c r="B14" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>129060022</v>
       </c>
       <c r="B17" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>129060007</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>129059685</v>
       </c>
       <c r="B19" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>129060013</v>
       </c>
       <c r="B25" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>129060010</v>
       </c>
       <c r="B26" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>129060027</v>
       </c>
       <c r="B29" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>129059681</v>
       </c>
       <c r="B34" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>129060009</v>
       </c>
       <c r="B37" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>129059684</v>
       </c>
       <c r="B38" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>129060026</v>
       </c>
       <c r="B39" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>129059715</v>
       </c>
       <c r="B40" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>129060018</v>
       </c>
       <c r="B47" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>129060017</v>
       </c>
       <c r="B48" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>129059704</v>
       </c>
       <c r="B53" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>129060031</v>
       </c>
       <c r="B54" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>129060032</v>
       </c>
       <c r="B57" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>129060029</v>
       </c>
       <c r="B66" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         <v>129060021</v>
       </c>
       <c r="B67" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>129060025</v>
       </c>
       <c r="B68" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>129059670</v>
       </c>
       <c r="B70" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>129060011</v>
       </c>
       <c r="B71" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>129059714</v>
       </c>
       <c r="B75" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>129059701</v>
       </c>
       <c r="B76" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>129059680</v>
       </c>
       <c r="B79" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>129060016</v>
       </c>
       <c r="B80" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>129060014</v>
       </c>
       <c r="B81" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>129059679</v>
       </c>
       <c r="B86" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>129059713</v>
       </c>
       <c r="B87" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>129059692</v>
       </c>
       <c r="B88" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AY84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129060044</v>
+        <v>129059694</v>
       </c>
       <c r="B2" t="n">
-        <v>80149</v>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469111</v>
+        <v>469141</v>
       </c>
       <c r="R2" t="n">
-        <v>7065086</v>
+        <v>7065114</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,6 +756,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälgticka</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Phellinopsis conchata</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -772,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129059711</v>
+        <v>129059686</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>83302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468844</v>
+        <v>468843</v>
       </c>
       <c r="R3" t="n">
-        <v>7064978</v>
+        <v>7065390</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129059710</v>
+        <v>129059709</v>
       </c>
       <c r="B4" t="n">
-        <v>80150</v>
+        <v>83302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -996,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129059689</v>
+        <v>129059675</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468887</v>
+        <v>469197</v>
       </c>
       <c r="R5" t="n">
-        <v>7065318</v>
+        <v>7065308</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129059683</v>
+        <v>129060046</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468964</v>
+        <v>469215</v>
       </c>
       <c r="R6" t="n">
-        <v>7065331</v>
+        <v>7065278</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129060024</v>
+        <v>129059682</v>
       </c>
       <c r="B7" t="n">
-        <v>57740</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,39 +1216,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469131</v>
+        <v>468990</v>
       </c>
       <c r="R7" t="n">
-        <v>7065083</v>
+        <v>7065370</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129060012</v>
+        <v>129059702</v>
       </c>
       <c r="B8" t="n">
-        <v>57740</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,39 +1313,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469235</v>
+        <v>468889</v>
       </c>
       <c r="R8" t="n">
-        <v>7065256</v>
+        <v>7065025</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,11 +1373,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129060023</v>
+        <v>129060002</v>
       </c>
       <c r="B9" t="n">
-        <v>57740</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,39 +1410,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469142</v>
+        <v>469031</v>
       </c>
       <c r="R9" t="n">
-        <v>7065079</v>
+        <v>7065017</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,11 +1470,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129060033</v>
+        <v>129060003</v>
       </c>
       <c r="B10" t="n">
-        <v>57740</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,39 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469047</v>
+        <v>469006</v>
       </c>
       <c r="R10" t="n">
-        <v>7064905</v>
+        <v>7065358</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,11 +1567,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129060008</v>
+        <v>129060005</v>
       </c>
       <c r="B11" t="n">
-        <v>57740</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,39 +1604,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469327</v>
+        <v>468821</v>
       </c>
       <c r="R11" t="n">
-        <v>7065224</v>
+        <v>7065043</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,11 +1664,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129060020</v>
+        <v>129059708</v>
       </c>
       <c r="B12" t="n">
-        <v>57740</v>
+        <v>83312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,39 +1701,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468803</v>
+        <v>468783</v>
       </c>
       <c r="R12" t="n">
-        <v>7065369</v>
+        <v>7065001</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1803,11 +1763,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1816,6 +1771,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1832,32 +1802,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129059678</v>
+        <v>129060047</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>92283</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2063</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469160</v>
+        <v>469012</v>
       </c>
       <c r="R13" t="n">
-        <v>7065329</v>
+        <v>7065037</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129060015</v>
+        <v>129059687</v>
       </c>
       <c r="B14" t="n">
-        <v>57740</v>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1940,39 +1910,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469142</v>
+        <v>468843</v>
       </c>
       <c r="R14" t="n">
-        <v>7065300</v>
+        <v>7065390</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2007,11 +1972,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2020,6 +1980,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2036,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129060037</v>
+        <v>129059698</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,39 +2022,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468874</v>
+        <v>469120</v>
       </c>
       <c r="R15" t="n">
-        <v>7064975</v>
+        <v>7065078</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,6 +2092,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2138,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129060045</v>
+        <v>129059700</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2173,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469013</v>
+        <v>469036</v>
       </c>
       <c r="R16" t="n">
-        <v>7065018</v>
+        <v>7065082</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,6 +2204,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2235,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129060022</v>
+        <v>129059706</v>
       </c>
       <c r="B17" t="n">
-        <v>57740</v>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,39 +2246,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468893</v>
+        <v>468850</v>
       </c>
       <c r="R17" t="n">
-        <v>7065289</v>
+        <v>7065034</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2313,11 +2308,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2326,6 +2316,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2342,10 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129060007</v>
+        <v>129059710</v>
       </c>
       <c r="B18" t="n">
-        <v>57740</v>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,39 +2358,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>469364</v>
+        <v>468844</v>
       </c>
       <c r="R18" t="n">
-        <v>7065232</v>
+        <v>7064978</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2420,11 +2420,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2433,6 +2428,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2449,10 +2459,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129059685</v>
+        <v>129060039</v>
       </c>
       <c r="B19" t="n">
-        <v>57740</v>
+        <v>80433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2460,39 +2470,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468878</v>
+        <v>469139</v>
       </c>
       <c r="R19" t="n">
-        <v>7065401</v>
+        <v>7065094</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2525,11 +2530,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129060039</v>
+        <v>129060040</v>
       </c>
       <c r="B20" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>469139</v>
+        <v>469148</v>
       </c>
       <c r="R20" t="n">
-        <v>7065094</v>
+        <v>7065056</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,10 +2653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129059695</v>
+        <v>129060041</v>
       </c>
       <c r="B21" t="n">
-        <v>80149</v>
+        <v>80433</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2664,21 +2664,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>469141</v>
+        <v>469143</v>
       </c>
       <c r="R21" t="n">
-        <v>7065114</v>
+        <v>7065030</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,21 +2734,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2765,32 +2750,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129059708</v>
+        <v>129060006</v>
       </c>
       <c r="B22" t="n">
-        <v>83017</v>
+        <v>92632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1467</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2800,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468783</v>
+        <v>469045</v>
       </c>
       <c r="R22" t="n">
-        <v>7065001</v>
+        <v>7065011</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,21 +2831,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2877,32 +2847,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129060003</v>
+        <v>129060001</v>
       </c>
       <c r="B23" t="n">
-        <v>91553</v>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2912,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>469006</v>
+        <v>468967</v>
       </c>
       <c r="R23" t="n">
-        <v>7065358</v>
+        <v>7065256</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2974,50 +2944,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129060038</v>
+        <v>129059671</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>469007</v>
+        <v>469328</v>
       </c>
       <c r="R24" t="n">
-        <v>7064930</v>
+        <v>7065269</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3076,50 +3041,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129060013</v>
+        <v>129059674</v>
       </c>
       <c r="B25" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>469205</v>
+        <v>469226</v>
       </c>
       <c r="R25" t="n">
-        <v>7065283</v>
+        <v>7065299</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,11 +3112,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,50 +3138,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129060010</v>
+        <v>129059678</v>
       </c>
       <c r="B26" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>469310</v>
+        <v>469160</v>
       </c>
       <c r="R26" t="n">
-        <v>7065244</v>
+        <v>7065329</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3259,11 +3209,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3290,30 +3235,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129060048</v>
+        <v>129059683</v>
       </c>
       <c r="B27" t="n">
-        <v>91573</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3321,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469135</v>
+        <v>468964</v>
       </c>
       <c r="R27" t="n">
-        <v>7065166</v>
+        <v>7065331</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3383,32 +3332,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129060006</v>
+        <v>129059689</v>
       </c>
       <c r="B28" t="n">
-        <v>92271</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3418,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469045</v>
+        <v>468887</v>
       </c>
       <c r="R28" t="n">
-        <v>7065011</v>
+        <v>7065318</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3480,50 +3429,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129060027</v>
+        <v>129059691</v>
       </c>
       <c r="B29" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>468896</v>
+        <v>468992</v>
       </c>
       <c r="R29" t="n">
-        <v>7064986</v>
+        <v>7065224</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,11 +3500,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3587,32 +3526,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129060046</v>
+        <v>129059699</v>
       </c>
       <c r="B30" t="n">
-        <v>91549</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3622,10 +3561,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469215</v>
+        <v>469071</v>
       </c>
       <c r="R30" t="n">
-        <v>7065278</v>
+        <v>7065075</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3684,54 +3623,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129060035</v>
+        <v>129059703</v>
       </c>
       <c r="B31" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469149</v>
+        <v>468883</v>
       </c>
       <c r="R31" t="n">
-        <v>7065169</v>
+        <v>7065026</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3790,10 +3720,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129059690</v>
+        <v>129059712</v>
       </c>
       <c r="B32" t="n">
-        <v>83010</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3801,21 +3731,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3825,10 +3755,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468887</v>
+        <v>468868</v>
       </c>
       <c r="R32" t="n">
-        <v>7065318</v>
+        <v>7064989</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3887,14 +3817,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129059691</v>
+        <v>129060050</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3922,10 +3852,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>468992</v>
+        <v>469118</v>
       </c>
       <c r="R33" t="n">
-        <v>7065224</v>
+        <v>7065190</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3958,6 +3888,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3984,50 +3919,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129059681</v>
+        <v>129060051</v>
       </c>
       <c r="B34" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>469043</v>
+        <v>469121</v>
       </c>
       <c r="R34" t="n">
-        <v>7065365</v>
+        <v>7064885</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4064,7 +3994,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4091,32 +4021,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129059700</v>
+        <v>129060043</v>
       </c>
       <c r="B35" t="n">
-        <v>80150</v>
+        <v>75300</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6428</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4126,10 +4056,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>469036</v>
+        <v>469011</v>
       </c>
       <c r="R35" t="n">
-        <v>7065082</v>
+        <v>7065022</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4172,21 +4102,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4203,10 +4118,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129059694</v>
+        <v>129059676</v>
       </c>
       <c r="B36" t="n">
-        <v>83004</v>
+        <v>83307</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4214,21 +4129,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4238,10 +4153,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>469141</v>
+        <v>469160</v>
       </c>
       <c r="R36" t="n">
-        <v>7065114</v>
+        <v>7065329</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4284,21 +4199,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>sälgticka</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Phellinopsis conchata</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Hymeniet på död ticka # Phellinopsis conchata</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4315,50 +4215,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129060009</v>
+        <v>129060042</v>
       </c>
       <c r="B37" t="n">
-        <v>57740</v>
+        <v>80336</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>469298</v>
+        <v>469356</v>
       </c>
       <c r="R37" t="n">
-        <v>7065235</v>
+        <v>7065233</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4391,11 +4286,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4422,10 +4312,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129059684</v>
+        <v>129059695</v>
       </c>
       <c r="B38" t="n">
-        <v>57740</v>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4433,39 +4323,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>468895</v>
+        <v>469141</v>
       </c>
       <c r="R38" t="n">
-        <v>7065399</v>
+        <v>7065114</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4500,11 +4385,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4513,6 +4393,21 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4529,10 +4424,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129060026</v>
+        <v>129059697</v>
       </c>
       <c r="B39" t="n">
-        <v>57740</v>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4540,39 +4435,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468886</v>
+        <v>469114</v>
       </c>
       <c r="R39" t="n">
-        <v>7065015</v>
+        <v>7065083</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4607,11 +4497,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4620,6 +4505,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4636,10 +4536,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129059715</v>
+        <v>129059711</v>
       </c>
       <c r="B40" t="n">
-        <v>57740</v>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4647,39 +4547,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>469047</v>
+        <v>468844</v>
       </c>
       <c r="R40" t="n">
-        <v>7064912</v>
+        <v>7064978</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4714,11 +4609,6 @@
           <t>2025-10-11</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4727,6 +4617,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4743,32 +4648,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129060001</v>
+        <v>129060044</v>
       </c>
       <c r="B41" t="n">
-        <v>91517</v>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4778,10 +4683,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468967</v>
+        <v>469111</v>
       </c>
       <c r="R41" t="n">
-        <v>7065256</v>
+        <v>7065086</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4840,10 +4745,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129060002</v>
+        <v>129060045</v>
       </c>
       <c r="B42" t="n">
-        <v>91553</v>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4851,21 +4756,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4875,10 +4780,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>469031</v>
+        <v>469013</v>
       </c>
       <c r="R42" t="n">
-        <v>7065017</v>
+        <v>7065018</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4937,32 +4842,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129059671</v>
+        <v>129059690</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>83305</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4972,10 +4877,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>469328</v>
+        <v>468887</v>
       </c>
       <c r="R43" t="n">
-        <v>7065269</v>
+        <v>7065318</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5034,10 +4939,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129059703</v>
+        <v>129059670</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5045,34 +4950,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>468883</v>
+        <v>469326</v>
       </c>
       <c r="R44" t="n">
-        <v>7065026</v>
+        <v>7065255</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5105,6 +5015,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5131,10 +5046,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129059699</v>
+        <v>129059679</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5142,34 +5057,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>469071</v>
+        <v>469108</v>
       </c>
       <c r="R45" t="n">
-        <v>7065075</v>
+        <v>7065364</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5202,6 +5122,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5228,10 +5153,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129060049</v>
+        <v>129059680</v>
       </c>
       <c r="B46" t="n">
-        <v>91573</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5239,30 +5164,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>469012</v>
+        <v>469094</v>
       </c>
       <c r="R46" t="n">
-        <v>7065037</v>
+        <v>7065363</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5295,6 +5229,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5321,10 +5260,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129060018</v>
+        <v>129059681</v>
       </c>
       <c r="B47" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5361,10 +5300,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>469093</v>
+        <v>469043</v>
       </c>
       <c r="R47" t="n">
-        <v>7065345</v>
+        <v>7065365</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5428,10 +5367,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129060017</v>
+        <v>129059684</v>
       </c>
       <c r="B48" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5468,10 +5407,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>469122</v>
+        <v>468895</v>
       </c>
       <c r="R48" t="n">
-        <v>7065303</v>
+        <v>7065399</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5535,10 +5474,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129059697</v>
+        <v>129059685</v>
       </c>
       <c r="B49" t="n">
-        <v>80149</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5546,34 +5485,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>469114</v>
+        <v>468878</v>
       </c>
       <c r="R49" t="n">
-        <v>7065083</v>
+        <v>7065401</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5608,6 +5552,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5616,21 +5565,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5647,10 +5581,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129059709</v>
+        <v>129059692</v>
       </c>
       <c r="B50" t="n">
-        <v>83007</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5658,34 +5592,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>468844</v>
+        <v>469137</v>
       </c>
       <c r="R50" t="n">
-        <v>7064978</v>
+        <v>7065206</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5720,6 +5659,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5728,21 +5672,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5759,45 +5688,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129060042</v>
+        <v>129059701</v>
       </c>
       <c r="B51" t="n">
-        <v>80053</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>469356</v>
+        <v>468991</v>
       </c>
       <c r="R51" t="n">
-        <v>7065233</v>
+        <v>7065056</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5830,6 +5764,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5856,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129059702</v>
+        <v>129059704</v>
       </c>
       <c r="B52" t="n">
-        <v>91553</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5867,34 +5806,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>468889</v>
+        <v>468883</v>
       </c>
       <c r="R52" t="n">
-        <v>7065025</v>
+        <v>7065026</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5927,6 +5871,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5953,10 +5902,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129059704</v>
+        <v>129059713</v>
       </c>
       <c r="B53" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5993,10 +5942,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>468883</v>
+        <v>468922</v>
       </c>
       <c r="R53" t="n">
-        <v>7065026</v>
+        <v>7064998</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6060,10 +6009,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129060031</v>
+        <v>129059714</v>
       </c>
       <c r="B54" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6091,7 +6040,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6100,10 +6049,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>469014</v>
+        <v>468946</v>
       </c>
       <c r="R54" t="n">
-        <v>7064913</v>
+        <v>7064969</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6167,10 +6116,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129060041</v>
+        <v>129059715</v>
       </c>
       <c r="B55" t="n">
-        <v>80150</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6178,34 +6127,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>469143</v>
+        <v>469047</v>
       </c>
       <c r="R55" t="n">
-        <v>7065030</v>
+        <v>7064912</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6238,6 +6192,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6264,10 +6223,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129060036</v>
+        <v>129060007</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6275,27 +6234,27 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6304,10 +6263,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>468801</v>
+        <v>469364</v>
       </c>
       <c r="R56" t="n">
-        <v>7065038</v>
+        <v>7065232</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6340,6 +6299,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6366,10 +6330,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129060032</v>
+        <v>129060008</v>
       </c>
       <c r="B57" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6406,10 +6370,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>469043</v>
+        <v>469327</v>
       </c>
       <c r="R57" t="n">
-        <v>7064905</v>
+        <v>7065224</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6473,10 +6437,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129059693</v>
+        <v>129060009</v>
       </c>
       <c r="B58" t="n">
-        <v>91573</v>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6484,30 +6448,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>469137</v>
+        <v>469298</v>
       </c>
       <c r="R58" t="n">
-        <v>7065120</v>
+        <v>7065235</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6540,6 +6513,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6566,10 +6544,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129060005</v>
+        <v>129060010</v>
       </c>
       <c r="B59" t="n">
-        <v>91553</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6577,34 +6555,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>468821</v>
+        <v>469310</v>
       </c>
       <c r="R59" t="n">
-        <v>7065043</v>
+        <v>7065244</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6637,6 +6620,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6663,10 +6651,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129059674</v>
+        <v>129060011</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6674,34 +6662,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>469226</v>
+        <v>469245</v>
       </c>
       <c r="R60" t="n">
-        <v>7065299</v>
+        <v>7065256</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6734,6 +6727,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6760,45 +6758,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129060043</v>
+        <v>129060012</v>
       </c>
       <c r="B61" t="n">
-        <v>75033</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>469011</v>
+        <v>469235</v>
       </c>
       <c r="R61" t="n">
-        <v>7065022</v>
+        <v>7065256</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6831,6 +6834,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6857,10 +6865,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129059675</v>
+        <v>129060013</v>
       </c>
       <c r="B62" t="n">
-        <v>91549</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6868,34 +6876,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>469197</v>
+        <v>469205</v>
       </c>
       <c r="R62" t="n">
-        <v>7065308</v>
+        <v>7065283</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6928,6 +6941,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6954,10 +6972,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129059687</v>
+        <v>129060014</v>
       </c>
       <c r="B63" t="n">
-        <v>80150</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6965,34 +6983,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>468843</v>
+        <v>469198</v>
       </c>
       <c r="R63" t="n">
-        <v>7065390</v>
+        <v>7065284</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7027,6 +7050,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7035,21 +7063,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7066,10 +7079,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129059686</v>
+        <v>129060015</v>
       </c>
       <c r="B64" t="n">
-        <v>83007</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7077,34 +7090,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>310</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>468843</v>
+        <v>469142</v>
       </c>
       <c r="R64" t="n">
-        <v>7065390</v>
+        <v>7065300</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7139,6 +7157,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7147,21 +7170,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7178,10 +7186,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129060050</v>
+        <v>129060016</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7189,34 +7197,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>469118</v>
+        <v>469152</v>
       </c>
       <c r="R65" t="n">
-        <v>7065190</v>
+        <v>7065299</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7253,7 +7266,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7280,10 +7293,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129060029</v>
+        <v>129060017</v>
       </c>
       <c r="B66" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7320,10 +7333,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468970</v>
+        <v>469122</v>
       </c>
       <c r="R66" t="n">
-        <v>7064946</v>
+        <v>7065303</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7387,10 +7400,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129060021</v>
+        <v>129060018</v>
       </c>
       <c r="B67" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7418,7 +7431,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7427,10 +7440,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468788</v>
+        <v>469093</v>
       </c>
       <c r="R67" t="n">
-        <v>7065344</v>
+        <v>7065345</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7494,10 +7507,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129060025</v>
+        <v>129060020</v>
       </c>
       <c r="B68" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7525,7 +7538,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7534,10 +7547,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>469101</v>
+        <v>468803</v>
       </c>
       <c r="R68" t="n">
-        <v>7065026</v>
+        <v>7065369</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7601,10 +7614,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129059682</v>
+        <v>129060021</v>
       </c>
       <c r="B69" t="n">
-        <v>91553</v>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7612,34 +7625,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>468990</v>
+        <v>468788</v>
       </c>
       <c r="R69" t="n">
-        <v>7065370</v>
+        <v>7065344</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7672,6 +7690,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7698,10 +7721,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129059670</v>
+        <v>129060022</v>
       </c>
       <c r="B70" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7729,7 +7752,7 @@
       <c r="I70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -7738,10 +7761,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>469326</v>
+        <v>468893</v>
       </c>
       <c r="R70" t="n">
-        <v>7065255</v>
+        <v>7065289</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7805,10 +7828,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129060011</v>
+        <v>129060023</v>
       </c>
       <c r="B71" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7845,10 +7868,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>469245</v>
+        <v>469142</v>
       </c>
       <c r="R71" t="n">
-        <v>7065256</v>
+        <v>7065079</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7912,10 +7935,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129060051</v>
+        <v>129060024</v>
       </c>
       <c r="B72" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7923,34 +7946,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>469121</v>
+        <v>469131</v>
       </c>
       <c r="R72" t="n">
-        <v>7064885</v>
+        <v>7065083</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7987,7 +8015,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Med apotechier</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8014,10 +8042,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129059677</v>
+        <v>129060025</v>
       </c>
       <c r="B73" t="n">
-        <v>78057</v>
+        <v>57953</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8025,34 +8053,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>469160</v>
+        <v>469101</v>
       </c>
       <c r="R73" t="n">
-        <v>7065329</v>
+        <v>7065026</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8085,6 +8118,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8111,10 +8149,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129059698</v>
+        <v>129060026</v>
       </c>
       <c r="B74" t="n">
-        <v>80150</v>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8122,34 +8160,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>469120</v>
+        <v>468886</v>
       </c>
       <c r="R74" t="n">
-        <v>7065078</v>
+        <v>7065015</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8184,6 +8227,11 @@
           <t>2025-10-11</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8192,21 +8240,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8223,10 +8256,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129059714</v>
+        <v>129060027</v>
       </c>
       <c r="B75" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8263,10 +8296,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>468946</v>
+        <v>468896</v>
       </c>
       <c r="R75" t="n">
-        <v>7064969</v>
+        <v>7064986</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8330,10 +8363,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129059701</v>
+        <v>129060029</v>
       </c>
       <c r="B76" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8370,10 +8403,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>468991</v>
+        <v>468970</v>
       </c>
       <c r="R76" t="n">
-        <v>7065056</v>
+        <v>7064946</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8437,45 +8470,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129060047</v>
+        <v>129060031</v>
       </c>
       <c r="B77" t="n">
-        <v>91926</v>
+        <v>57953</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>469012</v>
+        <v>469014</v>
       </c>
       <c r="R77" t="n">
-        <v>7065037</v>
+        <v>7064913</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8508,6 +8546,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8534,10 +8577,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129060040</v>
+        <v>129060032</v>
       </c>
       <c r="B78" t="n">
-        <v>80150</v>
+        <v>57953</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8545,34 +8588,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>469148</v>
+        <v>469043</v>
       </c>
       <c r="R78" t="n">
-        <v>7065056</v>
+        <v>7064905</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8605,6 +8653,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8631,10 +8684,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129059680</v>
+        <v>129060033</v>
       </c>
       <c r="B79" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8662,7 +8715,7 @@
       <c r="I79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8671,10 +8724,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>469094</v>
+        <v>469047</v>
       </c>
       <c r="R79" t="n">
-        <v>7065363</v>
+        <v>7064905</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8738,10 +8791,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129060016</v>
+        <v>129060035</v>
       </c>
       <c r="B80" t="n">
-        <v>57740</v>
+        <v>58114</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8749,27 +8802,31 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -8778,10 +8835,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>469152</v>
+        <v>469149</v>
       </c>
       <c r="R80" t="n">
-        <v>7065299</v>
+        <v>7065169</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8814,11 +8871,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8845,10 +8897,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129060014</v>
+        <v>129060036</v>
       </c>
       <c r="B81" t="n">
-        <v>57740</v>
+        <v>58114</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8856,27 +8908,27 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -8885,10 +8937,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>469198</v>
+        <v>468801</v>
       </c>
       <c r="R81" t="n">
-        <v>7065284</v>
+        <v>7065038</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8921,11 +8973,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8952,10 +8999,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129059676</v>
+        <v>129060037</v>
       </c>
       <c r="B82" t="n">
-        <v>83012</v>
+        <v>58114</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8963,34 +9010,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>469160</v>
+        <v>468874</v>
       </c>
       <c r="R82" t="n">
-        <v>7065329</v>
+        <v>7064975</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9049,10 +9101,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129059712</v>
+        <v>129060038</v>
       </c>
       <c r="B83" t="n">
-        <v>79044</v>
+        <v>58114</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9060,34 +9112,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Pennflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>468868</v>
+        <v>469007</v>
       </c>
       <c r="R83" t="n">
-        <v>7064989</v>
+        <v>7064930</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9146,10 +9203,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129059706</v>
+        <v>129059677</v>
       </c>
       <c r="B84" t="n">
-        <v>80150</v>
+        <v>78339</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9157,21 +9214,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9181,10 +9238,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>468850</v>
+        <v>469160</v>
       </c>
       <c r="R84" t="n">
-        <v>7065034</v>
+        <v>7065329</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9228,21 +9285,6 @@
       <c r="AG84" t="b">
         <v>0</v>
       </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
@@ -9255,420 +9297,6 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>129059696</v>
-      </c>
-      <c r="B85" t="n">
-        <v>91573</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Pennflon Ö, Jmt</t>
-        </is>
-      </c>
-      <c r="Q85" t="n">
-        <v>469141</v>
-      </c>
-      <c r="R85" t="n">
-        <v>7065095</v>
-      </c>
-      <c r="S85" t="n">
-        <v>10</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AD85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT85" t="inlineStr"/>
-      <c r="AW85" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>129059679</v>
-      </c>
-      <c r="B86" t="n">
-        <v>57740</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Pennflon Ö, Jmt</t>
-        </is>
-      </c>
-      <c r="Q86" t="n">
-        <v>469108</v>
-      </c>
-      <c r="R86" t="n">
-        <v>7065364</v>
-      </c>
-      <c r="S86" t="n">
-        <v>10</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT86" t="inlineStr"/>
-      <c r="AW86" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>129059713</v>
-      </c>
-      <c r="B87" t="n">
-        <v>57740</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Pennflon Ö, Jmt</t>
-        </is>
-      </c>
-      <c r="Q87" t="n">
-        <v>468922</v>
-      </c>
-      <c r="R87" t="n">
-        <v>7064998</v>
-      </c>
-      <c r="S87" t="n">
-        <v>10</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT87" t="inlineStr"/>
-      <c r="AW87" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>129059692</v>
-      </c>
-      <c r="B88" t="n">
-        <v>57740</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Pennflon Ö, Jmt</t>
-        </is>
-      </c>
-      <c r="Q88" t="n">
-        <v>469137</v>
-      </c>
-      <c r="R88" t="n">
-        <v>7065206</v>
-      </c>
-      <c r="S88" t="n">
-        <v>10</v>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>2025-10-11</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT88" t="inlineStr"/>
-      <c r="AW88" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43368-2025 artfynd.xlsx
+++ b/artfynd/A 43368-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AZ84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059694</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059686</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059709</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059675</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060046</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059682</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,6 +1431,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059702</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060002</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060003</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060005</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1799,6 +1854,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059708</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060047</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2008,6 +2073,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059687</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2120,6 +2190,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059698</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2232,6 +2307,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059700</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2344,6 +2424,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059706</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2456,6 +2541,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059710</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2553,6 +2643,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060039</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2650,6 +2745,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060040</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2747,6 +2847,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060041</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2844,6 +2949,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060006</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2941,6 +3051,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060001</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3038,6 +3153,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059671</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3135,6 +3255,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059674</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3232,6 +3357,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059678</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3329,6 +3459,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059683</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3426,6 +3561,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059689</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3523,6 +3663,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059691</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3620,6 +3765,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059699</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3717,6 +3867,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059703</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3814,6 +3969,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059712</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3916,6 +4076,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060050</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4018,6 +4183,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060051</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4115,6 +4285,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060043</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4212,6 +4387,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059676</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4309,6 +4489,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060042</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4421,6 +4606,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059695</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4533,6 +4723,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059697</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4645,6 +4840,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059711</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4742,6 +4942,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060044</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4839,6 +5044,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060045</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4936,6 +5146,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059690</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5043,6 +5258,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059670</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5150,6 +5370,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059679</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5257,6 +5482,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059680</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5364,6 +5594,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059681</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5471,6 +5706,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059684</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5578,6 +5818,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059685</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5685,6 +5930,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059692</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5792,6 +6042,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059701</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5899,6 +6154,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059704</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6006,6 +6266,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059713</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6113,6 +6378,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059714</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6220,6 +6490,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059715</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6327,6 +6602,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060007</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6434,6 +6714,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060008</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6541,6 +6826,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060009</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6648,6 +6938,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060010</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6755,6 +7050,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060011</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6862,6 +7162,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060012</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6969,6 +7274,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060013</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7076,6 +7386,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060014</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7183,6 +7498,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060015</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7290,6 +7610,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060016</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7397,6 +7722,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060017</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7504,6 +7834,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060018</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7611,6 +7946,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060020</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7718,6 +8058,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060021</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7825,6 +8170,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060022</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7932,6 +8282,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060023</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8039,6 +8394,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060024</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8146,6 +8506,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060025</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8253,6 +8618,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060026</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8360,6 +8730,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060027</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8467,6 +8842,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060029</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8574,6 +8954,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060031</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8681,6 +9066,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060032</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8788,6 +9178,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060033</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8894,6 +9289,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060035</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8996,6 +9396,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060036</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9098,6 +9503,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060037</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9200,6 +9610,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129060038</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9297,8 +9712,98 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129059677</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>